--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE242"/>
+  <dimension ref="A1:AE241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57938-2025</t>
+          <t>A 58185-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 57938-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58185-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54980-2021</t>
+          <t>A 7739-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44474</v>
+        <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 67835-2021</t>
+          <t>A 54980-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44525</v>
+        <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7739-2022</t>
+          <t>A 67835-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44608</v>
+        <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44454</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44487</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44617</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44462</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44511</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44830</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44867</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44888</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44629</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44752</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44735</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44480</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>44680</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44655</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44475</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44725</v>
+        <v>44734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44918</v>
+        <v>45755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45321</v>
+        <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44859</v>
+        <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44859</v>
+        <v>45735</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44979</v>
+        <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45432</v>
+        <v>44977</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45306</v>
+        <v>45483</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45529</v>
+        <v>44496</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44903</v>
+        <v>45013</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4549,7 +4549,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4559,14 +4559,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44476</v>
+        <v>45343</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45109</v>
+        <v>45184</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4651,8 +4651,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>11.8</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4695,7 +4700,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4709,10 +4714,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44496</v>
+        <v>45036</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4725,7 +4730,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4768,7 +4773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4782,10 +4787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44475</v>
+        <v>45275</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4798,7 +4803,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4841,7 +4846,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4851,14 +4856,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44511</v>
+        <v>45594</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4870,8 +4875,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4914,7 +4924,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4928,10 +4938,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45448</v>
+        <v>44937</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4944,7 +4954,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4987,7 +4997,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5001,10 +5011,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44617</v>
+        <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5016,13 +5026,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>4.7</v>
+        <v>17.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5065,7 +5070,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44917</v>
+        <v>45191</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5095,7 +5100,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44917</v>
+        <v>44593</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5211,7 +5216,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5225,10 +5230,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44910</v>
+        <v>44594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5241,7 +5246,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5284,7 +5289,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5298,10 +5303,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45041</v>
+        <v>46023</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5314,7 +5319,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5357,7 +5362,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44594</v>
+        <v>45120</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5386,8 +5391,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5430,7 +5440,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5444,10 +5454,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44671</v>
+        <v>45817</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5460,7 +5470,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5503,7 +5513,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5517,10 +5527,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45056</v>
+        <v>44999</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5532,8 +5542,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5576,7 +5591,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5590,10 +5605,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44937</v>
+        <v>46037</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5606,7 +5621,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5649,7 +5664,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5663,10 +5678,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45594</v>
+        <v>45076</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5679,7 +5694,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5722,7 +5737,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5736,10 +5751,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44938</v>
+        <v>45076</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5752,7 +5767,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5795,7 +5810,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5805,14 +5820,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45552</v>
+        <v>44623</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5825,7 +5840,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5868,7 +5883,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5882,10 +5897,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45803</v>
+        <v>44476</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5898,7 +5913,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5941,7 +5956,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5955,10 +5970,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45733</v>
+        <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5971,7 +5986,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6014,7 +6029,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6028,10 +6043,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44685</v>
+        <v>45905</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6044,7 +6059,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6087,7 +6102,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6101,10 +6116,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45905</v>
+        <v>44938</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6117,7 +6132,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6160,7 +6175,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6170,14 +6185,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45905</v>
+        <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6190,7 +6205,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6233,7 +6248,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6247,10 +6262,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46077</v>
+        <v>44678</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6263,7 +6278,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6306,7 +6321,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6320,10 +6335,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46077</v>
+        <v>45041</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6336,7 +6351,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6379,7 +6394,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6393,10 +6408,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45880</v>
+        <v>45803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6409,7 +6424,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6452,7 +6467,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6466,10 +6481,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44496</v>
+        <v>44918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6482,7 +6497,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6525,7 +6540,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6539,10 +6554,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44999</v>
+        <v>44685</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6554,13 +6569,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6603,7 +6613,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6617,10 +6627,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44496</v>
+        <v>45733</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6633,7 +6643,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6676,7 +6686,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6690,10 +6700,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45096</v>
+        <v>45576</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6705,13 +6715,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6754,7 +6759,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6764,14 +6769,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46069</v>
+        <v>45096</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6783,8 +6788,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6827,7 +6837,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6841,10 +6851,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45483</v>
+        <v>45210</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6857,7 +6867,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6900,7 +6910,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6914,10 +6924,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45051</v>
+        <v>45432</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6930,7 +6940,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6973,7 +6983,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45959</v>
+        <v>45754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7002,8 +7012,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7046,7 +7061,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7060,10 +7075,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45191</v>
+        <v>46077</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7076,7 +7091,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7119,7 +7134,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7133,10 +7148,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45297</v>
+        <v>46077</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7149,7 +7164,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7192,7 +7207,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7206,10 +7221,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45774</v>
+        <v>44511</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7222,7 +7237,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.5</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7265,7 +7280,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7279,10 +7294,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45440</v>
+        <v>45236</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7295,7 +7310,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7338,7 +7353,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7352,10 +7367,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44945</v>
+        <v>45880</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7368,7 +7383,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7411,7 +7426,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7421,14 +7436,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44888</v>
+        <v>46069</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7441,7 +7456,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7484,7 +7499,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7498,10 +7513,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45980</v>
+        <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7514,7 +7529,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7557,7 +7572,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7571,10 +7586,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45981</v>
+        <v>44594</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7586,13 +7601,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>15.9</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7635,7 +7645,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7649,10 +7659,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45982</v>
+        <v>44496</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7665,7 +7675,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7708,7 +7718,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7718,14 +7728,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46121</v>
+        <v>45175</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7738,7 +7748,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7781,7 +7791,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7795,10 +7805,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45237</v>
+        <v>45959</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7811,7 +7821,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7854,7 +7864,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7864,14 +7874,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45236</v>
+        <v>46121</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7884,7 +7894,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7927,7 +7937,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7941,10 +7951,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45053</v>
+        <v>44742</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7957,7 +7967,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8000,7 +8010,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8014,10 +8024,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45735</v>
+        <v>46135</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8030,7 +8040,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8073,7 +8083,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8087,10 +8097,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45076</v>
+        <v>45981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8102,8 +8112,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>15.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8146,7 +8161,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8160,10 +8175,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44474</v>
+        <v>45980</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8176,7 +8191,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8219,7 +8234,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8233,10 +8248,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44470</v>
+        <v>44902</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8249,7 +8264,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8292,7 +8307,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8306,10 +8321,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45076</v>
+        <v>45982</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8322,7 +8337,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8365,7 +8380,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8379,10 +8394,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45995</v>
+        <v>45582</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8395,7 +8410,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8438,7 +8453,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8452,10 +8467,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44468</v>
+        <v>46136</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8468,7 +8483,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8511,7 +8526,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8525,10 +8540,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45615</v>
+        <v>45294</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8541,7 +8556,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8.9</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8584,7 +8599,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8594,14 +8609,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46002</v>
+        <v>44474</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8614,7 +8629,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8657,7 +8672,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48550-2021</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8671,10 +8686,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44452</v>
+        <v>45529</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8687,7 +8702,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8730,7 +8745,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8744,10 +8759,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44918</v>
+        <v>45995</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8760,7 +8775,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8803,7 +8818,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8817,10 +8832,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46135</v>
+        <v>45278</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8876,7 +8891,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8890,10 +8905,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46136</v>
+        <v>45986</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8906,7 +8921,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8949,7 +8964,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8963,10 +8978,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45275</v>
+        <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8979,7 +8994,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9022,7 +9037,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9036,10 +9051,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45120</v>
+        <v>45636</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9051,13 +9066,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9100,7 +9110,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9110,14 +9120,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45021</v>
+        <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9130,7 +9140,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9173,7 +9183,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9187,10 +9197,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46023</v>
+        <v>44945</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9203,7 +9213,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9246,7 +9256,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9260,10 +9270,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46037</v>
+        <v>44943</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9276,7 +9286,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9319,7 +9329,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9329,14 +9339,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44623</v>
+        <v>45297</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9349,7 +9359,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9392,7 +9402,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9406,10 +9416,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45582</v>
+        <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9422,7 +9432,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9465,7 +9475,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9479,10 +9489,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45986</v>
+        <v>44917</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9495,7 +9505,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9538,7 +9548,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9552,10 +9562,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45275</v>
+        <v>44917</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9568,7 +9578,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9611,7 +9621,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9625,10 +9635,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44859</v>
+        <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9641,7 +9651,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9684,7 +9694,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9698,10 +9708,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44937</v>
+        <v>45247</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9714,7 +9724,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9757,7 +9767,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9771,10 +9781,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44990</v>
+        <v>45285</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9787,7 +9797,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9830,7 +9840,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9844,10 +9854,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45428</v>
+        <v>45239</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9860,7 +9870,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9903,7 +9913,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9917,10 +9927,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46136</v>
+        <v>44565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9933,7 +9943,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9976,7 +9986,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9990,10 +10000,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45174</v>
+        <v>45923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10006,7 +10016,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10049,7 +10059,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10059,14 +10069,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44977</v>
+        <v>44990</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10079,7 +10089,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10122,7 +10132,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10132,14 +10142,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45302</v>
+        <v>46155</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10152,7 +10162,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10195,7 +10205,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10209,10 +10219,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45418</v>
+        <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10225,7 +10235,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10268,7 +10278,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10282,10 +10292,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44993</v>
+        <v>45597</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10297,13 +10307,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>18.6</v>
+        <v>4.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10346,7 +10351,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10360,10 +10365,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44573</v>
+        <v>44859</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10376,7 +10381,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10419,7 +10424,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10433,10 +10438,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44967</v>
+        <v>46181</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10449,7 +10454,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10492,7 +10497,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10506,10 +10511,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45754</v>
+        <v>46181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10521,13 +10526,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10570,7 +10570,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10584,10 +10584,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45764</v>
+        <v>46181</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,13 +10599,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10648,7 +10643,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10662,10 +10657,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46147</v>
+        <v>46181</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10678,7 +10673,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10721,7 +10716,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10735,10 +10730,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44594</v>
+        <v>46181</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10751,7 +10746,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10794,7 +10789,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10808,10 +10803,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45630</v>
+        <v>46181</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10824,7 +10819,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10867,7 +10862,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10881,10 +10876,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45036</v>
+        <v>46181</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10897,7 +10892,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10940,7 +10935,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10950,14 +10945,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45923</v>
+        <v>44918</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10970,7 +10965,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11013,7 +11008,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11027,10 +11022,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44593</v>
+        <v>46195</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11043,7 +11038,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11086,7 +11081,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11100,10 +11095,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46155</v>
+        <v>45306</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11116,7 +11111,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11159,7 +11154,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11173,10 +11168,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45181</v>
+        <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11189,7 +11184,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11232,7 +11227,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11246,10 +11241,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44651</v>
+        <v>44859</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11261,13 +11256,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11310,7 +11300,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11324,10 +11314,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45905</v>
+        <v>45630</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11340,7 +11330,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11383,7 +11373,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11397,10 +11387,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45076</v>
+        <v>44859</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11413,7 +11403,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11456,7 +11446,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11470,10 +11460,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44594</v>
+        <v>44859</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11486,7 +11476,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11529,7 +11519,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11543,10 +11533,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44565</v>
+        <v>46253</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11559,7 +11549,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11602,7 +11592,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11616,10 +11606,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45069</v>
+        <v>44475</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11632,7 +11622,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11675,7 +11665,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11689,10 +11679,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45239</v>
+        <v>45191</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11705,7 +11695,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11748,7 +11738,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11762,10 +11752,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44642</v>
+        <v>46213</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11777,8 +11767,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11821,7 +11816,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11831,14 +11826,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45096</v>
+        <v>46213</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11852,11 +11847,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11899,7 +11894,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11913,10 +11908,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45109</v>
+        <v>44468</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11929,7 +11924,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11972,7 +11967,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11986,10 +11981,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45195</v>
+        <v>45056</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12001,13 +11996,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12050,7 +12040,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12064,10 +12054,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45247</v>
+        <v>46265</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12080,7 +12070,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12123,7 +12113,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12137,10 +12127,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44734</v>
+        <v>46265</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12152,8 +12142,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12196,7 +12191,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12210,10 +12205,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44791</v>
+        <v>46265</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12225,8 +12220,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12269,7 +12269,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12283,10 +12283,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45194</v>
+        <v>45109</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12356,10 +12356,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45135</v>
+        <v>44617</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12373,11 +12373,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12420,7 +12420,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12434,10 +12434,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45755</v>
+        <v>46265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12449,8 +12449,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12493,7 +12498,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12507,10 +12512,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45236</v>
+        <v>44893</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12523,7 +12528,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12566,7 +12571,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12580,10 +12585,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46181</v>
+        <v>45153</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12596,7 +12601,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12639,7 +12644,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12653,10 +12658,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46181</v>
+        <v>44990</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12669,7 +12674,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12712,7 +12717,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12726,10 +12731,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46181</v>
+        <v>44993</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12741,8 +12746,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.8</v>
+        <v>18.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12785,7 +12795,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12799,10 +12809,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46181</v>
+        <v>45755</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12815,7 +12825,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12858,7 +12868,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12872,10 +12882,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46181</v>
+        <v>46253</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12888,7 +12898,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12931,7 +12941,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12945,10 +12955,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46181</v>
+        <v>46231</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12961,7 +12971,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>10.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13004,7 +13014,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13014,14 +13024,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45755</v>
+        <v>45302</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13034,7 +13044,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13077,7 +13087,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13091,10 +13101,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46181</v>
+        <v>46274</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13106,8 +13116,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13150,7 +13165,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13164,10 +13179,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45317</v>
+        <v>46275</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13179,8 +13194,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13223,7 +13243,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13237,10 +13257,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44830</v>
+        <v>46274</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13253,7 +13273,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13296,7 +13316,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13310,10 +13330,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45294</v>
+        <v>45237</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13326,7 +13346,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13369,7 +13389,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13383,10 +13403,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45210</v>
+        <v>45195</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13398,8 +13418,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13442,7 +13467,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13456,10 +13481,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45120</v>
+        <v>46274</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13473,11 +13498,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13520,7 +13545,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13534,10 +13559,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44678</v>
+        <v>44470</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13550,7 +13575,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13593,7 +13618,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13607,10 +13632,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44608</v>
+        <v>44651</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13622,8 +13647,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13666,7 +13696,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13680,10 +13710,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45243</v>
+        <v>45774</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13696,7 +13726,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13739,7 +13769,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13753,10 +13783,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45191</v>
+        <v>45053</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13769,7 +13799,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13812,7 +13842,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13826,10 +13856,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46195</v>
+        <v>45072</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13841,8 +13871,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13885,7 +13920,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13895,14 +13930,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44990</v>
+        <v>45194</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13915,7 +13950,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13958,7 +13993,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13972,10 +14007,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44910</v>
+        <v>44979</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13987,13 +14022,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14036,7 +14066,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14050,10 +14080,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45498</v>
+        <v>44565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14066,7 +14096,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.2</v>
+        <v>13.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14109,7 +14139,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14123,10 +14153,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45576</v>
+        <v>45275</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14139,7 +14169,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14182,7 +14212,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14196,10 +14226,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44798</v>
+        <v>44725</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14212,7 +14242,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14255,7 +14285,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14265,14 +14295,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45343</v>
+        <v>44791</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14285,7 +14315,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14328,7 +14358,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14342,10 +14372,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45072</v>
+        <v>44942</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14357,13 +14387,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>9.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14406,7 +14431,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14420,10 +14445,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44942</v>
+        <v>45076</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14436,7 +14461,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>9.1</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14479,7 +14504,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14493,10 +14518,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45153</v>
+        <v>45120</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14508,8 +14533,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14552,7 +14582,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14566,10 +14596,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44565</v>
+        <v>44977</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14582,7 +14612,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>13.4</v>
+        <v>2.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14625,7 +14655,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14639,10 +14669,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44573</v>
+        <v>45096</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14654,8 +14684,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14698,7 +14733,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14712,10 +14747,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44859</v>
+        <v>45109</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14728,7 +14763,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>11.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14771,7 +14806,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14785,10 +14820,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45013</v>
+        <v>44888</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14801,7 +14836,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14844,7 +14879,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14858,10 +14893,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45597</v>
+        <v>45615</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14874,7 +14909,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.1</v>
+        <v>8.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14917,7 +14952,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14931,10 +14966,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45076</v>
+        <v>45448</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14947,7 +14982,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14990,7 +15025,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15004,10 +15039,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45110</v>
+        <v>45236</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15020,7 +15055,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15063,7 +15098,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15077,10 +15112,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46253</v>
+        <v>45076</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15093,7 +15128,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15136,7 +15171,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15150,10 +15185,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45175</v>
+        <v>45321</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15166,7 +15201,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15209,7 +15244,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15223,10 +15258,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45281</v>
+        <v>45053</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15239,7 +15274,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15282,7 +15317,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15296,10 +15331,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44830</v>
+        <v>45297</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15312,7 +15347,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15355,7 +15390,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15369,10 +15404,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44917</v>
+        <v>44830</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15385,7 +15420,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15428,7 +15463,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15438,14 +15473,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44938</v>
+        <v>45174</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15458,7 +15493,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15501,7 +15536,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15515,10 +15550,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44977</v>
+        <v>45552</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15531,7 +15566,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15574,7 +15609,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15588,10 +15623,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46213</v>
+        <v>45021</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15603,13 +15638,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15652,7 +15682,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15666,10 +15696,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45278</v>
+        <v>44917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15682,7 +15712,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15725,7 +15755,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15735,14 +15765,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46213</v>
+        <v>45110</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15754,13 +15784,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15803,7 +15828,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15817,10 +15842,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44859</v>
+        <v>44671</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15833,7 +15858,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15876,7 +15901,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15890,10 +15915,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45636</v>
+        <v>45317</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15906,7 +15931,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15949,7 +15974,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15963,10 +15988,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45184</v>
+        <v>45069</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15978,13 +16003,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16027,7 +16047,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16041,10 +16061,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44893</v>
+        <v>45498</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16057,7 +16077,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16100,7 +16120,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16114,10 +16134,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45053</v>
+        <v>45764</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16129,8 +16149,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16173,7 +16198,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16187,10 +16212,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46265</v>
+        <v>45418</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16203,7 +16228,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16246,7 +16271,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16260,10 +16285,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46265</v>
+        <v>45440</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16275,13 +16300,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16324,7 +16344,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16338,10 +16358,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46265</v>
+        <v>45181</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16353,13 +16373,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16402,7 +16417,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16416,10 +16431,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46265</v>
+        <v>45051</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16431,13 +16446,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16480,7 +16490,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16494,10 +16504,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45630</v>
+        <v>45243</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16510,7 +16520,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16553,7 +16563,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16567,10 +16577,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44742</v>
+        <v>45281</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16583,7 +16593,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16626,7 +16636,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16640,10 +16650,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45076</v>
+        <v>44798</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16656,7 +16666,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16699,7 +16709,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16713,10 +16723,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46253</v>
+        <v>45594</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16729,7 +16739,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16772,7 +16782,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16786,10 +16796,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46231</v>
+        <v>45735</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16801,8 +16811,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>10.1</v>
+        <v>1.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16845,7 +16860,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16859,10 +16874,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45285</v>
+        <v>45735</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16874,8 +16889,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16918,7 +16938,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16932,10 +16952,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45297</v>
+        <v>44573</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16948,7 +16968,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16991,7 +17011,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17005,10 +17025,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44902</v>
+        <v>45076</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17021,7 +17041,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17064,7 +17084,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17078,10 +17098,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44943</v>
+        <v>44608</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17094,7 +17114,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17137,7 +17157,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17151,10 +17171,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46274</v>
+        <v>44594</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17167,7 +17187,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17210,7 +17230,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17224,10 +17244,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46274</v>
+        <v>44910</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17245,7 +17265,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17288,7 +17308,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17302,10 +17322,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45735</v>
+        <v>45630</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17317,13 +17337,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17366,7 +17381,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17380,10 +17395,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45735</v>
+        <v>44967</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17395,13 +17410,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17444,7 +17454,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17458,10 +17468,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46274</v>
+        <v>45135</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17475,11 +17485,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17522,7 +17532,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17536,10 +17546,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46275</v>
+        <v>44496</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17551,13 +17561,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17600,7 +17605,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17614,10 +17619,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45749</v>
+        <v>44937</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17630,7 +17635,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17673,7 +17678,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17687,10 +17692,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45740</v>
+        <v>44938</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17702,13 +17707,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17768,7 +17768,7 @@
         <v>44744</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45226</v>
+        <v>45740</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17853,8 +17853,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17897,7 +17902,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17911,10 +17916,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45576</v>
+        <v>45749</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17927,7 +17932,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17970,7 +17975,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17984,10 +17989,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45755</v>
+        <v>45226</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18000,7 +18005,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18043,7 +18048,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18057,10 +18062,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45598</v>
+        <v>45755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18073,7 +18078,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18116,7 +18121,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18126,14 +18131,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45594</v>
+        <v>45576</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18145,13 +18150,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45576</v>
+        <v>45598</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>17.1</v>
+        <v>1.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18267,24 +18267,24 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>S 1502-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45817</v>
+        <v>45051</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18296,8 +18296,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18340,7 +18345,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 1502-2023</t>
+          <t>S 1214-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18354,10 +18359,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45051</v>
+        <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18371,11 +18376,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18418,7 +18423,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 1214-2025</t>
+          <t>S 1213-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18435,7 +18440,7 @@
         <v>45761</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18453,7 +18458,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18496,7 +18501,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 1213-2025</t>
+          <t>S 1266-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18510,10 +18515,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45761</v>
+        <v>45764</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18531,7 +18536,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18574,7 +18579,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S 1266-2025</t>
+          <t>S 1260-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18588,10 +18593,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45764</v>
+        <v>45763</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18609,7 +18614,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18649,10 +18654,10 @@
       </c>
       <c r="V240" s="2" t="inlineStr"/>
     </row>
-    <row r="241" ht="15" customHeight="1">
+    <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S 1260-2025</t>
+          <t>S 1137-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18666,10 +18671,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45763</v>
+        <v>45755</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18681,13 +18686,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I241" t="n">
-        <v>1.3</v>
+        <v>10.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18726,79 +18726,6 @@
         <v>0</v>
       </c>
       <c r="V241" s="2" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>S 1137-2025</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D242" s="1" t="n">
-        <v>45755</v>
-      </c>
-      <c r="E242" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I242" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J242" t="n">
-        <v>0</v>
-      </c>
-      <c r="K242" t="n">
-        <v>0</v>
-      </c>
-      <c r="L242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="n">
-        <v>0</v>
-      </c>
-      <c r="N242" t="n">
-        <v>0</v>
-      </c>
-      <c r="O242" t="n">
-        <v>0</v>
-      </c>
-      <c r="P242" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
-      <c r="S242" t="n">
-        <v>0</v>
-      </c>
-      <c r="T242" t="n">
-        <v>0</v>
-      </c>
-      <c r="U242" t="n">
-        <v>0</v>
-      </c>
-      <c r="V242" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE241"/>
+  <dimension ref="A1:AE240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58185-2025</t>
+          <t>A 57938-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45983</v>
+        <v>45982</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58185-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 57938-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45982</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7739-2022</t>
+          <t>A 54980-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44608</v>
+        <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54980-2021</t>
+          <t>A 7739-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44474</v>
+        <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49267-2021</t>
+          <t>A 58031-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44454</v>
+        <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58031-2021</t>
+          <t>A 9648-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44487</v>
+        <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9648-2022</t>
+          <t>A 51865-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44617</v>
+        <v>44462</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 51865-2021</t>
+          <t>A 7742-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44462</v>
+        <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2865,7 +2865,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7742-2022</t>
+          <t>A 64406-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44608</v>
+        <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 64406-2021</t>
+          <t>A 42161-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44511</v>
+        <v>44830</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42161-2022</t>
+          <t>A 51891-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44830</v>
+        <v>44867</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 51891-2022</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44867</v>
+        <v>44734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55645-2022</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44888</v>
+        <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11326-2022</t>
+          <t>A 55645-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44629</v>
+        <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>10.4</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29366-2022</t>
+          <t>A 17628-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44752</v>
+        <v>44680</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26244-2022</t>
+          <t>A 14522-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44735</v>
+        <v>44655</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3405,8 +3405,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3449,7 +3454,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56633-2021</t>
+          <t>A 12856-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44480</v>
+        <v>44642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3479,7 +3484,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>11.2</v>
+        <v>4.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3522,7 +3527,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17628-2022</t>
+          <t>A 11326-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3536,10 +3541,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44680</v>
+        <v>44629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3552,7 +3557,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3595,7 +3600,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14522-2022</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3609,10 +3614,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44655</v>
+        <v>44791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3624,13 +3629,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12856-2022</t>
+          <t>A 29366-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44642</v>
+        <v>44752</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 55450-2021</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44475</v>
+        <v>45194</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 26244-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44734</v>
+        <v>44735</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 56633-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45755</v>
+        <v>44480</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>11.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 55450-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44642</v>
+        <v>44475</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44830</v>
+        <v>45135</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4067,8 +4067,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4116,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4130,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45735</v>
+        <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4146,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4189,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4203,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44910</v>
+        <v>44918</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4219,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4262,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4276,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44977</v>
+        <v>45880</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4287,7 +4292,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4330,7 +4335,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4344,10 +4349,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45483</v>
+        <v>45321</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4360,7 +4365,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4403,7 +4408,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44496</v>
+        <v>45236</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4433,7 +4438,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4476,7 +4481,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4490,10 +4495,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45013</v>
+        <v>45755</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4506,7 +4511,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4549,7 +4554,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4559,14 +4564,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45343</v>
+        <v>44496</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4579,7 +4584,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4622,7 +4627,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4636,10 +4641,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45184</v>
+        <v>45317</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4649,11 +4654,6 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -4700,7 +4700,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45036</v>
+        <v>44979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45275</v>
+        <v>44859</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4856,14 +4856,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45594</v>
+        <v>44859</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4875,13 +4875,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4924,7 +4919,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44937</v>
+        <v>44830</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4954,7 +4949,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4997,7 +4992,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45576</v>
+        <v>45294</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5027,7 +5022,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>17.1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5070,7 +5065,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5084,10 +5079,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45191</v>
+        <v>45210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5100,7 +5095,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5143,7 +5138,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5173,7 +5168,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5216,7 +5211,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5230,10 +5225,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44594</v>
+        <v>45120</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5245,8 +5240,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46023</v>
+        <v>44678</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5362,7 +5362,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45120</v>
+        <v>45432</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5391,13 +5391,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5440,7 +5435,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5454,10 +5449,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45817</v>
+        <v>45306</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5470,7 +5465,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5513,7 +5508,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5527,10 +5522,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44999</v>
+        <v>45529</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5542,13 +5537,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5591,7 +5581,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5601,14 +5591,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46037</v>
+        <v>44903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5621,7 +5611,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5664,7 +5654,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5678,10 +5668,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45076</v>
+        <v>44476</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5694,7 +5684,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5737,7 +5727,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5751,10 +5741,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45076</v>
+        <v>45109</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5767,7 +5757,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>11.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5810,7 +5800,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5820,14 +5810,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44623</v>
+        <v>44496</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5840,7 +5830,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5883,7 +5873,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5893,14 +5883,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44476</v>
+        <v>46069</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5913,7 +5903,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5956,7 +5946,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5970,10 +5960,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45905</v>
+        <v>44608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5986,7 +5976,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6029,7 +6019,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6043,10 +6033,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45905</v>
+        <v>44475</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6059,7 +6049,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6102,7 +6092,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6116,10 +6106,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44938</v>
+        <v>45243</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6132,7 +6122,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6175,7 +6165,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6185,14 +6175,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44903</v>
+        <v>44511</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6205,7 +6195,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6248,7 +6238,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6262,10 +6252,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44678</v>
+        <v>45905</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6321,7 +6311,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6335,10 +6325,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45041</v>
+        <v>45905</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6351,7 +6341,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6394,7 +6384,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6408,10 +6398,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45803</v>
+        <v>45448</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6424,7 +6414,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6467,7 +6457,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6481,10 +6471,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44918</v>
+        <v>45191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6497,7 +6487,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6540,7 +6530,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6554,10 +6544,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44685</v>
+        <v>44617</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6569,8 +6559,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6613,7 +6608,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6627,10 +6622,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45733</v>
+        <v>44917</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6643,7 +6638,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6686,7 +6681,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6700,10 +6695,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45576</v>
+        <v>44917</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6716,7 +6711,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6759,7 +6754,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6773,10 +6768,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45096</v>
+        <v>44910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6788,13 +6783,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6837,7 +6827,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6851,10 +6841,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45210</v>
+        <v>45041</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6867,7 +6857,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6910,7 +6900,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6920,14 +6910,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45432</v>
+        <v>44990</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6940,7 +6930,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6983,7 +6973,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6993,14 +6983,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45754</v>
+        <v>46121</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7012,13 +7002,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7061,7 +7046,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7075,10 +7060,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46077</v>
+        <v>44671</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7091,7 +7076,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7134,7 +7119,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7148,10 +7133,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46077</v>
+        <v>45056</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7164,7 +7149,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7207,7 +7192,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7221,10 +7206,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44511</v>
+        <v>44937</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7237,7 +7222,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7280,7 +7265,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7294,10 +7279,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45236</v>
+        <v>45594</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7310,7 +7295,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7353,7 +7338,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7367,10 +7352,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45880</v>
+        <v>44938</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7383,7 +7368,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7426,7 +7411,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7436,14 +7421,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46069</v>
+        <v>44910</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7455,8 +7440,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7499,7 +7489,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7513,10 +7503,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45428</v>
+        <v>46135</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7529,7 +7519,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7572,7 +7562,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7586,10 +7576,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44594</v>
+        <v>46136</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7602,7 +7592,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7645,7 +7635,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7659,10 +7649,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44496</v>
+        <v>45552</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7675,7 +7665,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7718,7 +7708,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7732,10 +7722,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45175</v>
+        <v>45959</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7748,7 +7738,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7791,7 +7781,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7805,10 +7795,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45959</v>
+        <v>45582</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7821,7 +7811,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7864,7 +7854,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7874,14 +7864,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46121</v>
+        <v>45986</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7894,7 +7884,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7937,7 +7927,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7951,10 +7941,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44742</v>
+        <v>45498</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7967,7 +7957,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8010,7 +8000,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8024,10 +8014,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46135</v>
+        <v>44496</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8040,7 +8030,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8083,7 +8073,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8097,10 +8087,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45981</v>
+        <v>45576</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8112,13 +8102,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>15.9</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8161,7 +8146,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8175,10 +8160,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45980</v>
+        <v>46136</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8191,7 +8176,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8234,7 +8219,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8248,10 +8233,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44902</v>
+        <v>44999</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8263,8 +8248,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8307,7 +8297,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8321,10 +8311,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45982</v>
+        <v>45980</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8337,7 +8327,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8380,7 +8370,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8394,10 +8384,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45582</v>
+        <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8453,7 +8443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8467,10 +8457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46136</v>
+        <v>45981</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8482,8 +8472,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>15.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8526,7 +8521,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8540,10 +8535,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45294</v>
+        <v>45982</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8556,7 +8551,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8599,7 +8594,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8609,14 +8604,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44474</v>
+        <v>45343</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8629,7 +8624,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8672,7 +8667,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8686,10 +8681,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45529</v>
+        <v>45072</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8701,8 +8696,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8745,7 +8745,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8759,10 +8759,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45995</v>
+        <v>44942</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.4</v>
+        <v>9.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8818,7 +8818,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8832,10 +8832,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45278</v>
+        <v>45096</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8847,8 +8847,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8891,7 +8896,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8905,10 +8910,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45986</v>
+        <v>45153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8921,7 +8926,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8964,7 +8969,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8978,10 +8983,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46136</v>
+        <v>44474</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8994,7 +8999,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9037,7 +9042,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9051,10 +9056,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45636</v>
+        <v>44565</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9067,7 +9072,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>13.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9110,7 +9115,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9120,14 +9125,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46002</v>
+        <v>44573</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9140,7 +9145,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9183,7 +9188,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9197,10 +9202,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44945</v>
+        <v>45995</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9213,7 +9218,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9256,7 +9261,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9270,10 +9275,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44943</v>
+        <v>46147</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9286,7 +9291,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9329,7 +9334,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9343,10 +9348,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45297</v>
+        <v>45483</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9359,7 +9364,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9402,7 +9407,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9412,14 +9417,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44573</v>
+        <v>46002</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9432,7 +9437,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9475,7 +9480,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9489,10 +9494,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44917</v>
+        <v>45051</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9505,7 +9510,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9548,7 +9553,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9558,14 +9563,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44917</v>
+        <v>45923</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9578,7 +9583,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9621,7 +9626,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9635,10 +9640,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46147</v>
+        <v>45191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9651,7 +9656,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9694,7 +9699,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9708,10 +9713,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45247</v>
+        <v>45297</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9724,7 +9729,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9767,7 +9772,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9781,10 +9786,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45285</v>
+        <v>45774</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9797,7 +9802,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9840,7 +9845,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9854,10 +9859,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45239</v>
+        <v>44859</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9870,7 +9875,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9913,7 +9918,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9927,10 +9932,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44565</v>
+        <v>46155</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9943,7 +9948,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9986,7 +9991,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9996,14 +10001,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45923</v>
+        <v>45013</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10016,7 +10021,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10059,7 +10064,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10069,14 +10074,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44990</v>
+        <v>45440</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10089,7 +10094,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10132,7 +10137,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10146,10 +10151,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46155</v>
+        <v>44945</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10162,7 +10167,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10222,7 +10227,7 @@
         <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10278,7 +10283,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10292,10 +10297,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45597</v>
+        <v>44888</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10308,7 +10313,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10351,7 +10356,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10365,10 +10370,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44859</v>
+        <v>46023</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10381,7 +10386,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10424,7 +10429,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10438,10 +10443,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46181</v>
+        <v>45237</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10454,7 +10459,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10497,7 +10502,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10511,10 +10516,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46181</v>
+        <v>45236</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10527,7 +10532,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10570,7 +10575,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10584,10 +10589,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46181</v>
+        <v>45053</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10600,7 +10605,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10643,7 +10648,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10657,10 +10662,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46181</v>
+        <v>45735</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10673,7 +10678,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10716,7 +10721,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10730,10 +10735,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46181</v>
+        <v>45076</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10746,7 +10751,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10789,7 +10794,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10803,10 +10808,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46181</v>
+        <v>46037</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10819,7 +10824,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10862,7 +10867,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10876,10 +10881,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46181</v>
+        <v>44470</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10892,7 +10897,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10935,7 +10940,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10949,10 +10954,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44918</v>
+        <v>45076</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10965,7 +10970,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11008,7 +11013,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11022,10 +11027,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46195</v>
+        <v>45597</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11038,7 +11043,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11081,7 +11086,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11095,10 +11100,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45306</v>
+        <v>44468</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11111,7 +11116,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11154,7 +11159,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11168,10 +11173,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44859</v>
+        <v>45615</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11184,7 +11189,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>8.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11227,7 +11232,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11241,10 +11246,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44859</v>
+        <v>45076</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11257,7 +11262,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11300,7 +11305,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11314,10 +11319,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45630</v>
+        <v>44918</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11330,7 +11335,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11373,7 +11378,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11387,10 +11392,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44859</v>
+        <v>46181</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11403,7 +11408,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11446,7 +11451,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11460,10 +11465,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44859</v>
+        <v>45275</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11476,7 +11481,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11519,7 +11524,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11533,10 +11538,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46253</v>
+        <v>46181</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11549,7 +11554,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11592,7 +11597,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11606,10 +11611,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44475</v>
+        <v>46181</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11622,7 +11627,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11665,7 +11670,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11679,10 +11684,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45191</v>
+        <v>46181</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11695,7 +11700,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11738,7 +11743,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11752,10 +11757,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46213</v>
+        <v>46181</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11767,13 +11772,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11816,7 +11816,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11826,14 +11826,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46213</v>
+        <v>46181</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11845,13 +11845,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11894,7 +11889,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11908,10 +11903,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44468</v>
+        <v>45120</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11921,6 +11916,11 @@
       <c r="G150" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -11967,7 +11967,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11981,10 +11981,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45056</v>
+        <v>45021</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12040,7 +12040,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12054,10 +12054,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46265</v>
+        <v>46181</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12113,7 +12113,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46265</v>
+        <v>46077</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12142,13 +12142,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12191,7 +12186,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12205,10 +12200,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46265</v>
+        <v>46077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12220,13 +12215,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12269,7 +12259,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12283,10 +12273,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45109</v>
+        <v>45110</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12299,7 +12289,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12342,7 +12332,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12352,14 +12342,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44617</v>
+        <v>44623</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12371,13 +12361,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12420,7 +12405,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12434,10 +12419,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46265</v>
+        <v>45275</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12449,13 +12434,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12498,7 +12478,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12512,10 +12492,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44893</v>
+        <v>45175</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12528,7 +12508,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12571,7 +12551,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12585,10 +12565,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45153</v>
+        <v>44859</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12601,7 +12581,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12644,7 +12624,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12658,10 +12638,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44990</v>
+        <v>45281</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12674,7 +12654,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12717,7 +12697,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12731,10 +12711,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44993</v>
+        <v>44830</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12746,13 +12726,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>18.6</v>
+        <v>2.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12795,7 +12770,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12809,10 +12784,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45755</v>
+        <v>46195</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12825,7 +12800,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12868,7 +12843,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12882,10 +12857,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46253</v>
+        <v>44917</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12898,7 +12873,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12941,7 +12916,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12955,10 +12930,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46231</v>
+        <v>44937</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12971,7 +12946,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>10.1</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13014,7 +12989,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13024,14 +12999,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45302</v>
+        <v>44938</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13044,7 +13019,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13087,7 +13062,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13101,10 +13076,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46274</v>
+        <v>44977</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13116,13 +13091,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13165,7 +13135,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13179,10 +13149,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46275</v>
+        <v>45278</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13194,13 +13164,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13243,7 +13208,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13257,10 +13222,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46274</v>
+        <v>44990</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13273,7 +13238,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13316,7 +13281,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13330,10 +13295,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45237</v>
+        <v>45428</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13346,7 +13311,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13389,7 +13354,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13403,10 +13368,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45195</v>
+        <v>44859</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13418,13 +13383,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13467,7 +13427,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13481,10 +13441,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46274</v>
+        <v>45636</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13496,13 +13456,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13545,7 +13500,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13555,14 +13510,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44470</v>
+        <v>45174</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13575,7 +13530,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13618,7 +13573,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13632,10 +13587,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44651</v>
+        <v>44977</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13647,13 +13602,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13696,7 +13646,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13706,14 +13656,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45774</v>
+        <v>45302</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13726,7 +13676,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13769,7 +13719,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13783,10 +13733,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45053</v>
+        <v>45418</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13799,7 +13749,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13842,7 +13792,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13856,10 +13806,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45072</v>
+        <v>44993</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13873,11 +13823,11 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.1</v>
+        <v>18.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13920,7 +13870,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13934,10 +13884,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45194</v>
+        <v>44573</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13950,7 +13900,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13993,7 +13943,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14007,10 +13957,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44979</v>
+        <v>45184</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14022,8 +13972,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14066,7 +14021,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14080,10 +14035,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44565</v>
+        <v>44967</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14096,7 +14051,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>13.4</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14139,7 +14094,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14153,10 +14108,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45275</v>
+        <v>45754</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14168,8 +14123,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14212,7 +14172,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14226,10 +14186,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44725</v>
+        <v>45764</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14241,8 +14201,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14285,7 +14250,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14299,10 +14264,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44791</v>
+        <v>44893</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14315,7 +14280,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>8.800000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14358,7 +14323,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14372,10 +14337,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44942</v>
+        <v>44594</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14388,7 +14353,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>9.1</v>
+        <v>1.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14431,7 +14396,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14445,10 +14410,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45076</v>
+        <v>45630</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14461,7 +14426,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14504,7 +14469,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14518,10 +14483,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45120</v>
+        <v>45036</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14533,13 +14498,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14582,7 +14542,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14596,10 +14556,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44977</v>
+        <v>45053</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14612,7 +14572,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14655,7 +14615,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14669,10 +14629,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45096</v>
+        <v>44593</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14684,13 +14644,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14733,7 +14688,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14747,10 +14702,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45109</v>
+        <v>45181</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14763,7 +14718,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>11.8</v>
+        <v>5.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14806,7 +14761,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14820,10 +14775,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44888</v>
+        <v>44651</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14835,8 +14790,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14879,7 +14839,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14893,10 +14853,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45615</v>
+        <v>46253</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14909,7 +14869,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>8.9</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14952,7 +14912,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14966,10 +14926,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45448</v>
+        <v>45076</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14982,7 +14942,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15025,7 +14985,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15039,10 +14999,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45236</v>
+        <v>44594</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15055,7 +15015,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15098,7 +15058,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15112,10 +15072,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45076</v>
+        <v>44565</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15128,7 +15088,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15171,7 +15131,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15185,10 +15145,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45321</v>
+        <v>46213</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15200,8 +15160,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15244,7 +15209,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15258,10 +15223,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45053</v>
+        <v>45069</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15274,7 +15239,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15317,7 +15282,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15331,10 +15296,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45297</v>
+        <v>45239</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15347,7 +15312,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15390,7 +15355,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15400,14 +15365,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44830</v>
+        <v>46213</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15419,8 +15384,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15463,7 +15433,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15473,14 +15443,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45174</v>
+        <v>44642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15493,7 +15463,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15536,7 +15506,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15550,10 +15520,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45552</v>
+        <v>45096</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15565,8 +15535,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15609,7 +15584,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15623,10 +15598,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45021</v>
+        <v>45109</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15639,7 +15614,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15682,7 +15657,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15696,10 +15671,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44917</v>
+        <v>45195</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15711,8 +15686,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15755,7 +15735,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15769,10 +15749,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45110</v>
+        <v>45247</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15785,7 +15765,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15828,7 +15808,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15842,10 +15822,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44671</v>
+        <v>45630</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15858,7 +15838,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15901,7 +15881,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15915,10 +15895,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45317</v>
+        <v>44742</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15931,7 +15911,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15974,7 +15954,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15988,10 +15968,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45069</v>
+        <v>46265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16004,7 +15984,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16047,7 +16027,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16061,10 +16041,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45498</v>
+        <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16076,8 +16056,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16120,7 +16105,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16134,10 +16119,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45764</v>
+        <v>45076</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16149,13 +16134,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16198,7 +16178,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16212,10 +16192,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45418</v>
+        <v>46265</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16227,8 +16207,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16271,7 +16256,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16285,10 +16270,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45440</v>
+        <v>46265</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16300,8 +16285,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16344,7 +16334,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16358,10 +16348,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45181</v>
+        <v>45285</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16374,7 +16364,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16417,7 +16407,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16431,10 +16421,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45051</v>
+        <v>45297</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16447,7 +16437,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16490,7 +16480,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16504,10 +16494,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45243</v>
+        <v>46253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16520,7 +16510,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16563,7 +16553,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16577,10 +16567,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45281</v>
+        <v>44902</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16593,7 +16583,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16636,7 +16626,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16650,10 +16640,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44798</v>
+        <v>46231</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16666,7 +16656,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16709,7 +16699,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16723,10 +16713,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45594</v>
+        <v>44943</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16739,7 +16729,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16782,7 +16772,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16796,10 +16786,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45735</v>
+        <v>46274</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16811,13 +16801,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16860,7 +16845,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16877,7 +16862,7 @@
         <v>45735</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16895,7 +16880,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16938,7 +16923,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16952,10 +16937,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44573</v>
+        <v>45735</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16967,8 +16952,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17011,7 +17001,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17025,10 +17015,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45076</v>
+        <v>46274</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17040,8 +17030,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17084,7 +17079,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17098,10 +17093,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44608</v>
+        <v>46274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17113,8 +17108,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44594</v>
+        <v>46275</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17186,8 +17186,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17230,7 +17235,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17244,10 +17249,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44910</v>
+        <v>45749</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17259,13 +17264,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17308,7 +17308,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17322,10 +17322,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45630</v>
+        <v>45740</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17337,8 +17337,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17381,7 +17386,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17395,10 +17400,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44967</v>
+        <v>44744</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17411,7 +17416,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17454,7 +17459,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17468,10 +17473,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45135</v>
+        <v>45226</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17483,13 +17488,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17546,10 +17546,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44496</v>
+        <v>45576</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17605,7 +17605,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17619,10 +17619,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44937</v>
+        <v>45755</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17678,7 +17678,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17692,10 +17692,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44938</v>
+        <v>45598</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17761,14 +17761,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44744</v>
+        <v>45594</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17780,8 +17780,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17824,7 +17829,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17838,10 +17843,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45740</v>
+        <v>45576</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17853,13 +17858,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>2.2</v>
+        <v>17.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17902,7 +17902,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17916,10 +17916,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45749</v>
+        <v>45817</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6.7</v>
+        <v>3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17989,10 +17989,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45226</v>
+        <v>45803</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45755</v>
+        <v>45733</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45576</v>
+        <v>44685</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18194,24 +18194,24 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>S 1502-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45598</v>
+        <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18223,8 +18223,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18267,7 +18272,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 1502-2023</t>
+          <t>S 1214-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18281,10 +18286,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45051</v>
+        <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18298,11 +18303,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18345,7 +18350,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 1214-2025</t>
+          <t>S 1213-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18362,7 +18367,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18380,7 +18385,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18423,7 +18428,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 1213-2025</t>
+          <t>S 1266-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18437,10 +18442,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45761</v>
+        <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18458,7 +18463,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18501,7 +18506,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 1266-2025</t>
+          <t>S 1260-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18515,10 +18520,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45764</v>
+        <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18536,7 +18541,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18576,10 +18581,10 @@
       </c>
       <c r="V239" s="2" t="inlineStr"/>
     </row>
-    <row r="240" ht="15" customHeight="1">
+    <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S 1260-2025</t>
+          <t>S 1137-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18593,10 +18598,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45763</v>
+        <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18608,13 +18613,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>1.3</v>
+        <v>10.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18653,79 +18653,6 @@
         <v>0</v>
       </c>
       <c r="V240" s="2" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>S 1137-2025</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D241" s="1" t="n">
-        <v>45755</v>
-      </c>
-      <c r="E241" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I241" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J241" t="n">
-        <v>0</v>
-      </c>
-      <c r="K241" t="n">
-        <v>0</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>0</v>
-      </c>
-      <c r="O241" t="n">
-        <v>0</v>
-      </c>
-      <c r="P241" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" t="n">
-        <v>0</v>
-      </c>
-      <c r="T241" t="n">
-        <v>0</v>
-      </c>
-      <c r="U241" t="n">
-        <v>0</v>
-      </c>
-      <c r="V241" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57938-2025</t>
+          <t>A 58185-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 57938-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58185-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44462</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7742-2022</t>
+          <t>A 64406-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44608</v>
+        <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2865,7 +2865,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 64406-2021</t>
+          <t>A 42161-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44511</v>
+        <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42161-2022</t>
+          <t>A 7742-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44830</v>
+        <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>44867</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 55645-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44734</v>
+        <v>44888</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 11326-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44725</v>
+        <v>44629</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>10.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55645-2022</t>
+          <t>A 29366-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44888</v>
+        <v>44752</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17628-2022</t>
+          <t>A 26244-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44680</v>
+        <v>44735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 14522-2022</t>
+          <t>A 56633-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44655</v>
+        <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3405,13 +3405,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>11.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3454,7 +3449,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12856-2022</t>
+          <t>A 17628-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44642</v>
+        <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3484,7 +3479,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3527,7 +3522,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11326-2022</t>
+          <t>A 14522-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3541,10 +3536,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44629</v>
+        <v>44655</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3556,8 +3551,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>10.4</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 12856-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44791</v>
+        <v>44642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29366-2022</t>
+          <t>A 55450-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44752</v>
+        <v>44475</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45194</v>
+        <v>44734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26244-2022</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44735</v>
+        <v>45755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56633-2021</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44480</v>
+        <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>11.2</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55450-2021</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44475</v>
+        <v>44830</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45135</v>
+        <v>45735</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4067,13 +4067,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4116,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4130,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45755</v>
+        <v>44910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4146,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4189,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4203,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44918</v>
+        <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4219,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4262,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4276,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45880</v>
+        <v>45483</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4292,7 +4287,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4335,7 +4330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4349,10 +4344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45321</v>
+        <v>44496</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4365,7 +4360,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4408,7 +4403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4422,10 +4417,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45236</v>
+        <v>45013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4438,7 +4433,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4481,7 +4476,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4491,14 +4486,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45755</v>
+        <v>45343</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4511,7 +4506,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4554,7 +4549,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,10 +4563,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44496</v>
+        <v>45184</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4583,8 +4578,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45317</v>
+        <v>45036</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44979</v>
+        <v>45275</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44859</v>
+        <v>45191</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44859</v>
+        <v>44937</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44830</v>
+        <v>44594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45294</v>
+        <v>45120</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5021,8 +5021,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5065,7 +5070,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45210</v>
+        <v>44593</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5095,7 +5100,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44594</v>
+        <v>45576</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>17.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5211,7 +5216,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5225,10 +5230,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45120</v>
+        <v>44999</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5242,7 +5247,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -5289,7 +5294,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5303,10 +5308,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44678</v>
+        <v>45076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5319,7 +5324,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5362,7 +5367,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5376,10 +5381,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45432</v>
+        <v>45076</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5392,7 +5397,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5435,7 +5440,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5445,14 +5450,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45306</v>
+        <v>44623</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5465,7 +5470,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5508,7 +5513,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5522,10 +5527,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45529</v>
+        <v>44476</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5538,7 +5543,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5581,7 +5586,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5591,14 +5596,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44903</v>
+        <v>44938</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5611,7 +5616,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5654,7 +5659,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5668,10 +5673,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44476</v>
+        <v>45817</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5684,7 +5689,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5727,7 +5732,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5737,14 +5742,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45109</v>
+        <v>44903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5757,7 +5762,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11.8</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5800,7 +5805,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5814,10 +5819,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44496</v>
+        <v>44678</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5830,7 +5835,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5873,7 +5878,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5883,14 +5888,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46069</v>
+        <v>45041</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5903,7 +5908,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5946,7 +5951,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5960,10 +5965,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44608</v>
+        <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5976,7 +5981,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6019,7 +6024,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6033,10 +6038,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44475</v>
+        <v>45905</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6049,7 +6054,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6092,7 +6097,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6106,10 +6111,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45243</v>
+        <v>44918</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6122,7 +6127,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6165,7 +6170,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6179,10 +6184,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44511</v>
+        <v>45576</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6195,7 +6200,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6238,7 +6243,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6252,10 +6257,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45905</v>
+        <v>45096</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6267,8 +6272,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6311,7 +6321,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6325,10 +6335,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45905</v>
+        <v>45210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6341,7 +6351,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6384,7 +6394,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6398,10 +6408,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45448</v>
+        <v>45432</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6414,7 +6424,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6457,7 +6467,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6471,10 +6481,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45191</v>
+        <v>45754</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6486,8 +6496,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6530,7 +6545,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6544,10 +6559,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44617</v>
+        <v>44511</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6559,13 +6574,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6608,7 +6618,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6622,10 +6632,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44917</v>
+        <v>45803</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6638,7 +6648,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6681,7 +6691,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6695,10 +6705,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44917</v>
+        <v>45236</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6711,7 +6721,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6754,7 +6764,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6768,10 +6778,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44910</v>
+        <v>46037</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6784,7 +6794,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6827,7 +6837,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6841,10 +6851,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45041</v>
+        <v>44685</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6857,7 +6867,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6900,7 +6910,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6910,14 +6920,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44990</v>
+        <v>45733</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6930,7 +6940,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6973,7 +6983,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6983,14 +6993,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46121</v>
+        <v>45428</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7003,7 +7013,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7046,7 +7056,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7060,10 +7070,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44671</v>
+        <v>45175</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7076,7 +7086,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7119,7 +7129,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7133,10 +7143,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45056</v>
+        <v>45880</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7149,7 +7159,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7192,7 +7202,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7206,10 +7216,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44937</v>
+        <v>44594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7222,7 +7232,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7265,7 +7275,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7279,10 +7289,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45594</v>
+        <v>45959</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7295,7 +7305,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7338,7 +7348,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7352,10 +7362,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44938</v>
+        <v>44496</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7368,7 +7378,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7411,7 +7421,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7425,10 +7435,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44910</v>
+        <v>44742</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7440,13 +7450,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7489,7 +7494,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7503,10 +7508,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46135</v>
+        <v>44902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7519,7 +7524,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7562,7 +7567,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7576,10 +7581,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46136</v>
+        <v>45294</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7592,7 +7597,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7635,7 +7640,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7649,10 +7654,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45552</v>
+        <v>45981</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7664,8 +7669,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>15.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7708,7 +7718,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7722,10 +7732,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45959</v>
+        <v>45980</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7738,7 +7748,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7781,7 +7791,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7795,10 +7805,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45582</v>
+        <v>45982</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7811,7 +7821,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7854,7 +7864,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7868,10 +7878,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45986</v>
+        <v>45529</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7884,7 +7894,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7927,7 +7937,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7941,10 +7951,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45498</v>
+        <v>46077</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7957,7 +7967,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8000,7 +8010,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8014,10 +8024,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44496</v>
+        <v>46077</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8030,7 +8040,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8073,7 +8083,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8087,10 +8097,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45576</v>
+        <v>45278</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8103,7 +8113,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8146,7 +8156,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8160,10 +8170,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46136</v>
+        <v>44474</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8176,7 +8186,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8219,7 +8229,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8233,10 +8243,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44999</v>
+        <v>45636</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8248,13 +8258,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8297,7 +8302,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8311,10 +8316,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45980</v>
+        <v>44945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8327,7 +8332,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8370,7 +8375,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8384,10 +8389,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44798</v>
+        <v>45995</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8400,7 +8405,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8443,7 +8448,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8457,10 +8462,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45981</v>
+        <v>44943</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8472,13 +8477,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>15.9</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8521,7 +8521,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8531,14 +8531,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45982</v>
+        <v>46002</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8594,7 +8594,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8604,14 +8604,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45343</v>
+        <v>46069</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8667,7 +8667,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8681,10 +8681,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45072</v>
+        <v>45297</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8696,13 +8696,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8745,7 +8740,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8759,10 +8754,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44942</v>
+        <v>46023</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8775,7 +8770,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>9.1</v>
+        <v>4.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8818,7 +8813,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8832,10 +8827,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45096</v>
+        <v>44573</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8847,13 +8842,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8896,7 +8886,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8910,10 +8900,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45153</v>
+        <v>44917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8926,7 +8916,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8969,7 +8959,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8983,10 +8973,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44474</v>
+        <v>44917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8999,7 +8989,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9042,7 +9032,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9056,10 +9046,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44565</v>
+        <v>45247</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9072,7 +9062,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>13.4</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9115,7 +9105,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9129,10 +9119,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44573</v>
+        <v>45285</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9145,7 +9135,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9188,7 +9178,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9202,10 +9192,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45995</v>
+        <v>45239</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9218,7 +9208,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9261,7 +9251,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9275,10 +9265,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46147</v>
+        <v>44565</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9291,7 +9281,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9334,7 +9324,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9344,14 +9334,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45483</v>
+        <v>44990</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9364,7 +9354,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9407,7 +9397,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9417,14 +9407,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46002</v>
+        <v>45597</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9437,7 +9427,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9480,7 +9470,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9490,14 +9480,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45051</v>
+        <v>46121</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9510,7 +9500,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9553,7 +9543,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9563,14 +9553,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45923</v>
+        <v>44859</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9583,7 +9573,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9626,7 +9616,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9640,10 +9630,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45191</v>
+        <v>44918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9656,7 +9646,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9699,7 +9689,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9713,10 +9703,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45297</v>
+        <v>45306</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9729,7 +9719,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9772,7 +9762,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9786,10 +9776,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45774</v>
+        <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9802,7 +9792,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9845,7 +9835,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9862,7 +9852,7 @@
         <v>44859</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9875,7 +9865,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9918,7 +9908,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9932,10 +9922,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46155</v>
+        <v>46135</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9948,7 +9938,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9991,7 +9981,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10005,10 +9995,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45013</v>
+        <v>45630</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10021,7 +10011,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10064,7 +10054,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10078,10 +10068,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45440</v>
+        <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10094,7 +10084,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10137,7 +10127,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10151,10 +10141,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44945</v>
+        <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10167,7 +10157,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10210,7 +10200,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10224,10 +10214,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45905</v>
+        <v>44475</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10240,7 +10230,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10283,7 +10273,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10297,10 +10287,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44888</v>
+        <v>45191</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10313,7 +10303,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10356,7 +10346,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10370,10 +10360,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46023</v>
+        <v>45582</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10386,7 +10376,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10429,7 +10419,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10443,10 +10433,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45237</v>
+        <v>46136</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10459,7 +10449,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10502,7 +10492,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10516,10 +10506,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45236</v>
+        <v>44468</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10532,7 +10522,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10575,7 +10565,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10589,10 +10579,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45053</v>
+        <v>45056</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10605,7 +10595,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10648,7 +10638,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10662,10 +10652,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45735</v>
+        <v>45109</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10678,7 +10668,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10721,7 +10711,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10735,10 +10725,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45076</v>
+        <v>44617</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10750,8 +10740,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10794,7 +10789,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10808,10 +10803,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46037</v>
+        <v>44893</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10824,7 +10819,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10867,7 +10862,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10881,10 +10876,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44470</v>
+        <v>45153</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10897,7 +10892,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.7</v>
+        <v>0.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10940,7 +10935,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10954,10 +10949,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45076</v>
+        <v>45986</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10970,7 +10965,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11013,7 +11008,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11027,10 +11022,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45597</v>
+        <v>46136</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11043,7 +11038,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11086,7 +11081,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11100,10 +11095,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44468</v>
+        <v>44990</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11116,7 +11111,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11159,7 +11154,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11173,10 +11168,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45615</v>
+        <v>44993</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11188,8 +11183,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>8.9</v>
+        <v>18.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11232,7 +11232,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45076</v>
+        <v>45755</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11315,14 +11315,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44918</v>
+        <v>45302</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11392,10 +11392,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46181</v>
+        <v>45237</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11451,7 +11451,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11465,10 +11465,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45275</v>
+        <v>45195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11480,8 +11480,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11524,7 +11529,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11538,10 +11543,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46181</v>
+        <v>44470</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11554,7 +11559,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11597,7 +11602,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11611,10 +11616,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46181</v>
+        <v>44651</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11626,8 +11631,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11670,7 +11680,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11684,10 +11694,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46181</v>
+        <v>46147</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11700,7 +11710,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11743,7 +11753,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11757,10 +11767,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46181</v>
+        <v>45774</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11773,7 +11783,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11816,7 +11826,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11830,10 +11840,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46181</v>
+        <v>45053</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11846,7 +11856,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11889,7 +11899,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11899,14 +11909,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45120</v>
+        <v>45923</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11918,13 +11928,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11967,7 +11972,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11981,10 +11986,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45021</v>
+        <v>45072</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11996,8 +12001,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12040,7 +12050,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12054,10 +12064,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46181</v>
+        <v>45194</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12070,7 +12080,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12113,7 +12123,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12127,10 +12137,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46077</v>
+        <v>44979</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12143,7 +12153,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12186,7 +12196,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12200,10 +12210,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46077</v>
+        <v>46155</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12216,7 +12226,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12259,7 +12269,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12273,10 +12283,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45110</v>
+        <v>44565</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12289,7 +12299,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.3</v>
+        <v>13.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12332,7 +12342,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12342,14 +12352,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44623</v>
+        <v>45275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12362,7 +12372,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12405,7 +12415,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12419,10 +12429,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45275</v>
+        <v>45905</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12435,7 +12445,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12478,7 +12488,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12492,10 +12502,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45175</v>
+        <v>44725</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12508,7 +12518,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12551,7 +12561,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12565,10 +12575,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44859</v>
+        <v>44791</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12581,7 +12591,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12624,7 +12634,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12638,10 +12648,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45281</v>
+        <v>44942</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12654,7 +12664,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>9.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12697,7 +12707,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12711,10 +12721,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44830</v>
+        <v>45076</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12727,7 +12737,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12770,7 +12780,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12784,10 +12794,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46195</v>
+        <v>45120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12799,8 +12809,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12843,7 +12858,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12857,10 +12872,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44917</v>
+        <v>44977</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12873,7 +12888,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12916,7 +12931,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12930,10 +12945,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44937</v>
+        <v>45096</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12943,6 +12958,11 @@
       <c r="G164" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -12989,7 +13009,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13003,10 +13023,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44938</v>
+        <v>45109</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13019,7 +13039,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13062,7 +13082,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13076,10 +13096,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44977</v>
+        <v>44888</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13092,7 +13112,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13135,7 +13155,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13149,10 +13169,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45278</v>
+        <v>45615</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13165,7 +13185,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13208,7 +13228,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13222,10 +13242,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44990</v>
+        <v>45448</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13238,7 +13258,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13281,7 +13301,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13295,10 +13315,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45428</v>
+        <v>45236</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13311,7 +13331,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13354,7 +13374,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13368,10 +13388,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44859</v>
+        <v>45076</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13384,7 +13404,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13427,7 +13447,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13441,10 +13461,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45636</v>
+        <v>45321</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13457,7 +13477,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13500,7 +13520,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13510,14 +13530,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45174</v>
+        <v>46181</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13530,7 +13550,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13573,7 +13593,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13587,10 +13607,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44977</v>
+        <v>46181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13603,7 +13623,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13646,7 +13666,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13656,14 +13676,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45302</v>
+        <v>46181</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13676,7 +13696,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13719,7 +13739,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13733,10 +13753,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45418</v>
+        <v>46181</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13749,7 +13769,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13792,7 +13812,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13806,10 +13826,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44993</v>
+        <v>46181</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13821,13 +13841,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>18.6</v>
+        <v>2.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13870,7 +13885,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13884,10 +13899,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44573</v>
+        <v>46181</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13900,7 +13915,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13943,7 +13958,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13957,10 +13972,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45184</v>
+        <v>46181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13972,13 +13987,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14021,7 +14031,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14035,10 +14045,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44967</v>
+        <v>45053</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14051,7 +14061,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14094,7 +14104,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14108,10 +14118,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45754</v>
+        <v>45297</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14123,13 +14133,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14172,7 +14177,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14186,10 +14191,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45764</v>
+        <v>44830</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14201,13 +14206,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14250,7 +14250,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14260,14 +14260,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44893</v>
+        <v>45174</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14323,7 +14323,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14337,10 +14337,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44594</v>
+        <v>45552</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14396,7 +14396,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14410,10 +14410,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45630</v>
+        <v>45021</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14469,7 +14469,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14483,10 +14483,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45036</v>
+        <v>44917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14542,7 +14542,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14556,10 +14556,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45053</v>
+        <v>45110</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14615,7 +14615,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14629,10 +14629,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44593</v>
+        <v>46195</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14688,7 +14688,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14702,10 +14702,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45181</v>
+        <v>44671</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14761,7 +14761,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14775,10 +14775,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44651</v>
+        <v>45317</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14790,13 +14790,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14839,7 +14834,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14853,10 +14848,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46253</v>
+        <v>45069</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14869,7 +14864,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14912,7 +14907,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14926,10 +14921,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45076</v>
+        <v>45498</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14942,7 +14937,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14985,7 +14980,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14999,10 +14994,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44594</v>
+        <v>45764</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15014,8 +15009,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15058,7 +15058,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15072,10 +15072,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44565</v>
+        <v>45418</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15131,7 +15131,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46213</v>
+        <v>46253</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15160,13 +15160,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15209,7 +15204,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15223,10 +15218,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45069</v>
+        <v>45440</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15239,7 +15234,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15282,7 +15277,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15296,10 +15291,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45239</v>
+        <v>46213</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15311,8 +15306,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15355,7 +15355,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15365,14 +15365,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46213</v>
+        <v>45181</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15384,13 +15384,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>0.3</v>
+        <v>5.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15433,7 +15428,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15447,10 +15442,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44642</v>
+        <v>45051</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15463,7 +15458,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15506,7 +15501,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15516,14 +15511,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45096</v>
+        <v>46213</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15537,11 +15532,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15584,7 +15579,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15598,10 +15593,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45109</v>
+        <v>45243</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15614,7 +15609,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15657,7 +15652,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15671,10 +15666,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45195</v>
+        <v>46265</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15686,13 +15681,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15735,7 +15725,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15749,10 +15739,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45247</v>
+        <v>45281</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15765,7 +15755,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15808,7 +15798,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15822,10 +15812,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45630</v>
+        <v>46265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15837,8 +15827,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15881,7 +15876,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15895,10 +15890,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44742</v>
+        <v>46265</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15910,8 +15905,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15968,10 +15968,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46265</v>
+        <v>44798</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16119,10 +16119,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45076</v>
+        <v>45594</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16178,7 +16178,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16192,10 +16192,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46265</v>
+        <v>45735</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16209,11 +16209,11 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16256,7 +16256,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16270,10 +16270,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46265</v>
+        <v>45735</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16287,11 +16287,11 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16334,7 +16334,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16348,10 +16348,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45285</v>
+        <v>46253</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16407,7 +16407,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45297</v>
+        <v>44573</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16480,7 +16480,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16494,10 +16494,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46253</v>
+        <v>45076</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16553,7 +16553,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16567,10 +16567,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44902</v>
+        <v>46231</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16626,7 +16626,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16640,10 +16640,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46231</v>
+        <v>46274</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16655,8 +16655,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16699,7 +16704,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16713,10 +16718,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44943</v>
+        <v>46275</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16728,8 +16733,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16772,7 +16782,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16786,10 +16796,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46274</v>
+        <v>44608</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16802,7 +16812,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16845,7 +16855,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16859,10 +16869,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45735</v>
+        <v>46274</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16874,13 +16884,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16923,7 +16928,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16937,10 +16942,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45735</v>
+        <v>44594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16952,13 +16957,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46274</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17093,10 +17093,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46274</v>
+        <v>44910</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46275</v>
+        <v>45630</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17186,13 +17186,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17235,7 +17230,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17249,10 +17244,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45749</v>
+        <v>44967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17265,7 +17260,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17308,7 +17303,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17322,10 +17317,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45740</v>
+        <v>45135</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17339,11 +17334,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17386,7 +17381,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17400,10 +17395,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44744</v>
+        <v>44496</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17416,7 +17411,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17459,7 +17454,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17473,10 +17468,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45226</v>
+        <v>44937</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17489,7 +17484,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17532,7 +17527,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17546,10 +17541,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45576</v>
+        <v>44938</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17562,7 +17557,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17605,7 +17600,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17619,10 +17614,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45755</v>
+        <v>44744</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17635,7 +17630,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17678,7 +17673,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17692,10 +17687,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45598</v>
+        <v>45740</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17707,8 +17702,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17761,14 +17761,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45594</v>
+        <v>45749</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17780,13 +17780,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17829,7 +17824,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17843,10 +17838,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45576</v>
+        <v>45226</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17859,7 +17854,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>17.1</v>
+        <v>1.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17902,7 +17897,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17916,10 +17911,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45817</v>
+        <v>45755</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17932,7 +17927,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17975,7 +17970,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17989,10 +17984,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45803</v>
+        <v>45576</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18005,7 +18000,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18048,7 +18043,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18062,10 +18057,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45733</v>
+        <v>45598</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18121,7 +18116,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18131,14 +18126,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44685</v>
+        <v>45594</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18150,8 +18145,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
         <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58185-2025</t>
+          <t>A 57938-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45983</v>
+        <v>45982</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58185-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 57938-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45982</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44462</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 64406-2021</t>
+          <t>A 7742-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44511</v>
+        <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2865,7 +2865,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42161-2022</t>
+          <t>A 64406-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44830</v>
+        <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7742-2022</t>
+          <t>A 42161-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44608</v>
+        <v>44830</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>44867</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44888</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44629</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44752</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>44655</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44475</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44734</v>
+        <v>44725</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45755</v>
+        <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44642</v>
+        <v>45321</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44830</v>
+        <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45735</v>
+        <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44910</v>
+        <v>44979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44977</v>
+        <v>45306</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45483</v>
+        <v>45432</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44496</v>
+        <v>45529</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45013</v>
+        <v>44903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45343</v>
+        <v>44476</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4549,7 +4549,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45184</v>
+        <v>45109</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4578,13 +4578,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>11.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4627,7 +4622,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4641,10 +4636,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45036</v>
+        <v>44496</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4657,7 +4652,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4700,7 +4695,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4714,10 +4709,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45275</v>
+        <v>44475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4730,7 +4725,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4773,7 +4768,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4787,10 +4782,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45191</v>
+        <v>45448</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4803,7 +4798,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4846,7 +4841,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4860,10 +4855,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44937</v>
+        <v>44511</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4876,7 +4871,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4919,7 +4914,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4933,10 +4928,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44594</v>
+        <v>44617</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4948,8 +4943,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45120</v>
+        <v>44917</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5021,13 +5021,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5070,7 +5065,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5084,10 +5079,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44593</v>
+        <v>44917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5100,7 +5095,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5143,7 +5138,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45576</v>
+        <v>44910</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5173,7 +5168,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>17.1</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5216,7 +5211,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5230,10 +5225,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44999</v>
+        <v>45041</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5245,13 +5240,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5294,7 +5284,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5308,10 +5298,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45076</v>
+        <v>44594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5324,7 +5314,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5367,7 +5357,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45076</v>
+        <v>44671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5397,7 +5387,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5440,7 +5430,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5450,14 +5440,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44623</v>
+        <v>45056</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5470,7 +5460,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5513,7 +5503,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5527,10 +5517,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44476</v>
+        <v>46077</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5543,7 +5533,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5586,7 +5576,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5600,10 +5590,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44938</v>
+        <v>44937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5616,7 +5606,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5659,7 +5649,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,10 +5663,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45817</v>
+        <v>45594</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5689,7 +5679,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5732,7 +5722,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5742,14 +5732,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44903</v>
+        <v>46077</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5762,7 +5752,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5805,7 +5795,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5819,10 +5809,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44678</v>
+        <v>44938</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5835,7 +5825,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5878,7 +5868,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5892,10 +5882,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45041</v>
+        <v>45552</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5951,7 +5941,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5961,14 +5951,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45905</v>
+        <v>46069</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5981,7 +5971,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6024,7 +6014,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6038,10 +6028,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45905</v>
+        <v>45803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6054,7 +6044,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6097,7 +6087,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6111,10 +6101,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44918</v>
+        <v>45733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6127,7 +6117,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6170,7 +6160,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6184,10 +6174,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45576</v>
+        <v>44685</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6200,7 +6190,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6243,7 +6233,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6257,10 +6247,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45096</v>
+        <v>44496</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6272,13 +6262,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6321,7 +6306,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6335,10 +6320,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45210</v>
+        <v>44999</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6350,8 +6335,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6394,7 +6384,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6408,10 +6398,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45432</v>
+        <v>45880</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6424,7 +6414,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6467,7 +6457,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6477,14 +6467,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45754</v>
+        <v>46121</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6496,13 +6486,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6545,7 +6530,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6559,10 +6544,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44511</v>
+        <v>45096</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6574,8 +6559,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6618,7 +6608,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6632,10 +6622,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45803</v>
+        <v>45905</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6648,7 +6638,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6691,7 +6681,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6705,10 +6695,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45236</v>
+        <v>45905</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6721,7 +6711,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6764,7 +6754,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6778,10 +6768,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46037</v>
+        <v>44496</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6794,7 +6784,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6837,7 +6827,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6851,10 +6841,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44685</v>
+        <v>46135</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6867,7 +6857,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6910,7 +6900,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6924,10 +6914,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45733</v>
+        <v>46136</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6940,7 +6930,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6983,7 +6973,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6997,10 +6987,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45428</v>
+        <v>45483</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7056,7 +7046,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7070,10 +7060,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45175</v>
+        <v>45051</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7086,7 +7076,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7129,7 +7119,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7143,10 +7133,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45880</v>
+        <v>45191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7159,7 +7149,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7202,7 +7192,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7216,10 +7206,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44594</v>
+        <v>45297</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7232,7 +7222,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7275,7 +7265,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7289,10 +7279,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45959</v>
+        <v>45774</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7305,7 +7295,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7348,7 +7338,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7362,10 +7352,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44496</v>
+        <v>45440</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7378,7 +7368,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7421,7 +7411,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7435,10 +7425,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44742</v>
+        <v>44945</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7451,7 +7441,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7494,7 +7484,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7508,10 +7498,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44902</v>
+        <v>45582</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7524,7 +7514,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7567,7 +7557,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7581,10 +7571,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45294</v>
+        <v>44888</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7597,7 +7587,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7640,7 +7630,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7654,10 +7644,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45981</v>
+        <v>45986</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7669,13 +7659,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>15.9</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7718,7 +7703,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7732,10 +7717,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45980</v>
+        <v>46136</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7748,7 +7733,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7791,7 +7776,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7805,10 +7790,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45982</v>
+        <v>45237</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7821,7 +7806,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7864,7 +7849,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7878,10 +7863,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45529</v>
+        <v>45236</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7894,7 +7879,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7937,7 +7922,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7951,10 +7936,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46077</v>
+        <v>45053</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7967,7 +7952,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8010,7 +7995,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8024,10 +8009,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46077</v>
+        <v>45735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8040,7 +8025,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8083,7 +8068,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8097,10 +8082,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45278</v>
+        <v>45076</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8113,7 +8098,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8156,7 +8141,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8170,10 +8155,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44474</v>
+        <v>44470</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8186,7 +8171,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8229,7 +8214,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8243,10 +8228,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45636</v>
+        <v>45076</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8259,7 +8244,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8302,7 +8287,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8316,10 +8301,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44945</v>
+        <v>44468</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8375,7 +8360,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8389,10 +8374,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45995</v>
+        <v>45615</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8405,7 +8390,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.4</v>
+        <v>8.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8448,7 +8433,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8462,10 +8447,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44943</v>
+        <v>44918</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8478,7 +8463,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8521,7 +8506,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8531,14 +8516,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46002</v>
+        <v>46147</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8551,7 +8536,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8594,7 +8579,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8604,14 +8589,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46069</v>
+        <v>45923</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8624,7 +8609,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8667,7 +8652,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8681,10 +8666,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45297</v>
+        <v>45275</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8697,7 +8682,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8740,7 +8725,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8754,10 +8739,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46023</v>
+        <v>45120</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8769,8 +8754,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8813,7 +8803,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8827,10 +8817,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44573</v>
+        <v>45021</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8843,7 +8833,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8886,7 +8876,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8900,10 +8890,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44917</v>
+        <v>46155</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8916,7 +8906,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8959,7 +8949,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8973,10 +8963,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44917</v>
+        <v>45905</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8989,7 +8979,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9032,7 +9022,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9042,14 +9032,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45247</v>
+        <v>44623</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9062,7 +9052,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9105,7 +9095,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9119,10 +9109,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45285</v>
+        <v>45275</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9135,7 +9125,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9178,7 +9168,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9192,10 +9182,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45239</v>
+        <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9208,7 +9198,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9251,7 +9241,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9265,10 +9255,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44565</v>
+        <v>44937</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9281,7 +9271,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9324,7 +9314,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9334,14 +9324,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
         <v>44990</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9354,7 +9344,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9397,7 +9387,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9411,10 +9401,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45597</v>
+        <v>45428</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9427,7 +9417,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9470,7 +9460,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9484,10 +9474,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46121</v>
+        <v>45174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9500,7 +9490,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9543,7 +9533,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9557,10 +9547,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44859</v>
+        <v>44977</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9573,7 +9563,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9616,7 +9606,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9626,14 +9616,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44918</v>
+        <v>45302</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9646,7 +9636,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9689,7 +9679,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9703,10 +9693,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45306</v>
+        <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9719,7 +9709,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9762,7 +9752,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9776,10 +9766,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44859</v>
+        <v>45418</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9792,7 +9782,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9835,7 +9825,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9849,10 +9839,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44859</v>
+        <v>46181</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9865,7 +9855,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9908,7 +9898,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9922,10 +9912,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46135</v>
+        <v>46181</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9938,7 +9928,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9981,7 +9971,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9995,10 +9985,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45630</v>
+        <v>46181</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10011,7 +10001,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10054,7 +10044,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10068,10 +10058,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44859</v>
+        <v>46181</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10084,7 +10074,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10127,7 +10117,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10141,10 +10131,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44859</v>
+        <v>46181</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10157,7 +10147,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10200,7 +10190,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10214,10 +10204,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44475</v>
+        <v>44993</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,8 +10219,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>18.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10273,7 +10268,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10287,10 +10282,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45191</v>
+        <v>46181</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10303,7 +10298,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10346,7 +10341,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10360,10 +10355,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45582</v>
+        <v>44573</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10376,7 +10371,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10419,7 +10414,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10433,10 +10428,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46136</v>
+        <v>44967</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10449,7 +10444,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10492,7 +10487,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10506,10 +10501,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44468</v>
+        <v>45754</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10521,8 +10516,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10565,7 +10565,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45056</v>
+        <v>45764</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10594,8 +10594,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10638,7 +10643,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10652,10 +10657,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45109</v>
+        <v>44594</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10668,7 +10673,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10711,7 +10716,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10725,10 +10730,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44617</v>
+        <v>45630</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10740,13 +10745,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10789,7 +10789,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10803,10 +10803,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44893</v>
+        <v>45036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10862,7 +10862,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10876,10 +10876,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45153</v>
+        <v>45959</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10935,7 +10935,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45986</v>
+        <v>46195</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46136</v>
+        <v>44593</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11081,7 +11081,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44990</v>
+        <v>45181</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11168,10 +11168,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44993</v>
+        <v>44651</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11185,11 +11185,11 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>18.6</v>
+        <v>4.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11232,7 +11232,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45755</v>
+        <v>45076</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11305,7 +11305,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11315,14 +11315,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45302</v>
+        <v>44594</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11392,10 +11392,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45237</v>
+        <v>44565</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11451,7 +11451,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11465,10 +11465,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45195</v>
+        <v>45069</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11480,13 +11480,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11529,7 +11524,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11543,10 +11538,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44470</v>
+        <v>45239</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11559,7 +11554,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11602,7 +11597,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11616,10 +11611,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44651</v>
+        <v>45980</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11631,13 +11626,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11680,7 +11670,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11694,10 +11684,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46147</v>
+        <v>44642</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11710,7 +11700,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11753,7 +11743,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11767,10 +11757,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45774</v>
+        <v>45096</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11782,8 +11772,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11826,7 +11821,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11840,10 +11835,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45053</v>
+        <v>45981</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11855,8 +11850,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>15.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11899,7 +11899,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11909,14 +11909,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45923</v>
+        <v>45982</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11986,10 +11986,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45072</v>
+        <v>45109</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12001,13 +12001,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12050,7 +12045,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12064,10 +12059,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45194</v>
+        <v>45195</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12079,8 +12074,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12123,7 +12123,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12137,10 +12137,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44979</v>
+        <v>45247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12196,7 +12196,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12210,10 +12210,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46155</v>
+        <v>44734</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12269,7 +12269,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12283,10 +12283,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44565</v>
+        <v>44791</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>13.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12356,10 +12356,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45275</v>
+        <v>45194</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12415,7 +12415,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12429,10 +12429,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45905</v>
+        <v>45135</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12444,8 +12444,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12488,7 +12493,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12502,10 +12507,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44725</v>
+        <v>45755</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12518,7 +12523,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12561,7 +12566,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12575,10 +12580,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44791</v>
+        <v>45236</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12591,7 +12596,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>8.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12634,7 +12639,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12648,10 +12653,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44942</v>
+        <v>46253</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12664,7 +12669,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>9.1</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12707,7 +12712,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12721,10 +12726,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45076</v>
+        <v>44474</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12737,7 +12742,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12780,7 +12785,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12794,10 +12799,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45120</v>
+        <v>45755</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12809,13 +12814,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12872,10 +12872,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44977</v>
+        <v>46213</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12887,8 +12887,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12931,7 +12936,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12945,10 +12950,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45096</v>
+        <v>45317</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12960,13 +12965,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13009,7 +13009,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13019,14 +13019,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45109</v>
+        <v>46213</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13038,8 +13038,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>11.8</v>
+        <v>0.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13082,7 +13087,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13096,10 +13101,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44888</v>
+        <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13112,7 +13117,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13155,7 +13160,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13169,10 +13174,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45615</v>
+        <v>45294</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13185,7 +13190,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8.9</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13228,7 +13233,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13242,10 +13247,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45448</v>
+        <v>45210</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13258,7 +13263,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13301,7 +13306,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13315,10 +13320,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45236</v>
+        <v>45995</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13331,7 +13336,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13374,7 +13379,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13388,10 +13393,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45076</v>
+        <v>45120</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13403,8 +13408,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13447,7 +13457,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13461,10 +13471,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45321</v>
+        <v>44678</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13477,7 +13487,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13520,7 +13530,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13530,14 +13540,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46181</v>
+        <v>46002</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13550,7 +13560,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13593,7 +13603,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13607,10 +13617,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46181</v>
+        <v>46265</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13623,7 +13633,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13666,7 +13676,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13680,10 +13690,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46181</v>
+        <v>46265</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13695,8 +13705,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13739,7 +13754,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13753,10 +13768,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46181</v>
+        <v>46265</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13768,8 +13783,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13812,7 +13832,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13826,10 +13846,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46181</v>
+        <v>46265</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13841,8 +13861,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13885,7 +13910,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13899,10 +13924,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46181</v>
+        <v>44608</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13915,7 +13940,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13958,7 +13983,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13972,10 +13997,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46181</v>
+        <v>45243</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13988,7 +14013,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14031,7 +14056,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14045,10 +14070,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45053</v>
+        <v>46253</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14061,7 +14086,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14104,7 +14129,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14118,10 +14143,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45297</v>
+        <v>45191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14134,7 +14159,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14177,7 +14202,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14191,10 +14216,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44830</v>
+        <v>46231</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14207,7 +14232,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14250,7 +14275,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14264,10 +14289,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45174</v>
+        <v>44990</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14280,7 +14305,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14323,7 +14348,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14337,10 +14362,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45552</v>
+        <v>46274</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14353,7 +14378,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14396,7 +14421,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14410,10 +14435,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45021</v>
+        <v>46274</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14425,8 +14450,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14469,7 +14499,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14483,10 +14513,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44917</v>
+        <v>44910</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14498,8 +14528,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14542,7 +14577,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14556,10 +14591,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45110</v>
+        <v>46274</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14571,8 +14606,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14615,7 +14655,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14629,10 +14669,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46195</v>
+        <v>46275</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14644,8 +14684,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14688,7 +14733,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14702,10 +14747,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44671</v>
+        <v>45498</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14718,7 +14763,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14761,7 +14806,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14775,10 +14820,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45317</v>
+        <v>46023</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14791,7 +14836,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14834,7 +14879,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14848,10 +14893,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45069</v>
+        <v>45576</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14864,7 +14909,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14907,7 +14952,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14921,10 +14966,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45498</v>
+        <v>44798</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14937,7 +14982,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14980,7 +15025,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14990,14 +15035,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45764</v>
+        <v>45343</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15009,13 +15054,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15058,7 +15098,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15072,10 +15112,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45418</v>
+        <v>45072</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15087,8 +15127,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15131,7 +15176,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15145,10 +15190,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46253</v>
+        <v>44942</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15161,7 +15206,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>9.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15204,7 +15249,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15218,10 +15263,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45440</v>
+        <v>45153</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15234,7 +15279,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15277,7 +15322,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15291,10 +15336,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46213</v>
+        <v>44565</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15306,13 +15351,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>13.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15355,7 +15395,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15369,10 +15409,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45181</v>
+        <v>44573</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15385,7 +15425,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15428,7 +15468,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15442,10 +15482,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45051</v>
+        <v>44859</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15458,7 +15498,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15501,7 +15541,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15511,14 +15551,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46213</v>
+        <v>45013</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15530,13 +15570,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15579,7 +15614,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15593,10 +15628,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45243</v>
+        <v>46037</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15609,7 +15644,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15652,7 +15687,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15666,10 +15701,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46265</v>
+        <v>45597</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15682,7 +15717,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15725,7 +15760,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15739,10 +15774,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45281</v>
+        <v>45076</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15798,7 +15833,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15812,10 +15847,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46265</v>
+        <v>45110</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15827,13 +15862,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15876,7 +15906,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15890,10 +15920,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46265</v>
+        <v>45175</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15905,13 +15935,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15954,7 +15979,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15968,10 +15993,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44798</v>
+        <v>45281</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15984,7 +16009,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16027,7 +16052,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16041,10 +16066,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46265</v>
+        <v>44830</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16056,13 +16081,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16105,7 +16125,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16119,10 +16139,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45594</v>
+        <v>44917</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16135,7 +16155,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16178,7 +16198,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16192,10 +16212,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45735</v>
+        <v>44938</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16207,13 +16227,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16256,7 +16271,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16270,10 +16285,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45735</v>
+        <v>44977</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16285,13 +16300,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16334,7 +16344,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16348,10 +16358,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46253</v>
+        <v>45278</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16364,7 +16374,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16407,7 +16417,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16421,10 +16431,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44573</v>
+        <v>44859</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16437,7 +16447,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16480,7 +16490,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16494,10 +16504,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45076</v>
+        <v>45636</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16510,7 +16520,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16553,7 +16563,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16567,10 +16577,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46231</v>
+        <v>45184</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16582,8 +16592,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>10.1</v>
+        <v>2.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16626,7 +16641,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16640,10 +16655,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46274</v>
+        <v>44893</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16655,13 +16670,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16704,7 +16714,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16718,10 +16728,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46275</v>
+        <v>45053</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16733,13 +16743,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16782,7 +16787,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16796,10 +16801,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44608</v>
+        <v>45630</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16812,7 +16817,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16855,7 +16860,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16869,10 +16874,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46274</v>
+        <v>44742</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16885,7 +16890,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16928,7 +16933,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16942,10 +16947,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44594</v>
+        <v>45076</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16958,7 +16963,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17001,7 +17006,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17015,10 +17020,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46274</v>
+        <v>45285</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17030,13 +17035,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17079,7 +17079,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17093,10 +17093,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44910</v>
+        <v>45297</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17108,13 +17108,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17157,7 +17152,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17171,10 +17166,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45630</v>
+        <v>44902</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17187,7 +17182,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17230,7 +17225,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17244,10 +17239,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44967</v>
+        <v>44943</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17260,7 +17255,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17303,7 +17298,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17317,10 +17312,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45135</v>
+        <v>45735</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17334,11 +17329,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17381,7 +17376,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17395,10 +17390,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44496</v>
+        <v>45735</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17410,8 +17405,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17454,7 +17454,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17468,10 +17468,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44937</v>
+        <v>45749</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17527,7 +17527,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17541,10 +17541,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44938</v>
+        <v>45740</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17556,8 +17556,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17617,7 +17622,7 @@
         <v>44744</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17673,7 +17678,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17687,10 +17692,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45740</v>
+        <v>45226</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17702,13 +17707,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17765,10 +17765,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45749</v>
+        <v>45576</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17824,7 +17824,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45226</v>
+        <v>45755</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17897,7 +17897,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17911,10 +17911,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45755</v>
+        <v>45598</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17970,7 +17970,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17980,14 +17980,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45576</v>
+        <v>45594</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17999,8 +17999,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18043,7 +18048,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18057,10 +18062,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45598</v>
+        <v>45576</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18073,7 +18078,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>17.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18116,7 +18121,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18126,14 +18131,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45594</v>
+        <v>45817</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18145,13 +18150,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
         <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57938-2025</t>
+          <t>A 58185-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 57938-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58185-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44462</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44830</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44867</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44888</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44629</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29366-2022</t>
+          <t>A 26244-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44752</v>
+        <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26244-2022</t>
+          <t>A 29366-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44735</v>
+        <v>44752</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>44655</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44475</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44725</v>
+        <v>44734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44918</v>
+        <v>45755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45321</v>
+        <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44859</v>
+        <v>44830</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44859</v>
+        <v>45735</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44979</v>
+        <v>44910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45306</v>
+        <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45432</v>
+        <v>45483</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45529</v>
+        <v>45275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44903</v>
+        <v>44496</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44476</v>
+        <v>45013</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4549,7 +4549,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4559,14 +4559,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45109</v>
+        <v>45343</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>11.8</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44496</v>
+        <v>44937</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4695,7 +4695,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44475</v>
+        <v>45184</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4724,8 +4724,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4768,7 +4773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4782,10 +4787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45448</v>
+        <v>45036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4798,7 +4803,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4841,7 +4846,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4855,10 +4860,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44511</v>
+        <v>45191</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4871,7 +4876,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4914,7 +4919,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4928,10 +4933,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44617</v>
+        <v>44593</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4943,13 +4948,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44917</v>
+        <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44917</v>
+        <v>45120</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5094,8 +5094,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44910</v>
+        <v>44999</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5167,8 +5172,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5211,7 +5221,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5225,10 +5235,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45041</v>
+        <v>45076</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5241,7 +5251,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5284,7 +5294,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5298,10 +5308,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44594</v>
+        <v>45076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5314,7 +5324,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5357,7 +5367,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5367,14 +5377,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44671</v>
+        <v>44623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5387,7 +5397,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5430,7 +5440,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5444,10 +5454,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45056</v>
+        <v>44476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5460,7 +5470,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5503,7 +5513,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5513,14 +5523,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46077</v>
+        <v>44903</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5533,7 +5543,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5576,7 +5586,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5590,10 +5600,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44937</v>
+        <v>44678</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5606,7 +5616,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5649,7 +5659,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5663,10 +5673,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45594</v>
+        <v>44938</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5679,7 +5689,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5722,7 +5732,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5736,10 +5746,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46077</v>
+        <v>45041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5752,7 +5762,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5795,7 +5805,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5809,10 +5819,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44938</v>
+        <v>45576</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5825,7 +5835,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5868,7 +5878,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5882,10 +5892,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45552</v>
+        <v>45096</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5897,8 +5907,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5941,7 +5956,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5951,14 +5966,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46069</v>
+        <v>44918</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5971,7 +5986,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6014,7 +6029,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6028,10 +6043,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45803</v>
+        <v>45210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6044,7 +6059,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6087,7 +6102,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6101,10 +6116,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45733</v>
+        <v>45432</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6117,7 +6132,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6160,7 +6175,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6174,10 +6189,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44685</v>
+        <v>45754</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6189,8 +6204,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6233,7 +6253,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6247,10 +6267,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44496</v>
+        <v>44511</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6263,7 +6283,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6306,7 +6326,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6320,10 +6340,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44999</v>
+        <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6335,13 +6355,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6384,7 +6399,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6398,10 +6413,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45880</v>
+        <v>45428</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6414,7 +6429,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6457,7 +6472,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6467,14 +6482,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46121</v>
+        <v>45175</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6487,7 +6502,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6530,7 +6545,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6544,10 +6559,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45096</v>
+        <v>44742</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6557,11 +6572,6 @@
       <c r="G77" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -6608,7 +6618,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6622,10 +6632,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45905</v>
+        <v>45582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6638,7 +6648,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6681,7 +6691,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6695,10 +6705,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>44902</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6711,7 +6721,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6754,7 +6764,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6768,10 +6778,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44496</v>
+        <v>46136</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6784,7 +6794,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6827,7 +6837,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6841,10 +6851,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46135</v>
+        <v>45294</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6857,7 +6867,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6900,7 +6910,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6914,10 +6924,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46136</v>
+        <v>45529</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6930,7 +6940,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>6.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6973,7 +6983,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45483</v>
+        <v>45278</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7003,7 +7013,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7046,7 +7056,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7060,10 +7070,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45051</v>
+        <v>44594</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7076,7 +7086,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7119,7 +7129,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7133,10 +7143,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45191</v>
+        <v>45986</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7149,7 +7159,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7192,7 +7202,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7206,10 +7216,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45297</v>
+        <v>46136</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7222,7 +7232,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7265,7 +7275,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7279,10 +7289,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45774</v>
+        <v>44496</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7295,7 +7305,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7338,7 +7348,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7352,10 +7362,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45440</v>
+        <v>45636</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7368,7 +7378,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7428,7 +7438,7 @@
         <v>44945</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7484,7 +7494,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7498,10 +7508,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45582</v>
+        <v>44943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7514,7 +7524,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7557,7 +7567,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7571,10 +7581,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44888</v>
+        <v>45905</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7587,7 +7597,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7630,7 +7640,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7644,10 +7654,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45986</v>
+        <v>45905</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7660,7 +7670,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7703,7 +7713,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7717,10 +7727,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46136</v>
+        <v>45297</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7733,7 +7743,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7776,7 +7786,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7790,10 +7800,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45237</v>
+        <v>44573</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7806,7 +7816,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7849,7 +7859,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7863,10 +7873,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45236</v>
+        <v>44917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7879,7 +7889,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7922,7 +7932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7936,10 +7946,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45053</v>
+        <v>44917</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7995,7 +8005,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8009,10 +8019,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45735</v>
+        <v>45247</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8025,7 +8035,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8068,7 +8078,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8082,10 +8092,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45076</v>
+        <v>45285</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8098,7 +8108,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8141,7 +8151,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8155,10 +8165,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44470</v>
+        <v>45239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8171,7 +8181,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8214,7 +8224,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8228,10 +8238,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45076</v>
+        <v>44565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8244,7 +8254,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8287,7 +8297,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8301,10 +8311,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44468</v>
+        <v>46147</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8317,7 +8327,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8360,7 +8370,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8370,14 +8380,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45615</v>
+        <v>44990</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8390,7 +8400,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8.9</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8433,7 +8443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8447,10 +8457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44918</v>
+        <v>45597</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8463,7 +8473,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8506,7 +8516,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8520,10 +8530,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46147</v>
+        <v>44859</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8536,7 +8546,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8596,7 +8606,7 @@
         <v>45923</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8652,7 +8662,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8666,10 +8676,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45275</v>
+        <v>44918</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8682,7 +8692,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8725,7 +8735,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8739,10 +8749,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45120</v>
+        <v>45306</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8754,13 +8764,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8803,7 +8808,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8817,10 +8822,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45021</v>
+        <v>44859</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8833,7 +8838,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8876,7 +8881,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8890,10 +8895,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46155</v>
+        <v>44859</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8906,7 +8911,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8949,7 +8954,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8963,10 +8968,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45905</v>
+        <v>45630</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8979,7 +8984,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9022,7 +9027,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9032,14 +9037,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44623</v>
+        <v>44859</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9052,7 +9057,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9095,7 +9100,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9109,10 +9114,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45275</v>
+        <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9125,7 +9130,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9168,7 +9173,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9182,10 +9187,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44859</v>
+        <v>45959</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9198,7 +9203,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9241,7 +9246,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9255,10 +9260,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44937</v>
+        <v>44475</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9271,7 +9276,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9314,7 +9319,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9328,10 +9333,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44990</v>
+        <v>45191</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9344,7 +9349,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9387,7 +9392,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9401,10 +9406,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45428</v>
+        <v>44468</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9417,7 +9422,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9460,7 +9465,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9470,14 +9475,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45174</v>
+        <v>45056</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9490,7 +9495,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9533,7 +9538,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9547,10 +9552,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44977</v>
+        <v>45109</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9563,7 +9568,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9606,7 +9611,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9616,14 +9621,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45302</v>
+        <v>44617</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9635,8 +9640,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9679,7 +9689,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9693,10 +9703,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46181</v>
+        <v>45981</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9708,8 +9718,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>15.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9752,7 +9767,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9766,10 +9781,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45418</v>
+        <v>46155</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9782,7 +9797,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9825,7 +9840,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9839,10 +9854,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46181</v>
+        <v>44893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9855,7 +9870,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9898,7 +9913,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9912,10 +9927,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46181</v>
+        <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9928,7 +9943,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9971,7 +9986,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9985,10 +10000,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46181</v>
+        <v>45153</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10001,7 +10016,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10044,7 +10059,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10058,10 +10073,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46181</v>
+        <v>45982</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10074,7 +10089,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10117,7 +10132,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10131,10 +10146,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46181</v>
+        <v>44990</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10147,7 +10162,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10207,7 +10222,7 @@
         <v>44993</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10268,7 +10283,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10282,10 +10297,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46181</v>
+        <v>45755</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10298,7 +10313,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10341,7 +10356,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10355,10 +10370,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44573</v>
+        <v>45905</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10371,7 +10386,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10414,7 +10429,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10428,10 +10443,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44967</v>
+        <v>44474</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10444,7 +10459,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10487,7 +10502,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10497,14 +10512,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45754</v>
+        <v>45302</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10516,13 +10531,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>9</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10565,7 +10575,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10579,10 +10589,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45764</v>
+        <v>45237</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10594,13 +10604,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10643,7 +10648,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10657,10 +10662,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44594</v>
+        <v>45195</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10672,8 +10677,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10716,7 +10726,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10730,10 +10740,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45630</v>
+        <v>45995</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10746,7 +10756,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10789,7 +10799,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10803,10 +10813,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45036</v>
+        <v>44470</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10819,7 +10829,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10862,7 +10872,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10876,10 +10886,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45959</v>
+        <v>44651</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10891,8 +10901,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10935,7 +10950,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10945,14 +10960,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46195</v>
+        <v>46002</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10965,7 +10980,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11008,7 +11023,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11022,10 +11037,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44593</v>
+        <v>45774</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11038,7 +11053,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11081,7 +11096,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11095,10 +11110,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45181</v>
+        <v>45053</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11111,7 +11126,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11154,7 +11169,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11168,10 +11183,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44651</v>
+        <v>45072</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11189,7 +11204,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11232,7 +11247,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11246,10 +11261,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45076</v>
+        <v>45194</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11262,7 +11277,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11305,7 +11320,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11319,10 +11334,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44594</v>
+        <v>44979</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11335,7 +11350,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11378,7 +11393,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11392,10 +11407,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44565</v>
+        <v>46023</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11408,7 +11423,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11451,7 +11466,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11465,10 +11480,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45069</v>
+        <v>44565</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11481,7 +11496,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>13.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11524,7 +11539,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11538,10 +11553,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45239</v>
+        <v>45275</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11554,7 +11569,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11597,7 +11612,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11611,10 +11626,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45980</v>
+        <v>46037</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11627,7 +11642,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11670,7 +11685,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11684,10 +11699,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44642</v>
+        <v>44725</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11700,7 +11715,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11743,7 +11758,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11757,10 +11772,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45096</v>
+        <v>44791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11772,13 +11787,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11821,7 +11831,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11835,10 +11845,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45981</v>
+        <v>44942</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11850,13 +11860,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>15.9</v>
+        <v>9.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11899,7 +11904,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11913,10 +11918,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45982</v>
+        <v>45076</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11929,7 +11934,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11972,7 +11977,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11986,10 +11991,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45109</v>
+        <v>45120</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12001,8 +12006,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12045,7 +12055,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12059,10 +12069,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45195</v>
+        <v>44977</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12074,13 +12084,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12123,7 +12128,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12137,10 +12142,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45247</v>
+        <v>45096</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12152,8 +12157,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12196,7 +12206,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12210,10 +12220,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44734</v>
+        <v>45109</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12226,7 +12236,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.7</v>
+        <v>11.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12269,7 +12279,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12283,10 +12293,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44791</v>
+        <v>44888</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12299,7 +12309,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12342,7 +12352,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12356,10 +12366,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45194</v>
+        <v>45615</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12372,7 +12382,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12415,7 +12425,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12429,10 +12439,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45135</v>
+        <v>45448</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12444,13 +12454,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12493,7 +12498,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12507,10 +12512,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45755</v>
+        <v>45236</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12523,7 +12528,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12566,7 +12571,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12580,10 +12585,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45236</v>
+        <v>46181</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12596,7 +12601,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12639,7 +12644,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12653,10 +12658,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46253</v>
+        <v>45076</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12669,7 +12674,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12712,7 +12717,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12726,10 +12731,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44474</v>
+        <v>46181</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12742,7 +12747,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12785,7 +12790,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12799,10 +12804,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45755</v>
+        <v>46181</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12815,7 +12820,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12858,7 +12863,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12872,10 +12877,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46213</v>
+        <v>46181</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12887,13 +12892,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12936,7 +12936,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45317</v>
+        <v>45321</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13009,7 +13009,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13019,14 +13019,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46213</v>
+        <v>46181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13038,13 +13038,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13087,7 +13082,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13101,10 +13096,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44830</v>
+        <v>46181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13117,7 +13112,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13160,7 +13155,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13174,10 +13169,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45294</v>
+        <v>46181</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13190,7 +13185,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13233,7 +13228,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13247,10 +13242,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45210</v>
+        <v>46077</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13263,7 +13258,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13306,7 +13301,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13320,10 +13315,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45995</v>
+        <v>46077</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13336,7 +13331,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13379,7 +13374,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13393,10 +13388,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45120</v>
+        <v>45053</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13408,13 +13403,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13457,7 +13447,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13471,10 +13461,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44678</v>
+        <v>45297</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13487,7 +13477,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13530,7 +13520,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13540,14 +13530,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46002</v>
+        <v>44830</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13560,7 +13550,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13603,7 +13593,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13613,14 +13603,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46265</v>
+        <v>45174</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13633,7 +13623,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13676,7 +13666,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13690,10 +13680,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46265</v>
+        <v>45552</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13705,13 +13695,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13754,7 +13739,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13764,14 +13749,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46265</v>
+        <v>46069</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13783,13 +13768,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13832,7 +13812,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13846,10 +13826,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46265</v>
+        <v>45021</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13861,13 +13841,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>6</v>
+        <v>0.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13910,7 +13885,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13924,10 +13899,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44608</v>
+        <v>44917</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13940,7 +13915,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13983,7 +13958,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13997,10 +13972,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45243</v>
+        <v>46195</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14013,7 +13988,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14056,7 +14031,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14070,10 +14045,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46253</v>
+        <v>45110</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14086,7 +14061,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14129,7 +14104,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14143,10 +14118,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45191</v>
+        <v>44671</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14159,7 +14134,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14202,7 +14177,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14216,10 +14191,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46231</v>
+        <v>45317</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14232,7 +14207,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>10.1</v>
+        <v>2.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14275,7 +14250,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14285,14 +14260,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44990</v>
+        <v>45069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14305,7 +14280,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14348,7 +14323,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14358,14 +14333,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46274</v>
+        <v>46121</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14378,7 +14353,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14421,7 +14396,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14435,10 +14410,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46274</v>
+        <v>45498</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14450,13 +14425,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14499,7 +14469,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14513,10 +14483,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44910</v>
+        <v>45764</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14530,11 +14500,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14577,7 +14547,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14591,10 +14561,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46274</v>
+        <v>45418</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14606,13 +14576,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14655,7 +14620,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14669,10 +14634,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46275</v>
+        <v>46135</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14684,13 +14649,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14733,7 +14693,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14747,10 +14707,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45498</v>
+        <v>45440</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14763,7 +14723,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14806,7 +14766,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14820,10 +14780,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46023</v>
+        <v>45181</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14836,7 +14796,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14879,7 +14839,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14893,10 +14853,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45576</v>
+        <v>45051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14909,7 +14869,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14952,7 +14912,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14966,10 +14926,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44798</v>
+        <v>45243</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14982,7 +14942,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15025,7 +14985,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15035,14 +14995,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45343</v>
+        <v>45281</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15055,7 +15015,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15098,7 +15058,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15112,10 +15072,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45072</v>
+        <v>46253</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15127,13 +15087,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15176,7 +15131,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15190,10 +15145,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44942</v>
+        <v>44798</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15206,7 +15161,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>9.1</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15249,7 +15204,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15263,10 +15218,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45153</v>
+        <v>46213</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15278,8 +15233,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15322,7 +15282,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15336,10 +15296,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44565</v>
+        <v>45594</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15352,7 +15312,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>13.4</v>
+        <v>2.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15395,7 +15355,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15405,14 +15365,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44573</v>
+        <v>46213</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15424,8 +15384,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15468,7 +15433,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15482,10 +15447,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44859</v>
+        <v>45735</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15497,8 +15462,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15541,7 +15511,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15555,10 +15525,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45013</v>
+        <v>45735</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15570,8 +15540,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15614,7 +15589,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15628,10 +15603,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46037</v>
+        <v>44573</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15644,7 +15619,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15687,7 +15662,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15701,10 +15676,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45597</v>
+        <v>45076</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15717,7 +15692,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15760,7 +15735,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15774,10 +15749,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45076</v>
+        <v>46265</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15790,7 +15765,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15833,7 +15808,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15847,10 +15822,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45110</v>
+        <v>44608</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15863,7 +15838,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15906,7 +15881,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15920,10 +15895,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45175</v>
+        <v>46265</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15935,8 +15910,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15979,7 +15959,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15993,10 +15973,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45281</v>
+        <v>46265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16008,8 +15988,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16052,7 +16037,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16066,10 +16051,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44830</v>
+        <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16081,8 +16066,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16125,7 +16115,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16139,10 +16129,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44917</v>
+        <v>44594</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16155,7 +16145,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16198,7 +16188,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16212,10 +16202,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44938</v>
+        <v>44910</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16227,8 +16217,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16271,7 +16266,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16285,10 +16280,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44977</v>
+        <v>45630</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16301,7 +16296,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16344,7 +16339,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16358,10 +16353,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45278</v>
+        <v>44967</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16417,7 +16412,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16431,10 +16426,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44859</v>
+        <v>45135</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16446,8 +16441,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16490,7 +16490,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16504,10 +16504,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45636</v>
+        <v>44496</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16563,7 +16563,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16577,10 +16577,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45184</v>
+        <v>44937</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16592,13 +16592,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16641,7 +16636,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16655,10 +16650,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44893</v>
+        <v>44938</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16671,7 +16666,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16714,7 +16709,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16728,10 +16723,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45053</v>
+        <v>46253</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16744,7 +16739,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16787,7 +16782,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16801,10 +16796,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45630</v>
+        <v>46231</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16817,7 +16812,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16860,7 +16855,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16874,10 +16869,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44742</v>
+        <v>46274</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16889,8 +16884,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16933,7 +16933,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16947,10 +16947,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45076</v>
+        <v>46275</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16962,8 +16962,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17006,7 +17011,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17020,10 +17025,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45285</v>
+        <v>46274</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17036,7 +17041,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17079,7 +17084,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17093,10 +17098,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45297</v>
+        <v>46274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17108,8 +17113,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17152,7 +17162,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17166,10 +17176,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44902</v>
+        <v>44744</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17182,7 +17192,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17225,7 +17235,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17239,10 +17249,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44943</v>
+        <v>45740</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17254,8 +17264,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17298,7 +17313,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17312,10 +17327,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45735</v>
+        <v>45749</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17327,13 +17342,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.9</v>
+        <v>6.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17376,7 +17386,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17390,10 +17400,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45735</v>
+        <v>45226</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17405,13 +17415,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17454,7 +17459,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17468,10 +17473,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45749</v>
+        <v>45755</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17484,7 +17489,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17527,7 +17532,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17541,10 +17546,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45740</v>
+        <v>45576</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17556,13 +17561,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17605,7 +17605,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17619,10 +17619,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44744</v>
+        <v>45598</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17678,7 +17678,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17688,14 +17688,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45226</v>
+        <v>45594</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17707,8 +17707,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17751,7 +17756,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17768,7 +17773,7 @@
         <v>45576</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17781,7 +17786,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.8</v>
+        <v>17.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17824,7 +17829,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17838,10 +17843,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45755</v>
+        <v>45817</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17854,7 +17859,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17897,7 +17902,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17911,10 +17916,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45598</v>
+        <v>45803</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17927,7 +17932,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17970,7 +17975,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17980,14 +17985,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45594</v>
+        <v>44685</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17999,13 +18004,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45576</v>
+        <v>45733</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>17.1</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45817</v>
+        <v>45880</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
         <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45983</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45982</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44462</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44830</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44867</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44888</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44629</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44752</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>44655</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44475</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44830</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45735</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45483</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>45275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44496</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45013</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>45343</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44937</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45184</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45191</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44593</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45120</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44999</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>45076</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44903</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44678</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44938</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45576</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45096</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>44918</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>45432</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>45754</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>44511</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45428</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>45175</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>44742</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>44902</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>46136</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45294</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>45529</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45278</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44594</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>45986</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>46136</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>44496</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45636</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>44945</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>44943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45905</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45905</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45297</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>44573</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44917</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45247</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45285</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>46147</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44990</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45597</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44859</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45923</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44918</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45306</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>44859</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44859</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45630</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44859</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45959</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44475</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45191</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44468</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45056</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45109</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44617</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45981</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>46155</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45153</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45982</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>44990</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44993</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45755</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45905</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>44474</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45302</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45237</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45195</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>45995</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>44470</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>44651</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>46002</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45774</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45053</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45072</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45194</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44979</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>46023</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44565</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45275</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>46037</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44725</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>44791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44942</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45076</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45120</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44977</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45096</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45109</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44888</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45615</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45448</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45236</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>46181</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45076</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>46181</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>46181</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>46181</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>45321</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>46181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>46181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>46181</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>46077</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>46077</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45053</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>45297</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44830</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45174</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45552</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>46069</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45021</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44917</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>46195</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45110</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44671</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45317</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>46121</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45498</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45764</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45418</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>46135</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45440</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45181</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45243</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45281</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>46253</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>44798</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>46213</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45594</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>46213</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45735</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45735</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44573</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45076</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>46265</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>44608</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>46265</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>46265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44594</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44910</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45630</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44967</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45135</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44496</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>44937</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>44938</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>46253</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>46231</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>46274</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>46275</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>46274</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>46274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>44744</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45740</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45749</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45226</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45755</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45576</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45598</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45594</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45576</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45817</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45803</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44685</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45733</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45880</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45983</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45982</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44462</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44830</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44867</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44888</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44629</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26244-2022</t>
+          <t>A 29366-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44735</v>
+        <v>44752</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29366-2022</t>
+          <t>A 26244-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44752</v>
+        <v>44735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>44480</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>44655</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44475</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44734</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44830</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45735</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45483</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45275</v>
+        <v>45184</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4359,8 +4359,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4403,7 +4408,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44496</v>
+        <v>45036</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4433,7 +4438,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4476,7 +4481,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4490,10 +4495,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45013</v>
+        <v>45275</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4506,7 +4511,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4549,7 +4554,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4559,14 +4564,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45343</v>
+        <v>44496</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4579,7 +4584,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4622,7 +4627,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4636,10 +4641,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44937</v>
+        <v>45013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4652,7 +4657,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4695,7 +4700,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4705,14 +4710,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45184</v>
+        <v>45343</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4724,13 +4729,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45036</v>
+        <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>45191</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44593</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45120</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44999</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5231,14 +5231,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45076</v>
+        <v>44623</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45076</v>
+        <v>44476</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5367,7 +5367,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5377,14 +5377,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44623</v>
+        <v>44938</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5440,7 +5440,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5450,14 +5450,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44476</v>
+        <v>44903</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5513,7 +5513,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5523,14 +5523,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44903</v>
+        <v>44678</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5586,7 +5586,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44678</v>
+        <v>45041</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5659,7 +5659,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44938</v>
+        <v>45576</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45041</v>
+        <v>45096</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5761,8 +5761,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5805,7 +5810,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5819,10 +5824,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45576</v>
+        <v>44918</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5835,7 +5840,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5878,7 +5883,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5892,10 +5897,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45096</v>
+        <v>45432</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5907,13 +5912,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5956,7 +5956,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44918</v>
+        <v>45076</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45210</v>
+        <v>45076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6102,7 +6102,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45432</v>
+        <v>45210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6192,7 +6192,7 @@
         <v>45754</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>44511</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45428</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>45175</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44742</v>
+        <v>45880</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45582</v>
+        <v>44742</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44902</v>
+        <v>45582</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6781,7 +6781,7 @@
         <v>46136</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45294</v>
+        <v>44594</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45529</v>
+        <v>44496</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45278</v>
+        <v>44902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44594</v>
+        <v>45986</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7129,7 +7129,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45986</v>
+        <v>46136</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46136</v>
+        <v>45905</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44496</v>
+        <v>45905</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7348,7 +7348,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7362,10 +7362,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45636</v>
+        <v>45294</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44945</v>
+        <v>45529</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7494,7 +7494,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7508,10 +7508,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44943</v>
+        <v>45278</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7567,7 +7567,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45905</v>
+        <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7640,7 +7640,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7654,10 +7654,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45905</v>
+        <v>44945</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7713,7 +7713,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7727,10 +7727,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45297</v>
+        <v>44943</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7786,7 +7786,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44573</v>
+        <v>46147</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7859,7 +7859,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44917</v>
+        <v>45923</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7932,7 +7932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44917</v>
+        <v>45297</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8005,7 +8005,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45247</v>
+        <v>46155</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8078,7 +8078,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45285</v>
+        <v>44573</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8151,7 +8151,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45239</v>
+        <v>44917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8224,7 +8224,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44565</v>
+        <v>44917</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8297,7 +8297,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46147</v>
+        <v>45905</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44990</v>
+        <v>45959</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8443,7 +8443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8457,10 +8457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45597</v>
+        <v>45247</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8516,7 +8516,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44859</v>
+        <v>45285</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8589,7 +8589,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8599,14 +8599,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45923</v>
+        <v>45239</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8662,7 +8662,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44918</v>
+        <v>44565</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8735,7 +8735,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45306</v>
+        <v>44990</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44859</v>
+        <v>45981</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,8 +8837,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>15.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8886,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8895,10 +8900,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44859</v>
+        <v>45980</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8911,7 +8916,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8954,7 +8959,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8968,10 +8973,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45630</v>
+        <v>45597</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8984,7 +8989,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9027,7 +9032,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9041,10 +9046,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44859</v>
+        <v>45982</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9057,7 +9062,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9100,7 +9105,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9117,7 +9122,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9130,7 +9135,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9173,7 +9178,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9187,10 +9192,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45959</v>
+        <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9203,7 +9208,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9246,7 +9251,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9260,10 +9265,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44475</v>
+        <v>45306</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9276,7 +9281,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9319,7 +9324,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9333,10 +9338,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45191</v>
+        <v>44474</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9349,7 +9354,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9392,7 +9397,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9406,10 +9411,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44468</v>
+        <v>44859</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9422,7 +9427,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9465,7 +9470,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9479,10 +9484,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45056</v>
+        <v>44859</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9495,7 +9500,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9538,7 +9543,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9552,10 +9557,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45109</v>
+        <v>45995</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9568,7 +9573,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9611,7 +9616,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9625,10 +9630,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44617</v>
+        <v>45630</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9640,13 +9645,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45981</v>
+        <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,13 +9718,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>15.9</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9767,7 +9762,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9781,10 +9776,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46155</v>
+        <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9797,7 +9792,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9840,7 +9835,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9850,14 +9845,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44893</v>
+        <v>46002</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9913,7 +9908,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9927,10 +9922,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45980</v>
+        <v>44475</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9943,7 +9938,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9986,7 +9981,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10000,10 +9995,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45153</v>
+        <v>45191</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10016,7 +10011,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10059,7 +10054,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10073,10 +10068,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45982</v>
+        <v>44468</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10089,7 +10084,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10132,7 +10127,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10146,10 +10141,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44990</v>
+        <v>45056</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10162,7 +10157,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10205,7 +10200,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10219,10 +10214,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44993</v>
+        <v>45109</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,13 +10229,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>18.6</v>
+        <v>2.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10283,7 +10273,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10297,10 +10287,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45755</v>
+        <v>44617</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10312,8 +10302,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10356,7 +10351,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10370,10 +10365,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45905</v>
+        <v>46023</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10386,7 +10381,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10429,7 +10424,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10443,10 +10438,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44474</v>
+        <v>44893</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10459,7 +10454,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10502,7 +10497,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10512,14 +10507,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45302</v>
+        <v>46181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10532,7 +10527,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10575,7 +10570,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10589,10 +10584,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45237</v>
+        <v>45153</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10605,7 +10600,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10648,7 +10643,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10662,10 +10657,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45195</v>
+        <v>46181</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,13 +10672,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10726,7 +10716,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10740,10 +10730,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45995</v>
+        <v>46181</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10756,7 +10746,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10799,7 +10789,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10813,10 +10803,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44470</v>
+        <v>46181</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10829,7 +10819,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10872,7 +10862,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10886,10 +10876,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44651</v>
+        <v>44990</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10901,13 +10891,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10950,7 +10935,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10960,14 +10945,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46002</v>
+        <v>44993</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10979,8 +10964,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.7</v>
+        <v>18.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11023,7 +11013,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11037,10 +11027,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45774</v>
+        <v>46181</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11053,7 +11043,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11096,7 +11086,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11110,10 +11100,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45053</v>
+        <v>46181</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11126,7 +11116,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11169,7 +11159,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11183,10 +11173,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45072</v>
+        <v>46181</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11198,13 +11188,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11247,7 +11232,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11261,10 +11246,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45194</v>
+        <v>45755</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11277,7 +11262,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11320,7 +11305,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11334,10 +11319,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44979</v>
+        <v>46037</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11350,7 +11335,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11393,7 +11378,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11403,14 +11388,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46023</v>
+        <v>45302</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11423,7 +11408,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11466,7 +11451,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11480,10 +11465,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44565</v>
+        <v>45237</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11496,7 +11481,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>13.4</v>
+        <v>4.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11539,7 +11524,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11553,10 +11538,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45275</v>
+        <v>45195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11566,6 +11551,11 @@
       <c r="G145" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -11612,7 +11602,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11626,10 +11616,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46037</v>
+        <v>44470</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11642,7 +11632,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11685,7 +11675,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11699,10 +11689,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44725</v>
+        <v>44651</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11714,8 +11704,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11758,7 +11753,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11772,10 +11767,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44791</v>
+        <v>46195</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11788,7 +11783,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11831,7 +11826,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11845,10 +11840,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44942</v>
+        <v>45774</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11861,7 +11856,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11904,7 +11899,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11918,10 +11913,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45076</v>
+        <v>45053</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11934,7 +11929,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11977,7 +11972,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11991,10 +11986,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45120</v>
+        <v>46077</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12006,13 +12001,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12055,7 +12045,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12069,10 +12059,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44977</v>
+        <v>46077</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12085,7 +12075,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12128,7 +12118,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12142,10 +12132,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45096</v>
+        <v>45072</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12163,7 +12153,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12206,7 +12196,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12220,10 +12210,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45109</v>
+        <v>45194</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12236,7 +12226,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12279,7 +12269,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12293,10 +12283,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44888</v>
+        <v>44979</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12309,7 +12299,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12352,7 +12342,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12366,10 +12356,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45615</v>
+        <v>44565</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12382,7 +12372,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>8.9</v>
+        <v>13.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12425,7 +12415,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12435,14 +12425,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45448</v>
+        <v>46069</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12455,7 +12445,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12498,7 +12488,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12512,10 +12502,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45236</v>
+        <v>45275</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12528,7 +12518,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12571,7 +12561,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12585,10 +12575,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46181</v>
+        <v>44725</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12601,7 +12591,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12644,7 +12634,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12658,10 +12648,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45076</v>
+        <v>44791</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12674,7 +12664,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12717,7 +12707,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12731,10 +12721,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46181</v>
+        <v>44942</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12747,7 +12737,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.6</v>
+        <v>9.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12790,7 +12780,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12804,10 +12794,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46181</v>
+        <v>45076</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12820,7 +12810,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12863,7 +12853,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12877,10 +12867,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46181</v>
+        <v>45120</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12892,8 +12882,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12936,7 +12931,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12950,10 +12945,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45321</v>
+        <v>44977</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12966,7 +12961,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13009,7 +13004,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13023,10 +13018,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46181</v>
+        <v>45096</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13038,8 +13033,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13082,7 +13082,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13096,10 +13096,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46181</v>
+        <v>45109</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13155,7 +13155,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13169,10 +13169,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46181</v>
+        <v>44888</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13228,7 +13228,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13242,10 +13242,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46077</v>
+        <v>45615</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.3</v>
+        <v>8.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13301,7 +13301,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13311,14 +13311,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46077</v>
+        <v>46121</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13388,10 +13388,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45053</v>
+        <v>45448</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13447,7 +13447,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13461,10 +13461,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45297</v>
+        <v>45236</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13534,10 +13534,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44830</v>
+        <v>45076</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13603,14 +13603,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45174</v>
+        <v>46135</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13666,7 +13666,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13680,10 +13680,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45552</v>
+        <v>45321</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13739,7 +13739,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13749,14 +13749,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46069</v>
+        <v>45053</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13812,7 +13812,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13826,10 +13826,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45021</v>
+        <v>45297</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13885,7 +13885,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13899,10 +13899,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44917</v>
+        <v>44830</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13958,7 +13958,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46195</v>
+        <v>46253</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14031,7 +14031,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14041,14 +14041,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45110</v>
+        <v>45174</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14104,7 +14104,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14118,10 +14118,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44671</v>
+        <v>45552</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14177,7 +14177,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14191,10 +14191,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45317</v>
+        <v>45021</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14250,7 +14250,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14264,10 +14264,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45069</v>
+        <v>46213</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14279,8 +14279,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14323,7 +14328,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14337,10 +14342,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46121</v>
+        <v>46213</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14352,8 +14357,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14396,7 +14406,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14410,10 +14420,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45498</v>
+        <v>44917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14426,7 +14436,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14469,7 +14479,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14483,10 +14493,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45764</v>
+        <v>45110</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14498,13 +14508,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14547,7 +14552,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14561,10 +14566,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45418</v>
+        <v>44671</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14577,7 +14582,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14620,7 +14625,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14634,10 +14639,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46135</v>
+        <v>45317</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14650,7 +14655,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14693,7 +14698,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14707,10 +14712,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45440</v>
+        <v>45069</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14723,7 +14728,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14766,7 +14771,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14780,10 +14785,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45181</v>
+        <v>46265</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14796,7 +14801,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14839,7 +14844,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14853,10 +14858,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45051</v>
+        <v>46265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14868,8 +14873,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14912,7 +14922,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14926,10 +14936,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45243</v>
+        <v>46265</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14941,8 +14951,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14985,7 +15000,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14999,10 +15014,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45281</v>
+        <v>45498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15015,7 +15030,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15058,7 +15073,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15072,10 +15087,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15087,8 +15102,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15131,7 +15151,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15145,10 +15165,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44798</v>
+        <v>45764</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15160,8 +15180,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15204,7 +15229,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15218,10 +15243,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46213</v>
+        <v>45418</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15233,13 +15258,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15282,7 +15302,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15296,10 +15316,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45594</v>
+        <v>45440</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15312,7 +15332,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15355,7 +15375,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15365,14 +15385,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46213</v>
+        <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15384,13 +15404,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15433,7 +15448,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15447,10 +15462,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45735</v>
+        <v>45181</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15462,13 +15477,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15511,7 +15521,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15525,10 +15535,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45735</v>
+        <v>45051</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15540,13 +15550,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15589,7 +15594,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15603,10 +15608,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44573</v>
+        <v>46231</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15619,7 +15624,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15662,7 +15667,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15676,10 +15681,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45076</v>
+        <v>46274</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15691,8 +15696,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15735,7 +15745,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15749,10 +15759,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15764,8 +15774,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15808,7 +15823,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15822,10 +15837,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44608</v>
+        <v>45243</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15838,7 +15853,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15881,7 +15896,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15895,10 +15910,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15910,13 +15925,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15959,7 +15969,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15973,10 +15983,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15990,11 +16000,11 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16037,7 +16047,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16051,10 +16061,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46265</v>
+        <v>45281</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16066,13 +16076,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16115,7 +16120,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16129,10 +16134,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44594</v>
+        <v>44798</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16145,7 +16150,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16188,7 +16193,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16202,10 +16207,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44910</v>
+        <v>45594</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16217,13 +16222,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16266,7 +16266,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16280,10 +16280,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45630</v>
+        <v>45735</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16295,8 +16295,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16339,7 +16344,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16353,10 +16358,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44967</v>
+        <v>45735</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16368,8 +16373,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16412,7 +16422,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16426,10 +16436,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45135</v>
+        <v>44573</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16441,13 +16451,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16490,7 +16495,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16504,10 +16509,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44496</v>
+        <v>45076</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16520,7 +16525,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16563,7 +16568,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16577,10 +16582,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44937</v>
+        <v>44608</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16593,7 +16598,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16636,7 +16641,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16650,10 +16655,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44938</v>
+        <v>44594</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16666,7 +16671,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16709,7 +16714,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16723,10 +16728,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46253</v>
+        <v>44910</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16738,8 +16743,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16782,7 +16792,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16796,10 +16806,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46231</v>
+        <v>45630</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16812,7 +16822,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>10.1</v>
+        <v>1.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16855,7 +16865,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16869,10 +16879,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46274</v>
+        <v>44967</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16884,13 +16894,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16933,7 +16938,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16947,10 +16952,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46275</v>
+        <v>45135</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16964,7 +16969,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I218" t="n">
@@ -17011,7 +17016,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17025,10 +17030,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46274</v>
+        <v>44496</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17041,7 +17046,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17084,7 +17089,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17098,10 +17103,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46274</v>
+        <v>44937</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17113,13 +17118,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44744</v>
+        <v>44938</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17235,7 +17235,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45740</v>
+        <v>44744</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17264,13 +17264,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17313,7 +17308,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17327,10 +17322,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45749</v>
+        <v>45740</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17342,8 +17337,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17386,7 +17386,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17400,10 +17400,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45226</v>
+        <v>45749</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17473,10 +17473,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45755</v>
+        <v>45226</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17546,10 +17546,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45576</v>
+        <v>45755</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17605,7 +17605,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17619,10 +17619,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45598</v>
+        <v>45576</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17688,14 +17688,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45594</v>
+        <v>45598</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17707,13 +17707,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17756,7 +17751,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17766,14 +17761,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45576</v>
+        <v>45594</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17785,8 +17780,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>17.1</v>
+        <v>5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17829,7 +17829,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45817</v>
+        <v>45576</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3</v>
+        <v>17.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17902,7 +17902,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17916,10 +17916,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45803</v>
+        <v>45817</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17989,10 +17989,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44685</v>
+        <v>45803</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45733</v>
+        <v>44685</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45880</v>
+        <v>45733</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
         <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE240"/>
+  <dimension ref="A1:AE239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10541-2026</t>
+          <t>A 1826-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46077</v>
+        <v>44938</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1111,264 +1111,264 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Vanlig backsmörblomma
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 1826-2023 artfynd.xlsx", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 1826-2023 karta.png", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 1826-2023 georefererad karta.tif", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 1826-2023 FSC-klagomål.docx", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 1826-2023 FSC-klagomål mail.docx", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 1826-2023 tillsynsbegäran.docx", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 1826-2023 tillsynsbegäran mail.docx", "A 1826-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 30575-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44762</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Skogsknipprot
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 30575-2022 artfynd.xlsx", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 30575-2022 karta.png", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 30575-2022 georefererad karta.tif", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 30575-2022 FSC-klagomål.docx", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 30575-2022 FSC-klagomål mail.docx", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 30575-2022 tillsynsbegäran.docx", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 30575-2022 tillsynsbegäran mail.docx", "A 30575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 10541-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Ekticka
 Rödvingetrast
 Spillkråka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 10541-2026 artfynd.xlsx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 10541-2026 karta.png", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 10541-2026 georefererad karta.tif", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 10541-2026 FSC-klagomål.docx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 10541-2026 FSC-klagomål mail.docx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 10541-2026 tillsynsbegäran.docx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 10541-2026 tillsynsbegäran mail.docx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 10541-2026 prioriterade fågelarter.docx", "A 10541-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 1826-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44938</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Vanlig backsmörblomma
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 1826-2023 artfynd.xlsx", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 1826-2023 karta.png", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 1826-2023 georefererad karta.tif", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 1826-2023 FSC-klagomål.docx", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 1826-2023 FSC-klagomål mail.docx", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 1826-2023 tillsynsbegäran.docx", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 1826-2023 tillsynsbegäran mail.docx", "A 1826-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 30575-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44762</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Skogsknipprot
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 30575-2022 artfynd.xlsx", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 30575-2022 karta.png", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 30575-2022 georefererad karta.tif", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 30575-2022 FSC-klagomål.docx", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 30575-2022 FSC-klagomål mail.docx", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 30575-2022 tillsynsbegäran.docx", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 30575-2022 tillsynsbegäran mail.docx", "A 30575-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58185-2025</t>
+          <t>A 57938-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45983</v>
+        <v>45982</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58185-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 57938-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45982</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 14537-2022</t>
+          <t>A 7821-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44655</v>
+        <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2013,13 +2013,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2062,7 +2057,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10438-2022</t>
+          <t>A 14537-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2072,14 +2067,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44623</v>
+        <v>44655</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2091,8 +2086,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7821-2022</t>
+          <t>A 10438-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2145,14 +2145,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44608</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51865-2021</t>
+          <t>A 7742-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44462</v>
+        <v>44608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7742-2022</t>
+          <t>A 64406-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44608</v>
+        <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2865,7 +2865,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 64406-2021</t>
+          <t>A 42161-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44511</v>
+        <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42161-2022</t>
+          <t>A 51891-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44830</v>
+        <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51891-2022</t>
+          <t>A 55645-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44867</v>
+        <v>44888</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55645-2022</t>
+          <t>A 11326-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44888</v>
+        <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>10.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11326-2022</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44629</v>
+        <v>45096</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3186,8 +3186,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>10.4</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3230,7 +3235,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29366-2022</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3244,10 +3249,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44752</v>
+        <v>45749</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3260,7 +3265,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>6.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3303,7 +3308,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26244-2022</t>
+          <t>A 29366-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3317,10 +3322,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44735</v>
+        <v>44752</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3333,7 +3338,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3376,7 +3381,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56633-2021</t>
+          <t>A 26244-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3390,10 +3395,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44480</v>
+        <v>44735</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3406,7 +3411,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>11.2</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3449,7 +3454,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17628-2022</t>
+          <t>A 56633-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44680</v>
+        <v>44480</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3479,7 +3484,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>11.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3522,7 +3527,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 14522-2022</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3536,10 +3541,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44655</v>
+        <v>45483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3551,13 +3556,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12856-2022</t>
+          <t>A 55450-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44642</v>
+        <v>44475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55450-2021</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44475</v>
+        <v>45051</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44734</v>
+        <v>45740</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3775,8 +3775,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3819,7 +3824,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 17628-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3838,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45755</v>
+        <v>44680</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3854,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3897,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 14522-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3911,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44642</v>
+        <v>44655</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3921,8 +3926,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3975,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3989,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44830</v>
+        <v>44744</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +4005,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4048,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 12856-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4062,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45735</v>
+        <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4068,7 +4078,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4121,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4135,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44910</v>
+        <v>45191</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4151,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4194,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4208,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44977</v>
+        <v>45226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4224,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4267,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4281,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45483</v>
+        <v>44725</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4287,7 +4297,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4330,7 +4340,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4344,10 +4354,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45184</v>
+        <v>45297</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4359,13 +4369,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4408,7 +4413,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4422,10 +4427,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45036</v>
+        <v>45774</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4438,7 +4443,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4481,7 +4486,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4495,10 +4500,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45275</v>
+        <v>45576</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4554,7 +4559,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,10 +4573,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44496</v>
+        <v>45440</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4584,7 +4589,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4627,7 +4632,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4641,10 +4646,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45013</v>
+        <v>44945</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4657,7 +4662,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4700,7 +4705,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4710,14 +4715,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45343</v>
+        <v>44496</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4730,7 +4735,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4773,7 +4778,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44937</v>
+        <v>45755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4803,7 +4808,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4846,7 +4851,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4860,10 +4865,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45191</v>
+        <v>44888</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4876,7 +4881,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4919,7 +4924,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4933,10 +4938,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44593</v>
+        <v>45598</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4949,7 +4954,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4992,7 +4997,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44594</v>
+        <v>45237</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5022,7 +5027,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5065,7 +5070,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45120</v>
+        <v>44594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5094,13 +5099,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44999</v>
+        <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5172,13 +5172,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5221,7 +5216,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5231,14 +5226,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44623</v>
+        <v>45053</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5251,7 +5246,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5294,7 +5289,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5308,10 +5303,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44476</v>
+        <v>45735</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5324,7 +5319,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5367,7 +5362,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5381,10 +5376,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44938</v>
+        <v>44918</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5397,7 +5392,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5440,7 +5435,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5450,14 +5445,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44903</v>
+        <v>45076</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5470,7 +5465,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5513,7 +5508,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5527,10 +5522,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44678</v>
+        <v>44470</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5543,7 +5538,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5586,7 +5581,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5600,10 +5595,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45041</v>
+        <v>45076</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5616,7 +5611,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5659,7 +5654,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,10 +5668,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45576</v>
+        <v>45321</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5689,7 +5684,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5732,7 +5727,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5742,14 +5737,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45096</v>
+        <v>45594</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5763,11 +5758,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5810,7 +5805,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5824,10 +5819,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44918</v>
+        <v>44468</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5840,7 +5835,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5883,7 +5878,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5897,10 +5892,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45432</v>
+        <v>45615</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5913,7 +5908,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>8.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5956,7 +5951,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5970,10 +5965,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45076</v>
+        <v>44918</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5986,7 +5981,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6029,7 +6024,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6043,10 +6038,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45076</v>
+        <v>44979</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6059,7 +6054,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6102,7 +6097,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45210</v>
+        <v>44859</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6132,7 +6127,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6175,7 +6170,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6189,10 +6184,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45754</v>
+        <v>44859</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6204,13 +6199,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6253,7 +6243,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6267,10 +6257,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44511</v>
+        <v>45275</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6283,7 +6273,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6326,7 +6316,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6340,10 +6330,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45236</v>
+        <v>45576</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6356,7 +6346,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>17.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6399,7 +6389,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6413,10 +6403,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6429,7 +6419,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6472,7 +6462,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6486,10 +6476,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45175</v>
+        <v>45120</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6501,8 +6491,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6545,7 +6540,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6559,10 +6554,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45880</v>
+        <v>45021</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6575,7 +6570,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6618,7 +6613,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6632,10 +6627,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44742</v>
+        <v>45306</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6648,7 +6643,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6691,7 +6686,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6705,10 +6700,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45582</v>
+        <v>45905</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6721,7 +6716,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6764,7 +6759,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6778,10 +6773,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46136</v>
+        <v>45905</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6794,7 +6789,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6837,7 +6832,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6847,14 +6842,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44594</v>
+        <v>44623</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6867,7 +6862,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6910,7 +6905,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6924,10 +6919,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44496</v>
+        <v>45529</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6940,7 +6935,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6983,7 +6978,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6993,14 +6988,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44902</v>
+        <v>44903</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7013,7 +7008,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7056,7 +7051,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45986</v>
+        <v>44476</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7086,7 +7081,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7129,7 +7124,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7143,10 +7138,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46136</v>
+        <v>45109</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7159,7 +7154,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>11.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7202,7 +7197,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7216,10 +7211,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45905</v>
+        <v>44496</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7232,7 +7227,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7275,7 +7270,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7289,10 +7284,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45905</v>
+        <v>45275</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7305,7 +7300,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7348,7 +7343,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7362,10 +7357,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45294</v>
+        <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7378,7 +7373,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7421,7 +7416,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7435,10 +7430,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45529</v>
+        <v>44475</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7451,7 +7446,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7494,7 +7489,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7508,10 +7503,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45278</v>
+        <v>44937</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7524,7 +7519,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7567,7 +7562,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7581,10 +7576,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45636</v>
+        <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7640,7 +7635,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7654,10 +7649,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44945</v>
+        <v>44990</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7670,7 +7665,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7713,7 +7708,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7727,10 +7722,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44943</v>
+        <v>45428</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7743,7 +7738,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7786,7 +7781,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7800,10 +7795,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46147</v>
+        <v>45448</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7816,7 +7811,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7859,7 +7854,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7873,10 +7868,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45923</v>
+        <v>45174</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7889,7 +7884,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7932,7 +7927,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7946,10 +7941,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45297</v>
+        <v>44977</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7962,7 +7957,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8005,7 +8000,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8015,14 +8010,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46155</v>
+        <v>45302</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8035,7 +8030,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8078,7 +8073,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8092,10 +8087,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44573</v>
+        <v>45418</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8108,7 +8103,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8151,7 +8146,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8165,10 +8160,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44917</v>
+        <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8180,8 +8175,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>18.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8224,7 +8224,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44917</v>
+        <v>44573</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8297,7 +8297,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45905</v>
+        <v>44967</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8384,10 +8384,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45959</v>
+        <v>45754</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8399,8 +8399,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8443,7 +8448,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8457,10 +8462,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45247</v>
+        <v>44617</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8472,8 +8477,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8516,7 +8526,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8530,10 +8540,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45285</v>
+        <v>45764</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8545,8 +8555,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8589,7 +8604,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8603,10 +8618,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45239</v>
+        <v>44917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8619,7 +8634,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8662,7 +8677,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8676,10 +8691,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44565</v>
+        <v>44917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8692,7 +8707,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8735,7 +8750,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8745,14 +8760,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44990</v>
+        <v>44594</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8765,7 +8780,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8808,7 +8823,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8822,10 +8837,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45981</v>
+        <v>44910</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,13 +8852,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>15.9</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8886,7 +8896,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8900,10 +8910,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45980</v>
+        <v>45041</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8916,7 +8926,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8959,7 +8969,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8973,10 +8983,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45597</v>
+        <v>45630</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8989,7 +8999,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9032,7 +9042,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9046,10 +9056,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45982</v>
+        <v>45036</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9062,7 +9072,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9105,7 +9115,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9119,10 +9129,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44859</v>
+        <v>44671</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9135,7 +9145,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9178,7 +9188,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9192,10 +9202,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44918</v>
+        <v>45056</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9208,7 +9218,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9251,7 +9261,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9265,10 +9275,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45306</v>
+        <v>44937</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9281,7 +9291,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9324,7 +9334,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9338,10 +9348,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44474</v>
+        <v>45594</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9354,7 +9364,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9397,7 +9407,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9411,10 +9421,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44859</v>
+        <v>44938</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9427,7 +9437,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9470,7 +9480,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9484,10 +9494,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44859</v>
+        <v>45817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9500,7 +9510,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9543,7 +9553,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9557,10 +9567,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45995</v>
+        <v>44593</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9573,7 +9583,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9616,7 +9626,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9630,10 +9640,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45630</v>
+        <v>45181</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9646,7 +9656,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9689,7 +9699,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9703,10 +9713,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44859</v>
+        <v>44651</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,8 +9728,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9762,7 +9777,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9776,10 +9791,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44859</v>
+        <v>45076</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9792,7 +9807,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9835,7 +9850,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9845,14 +9860,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46002</v>
+        <v>45552</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9865,7 +9880,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9908,7 +9923,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9922,10 +9937,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44475</v>
+        <v>45959</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9938,7 +9953,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9981,7 +9996,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9995,10 +10010,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45191</v>
+        <v>44594</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10011,7 +10026,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10054,7 +10069,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10068,10 +10083,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44468</v>
+        <v>44565</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10084,7 +10099,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10127,7 +10142,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10141,10 +10156,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45056</v>
+        <v>45069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10157,7 +10172,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10200,7 +10215,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10214,10 +10229,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45109</v>
+        <v>45239</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10230,7 +10245,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10273,7 +10288,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10287,10 +10302,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44617</v>
+        <v>44642</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,13 +10317,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10351,7 +10361,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10365,10 +10375,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46023</v>
+        <v>45096</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,8 +10390,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10424,7 +10439,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10438,10 +10453,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44893</v>
+        <v>45109</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10454,7 +10469,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10497,7 +10512,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10511,10 +10526,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46181</v>
+        <v>45980</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10527,7 +10542,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10570,7 +10585,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10584,10 +10599,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45153</v>
+        <v>45195</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,8 +10614,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10643,7 +10663,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10657,10 +10677,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46181</v>
+        <v>45247</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10673,7 +10693,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10716,7 +10736,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10730,10 +10750,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46181</v>
+        <v>44734</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10746,7 +10766,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10789,7 +10809,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10803,10 +10823,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46181</v>
+        <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10819,7 +10839,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10862,7 +10882,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10876,10 +10896,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44990</v>
+        <v>45981</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10891,8 +10911,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>3.6</v>
+        <v>15.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10935,7 +10960,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10949,10 +10974,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44993</v>
+        <v>45982</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10964,13 +10989,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>18.6</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11013,7 +11033,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11027,10 +11047,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46181</v>
+        <v>44999</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11042,8 +11062,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11086,7 +11111,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11100,10 +11125,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46181</v>
+        <v>44791</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11116,7 +11141,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11159,7 +11184,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11173,10 +11198,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46181</v>
+        <v>45194</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11232,7 +11257,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11246,10 +11271,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45755</v>
+        <v>44474</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11262,7 +11287,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11305,7 +11330,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11319,10 +11344,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46037</v>
+        <v>45135</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11334,8 +11359,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11378,7 +11408,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11388,14 +11418,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45302</v>
+        <v>45755</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11408,7 +11438,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11451,7 +11481,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11465,10 +11495,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45237</v>
+        <v>45236</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11481,7 +11511,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11524,7 +11554,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11538,10 +11568,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45195</v>
+        <v>46023</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11553,13 +11583,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11602,7 +11627,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11616,10 +11641,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44470</v>
+        <v>45995</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11632,7 +11657,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11675,7 +11700,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11689,10 +11714,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44651</v>
+        <v>45755</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11704,13 +11729,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11753,7 +11773,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11763,14 +11783,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46195</v>
+        <v>46002</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11783,7 +11803,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11826,7 +11846,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11840,10 +11860,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45774</v>
+        <v>45317</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11856,7 +11876,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11899,7 +11919,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11913,10 +11933,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45053</v>
+        <v>44830</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11929,7 +11949,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11972,7 +11992,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11986,10 +12006,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46077</v>
+        <v>45294</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12002,7 +12022,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12045,7 +12065,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12059,10 +12079,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46077</v>
+        <v>45210</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12075,7 +12095,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12118,7 +12138,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12132,10 +12152,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45072</v>
+        <v>45120</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12153,7 +12173,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12196,7 +12216,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12210,10 +12230,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45194</v>
+        <v>44678</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12226,7 +12246,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12269,7 +12289,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12283,10 +12303,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44979</v>
+        <v>46037</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12299,7 +12319,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12342,7 +12362,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12356,10 +12376,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44565</v>
+        <v>44608</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12372,7 +12392,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>13.4</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12415,7 +12435,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12425,14 +12445,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46069</v>
+        <v>45243</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12445,7 +12465,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12488,7 +12508,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12502,10 +12522,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45275</v>
+        <v>45191</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12518,7 +12538,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12561,7 +12581,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12571,14 +12591,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44725</v>
+        <v>44990</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12591,7 +12611,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12634,7 +12654,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12648,10 +12668,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44791</v>
+        <v>44910</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12663,8 +12683,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12707,7 +12732,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12721,10 +12746,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44942</v>
+        <v>46077</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12737,7 +12762,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12780,7 +12805,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12794,10 +12819,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45076</v>
+        <v>46077</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12810,7 +12835,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12853,7 +12878,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12867,10 +12892,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45120</v>
+        <v>45498</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12882,13 +12907,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12931,7 +12951,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12945,10 +12965,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44977</v>
+        <v>45576</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12961,7 +12981,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13004,7 +13024,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13018,10 +13038,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45096</v>
+        <v>44798</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13031,11 +13051,6 @@
       <c r="G165" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I165" t="n">
@@ -13082,7 +13097,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13092,14 +13107,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45109</v>
+        <v>45343</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13112,7 +13127,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>11.8</v>
+        <v>1.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13155,7 +13170,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13165,14 +13180,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44888</v>
+        <v>46069</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13185,7 +13200,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13228,7 +13243,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13242,10 +13257,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45615</v>
+        <v>45072</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13257,8 +13272,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>8.9</v>
+        <v>2.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13301,7 +13321,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13311,14 +13331,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46121</v>
+        <v>44942</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13331,7 +13351,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>9.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13374,7 +13394,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13388,10 +13408,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45448</v>
+        <v>45153</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13404,7 +13424,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13447,7 +13467,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13461,10 +13481,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45236</v>
+        <v>44565</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13477,7 +13497,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13520,7 +13540,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13534,10 +13554,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45076</v>
+        <v>44573</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13550,7 +13570,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13593,7 +13613,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13607,10 +13627,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46135</v>
+        <v>45803</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13623,7 +13643,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13666,7 +13686,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13680,10 +13700,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45321</v>
+        <v>45733</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13696,7 +13716,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13739,7 +13759,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13753,10 +13773,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45053</v>
+        <v>44859</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13769,7 +13789,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13812,7 +13832,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13826,10 +13846,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45297</v>
+        <v>45013</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13842,7 +13862,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13885,7 +13905,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13899,10 +13919,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44830</v>
+        <v>44685</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13915,7 +13935,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13958,7 +13978,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13972,10 +13992,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46253</v>
+        <v>45597</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13988,7 +14008,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14031,7 +14051,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14041,14 +14061,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45174</v>
+        <v>45076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14061,7 +14081,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14104,7 +14124,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14118,10 +14138,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45552</v>
+        <v>45110</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14134,7 +14154,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14177,7 +14197,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14191,10 +14211,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45021</v>
+        <v>45175</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14207,7 +14227,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14250,7 +14270,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14264,10 +14284,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46213</v>
+        <v>45281</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14279,13 +14299,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14328,7 +14343,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14338,14 +14353,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46213</v>
+        <v>44830</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14357,13 +14372,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14406,7 +14416,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14416,14 +14426,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44917</v>
+        <v>46121</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14479,7 +14489,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14493,10 +14503,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45110</v>
+        <v>44917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14509,7 +14519,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14552,7 +14562,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14566,10 +14576,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44671</v>
+        <v>44938</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14582,7 +14592,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14625,7 +14635,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14639,10 +14649,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45317</v>
+        <v>44977</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14655,7 +14665,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14698,7 +14708,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14712,10 +14722,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45069</v>
+        <v>45278</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14728,7 +14738,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14771,7 +14781,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14785,10 +14795,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46265</v>
+        <v>44859</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14801,7 +14811,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14844,7 +14854,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14858,10 +14868,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46265</v>
+        <v>45636</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14873,13 +14883,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14922,7 +14927,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14936,10 +14941,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46265</v>
+        <v>46135</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14951,13 +14956,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15000,7 +15000,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45498</v>
+        <v>45880</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15073,7 +15073,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15087,10 +15087,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46265</v>
+        <v>46136</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15102,13 +15102,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15151,7 +15146,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15165,10 +15160,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45764</v>
+        <v>45184</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15182,11 +15177,11 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15229,7 +15224,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15243,10 +15238,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45418</v>
+        <v>44893</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15259,7 +15254,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15302,7 +15297,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15316,10 +15311,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45440</v>
+        <v>45053</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15332,7 +15327,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15375,7 +15370,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15389,10 +15384,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46253</v>
+        <v>45630</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15405,7 +15400,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15448,7 +15443,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15462,10 +15457,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45181</v>
+        <v>44742</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15478,7 +15473,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15521,7 +15516,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15535,10 +15530,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45051</v>
+        <v>45076</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15594,7 +15589,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15608,10 +15603,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46231</v>
+        <v>45582</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15624,7 +15619,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>10.1</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15667,7 +15662,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15681,10 +15676,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46274</v>
+        <v>45986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15696,13 +15691,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15745,7 +15735,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15759,10 +15749,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46275</v>
+        <v>45285</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15774,13 +15764,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15823,7 +15808,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15837,10 +15822,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45243</v>
+        <v>46136</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15853,7 +15838,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15896,7 +15881,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15910,10 +15895,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46274</v>
+        <v>45297</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15926,7 +15911,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15969,7 +15954,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15983,10 +15968,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46274</v>
+        <v>44902</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15998,13 +15983,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16047,7 +16027,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16061,10 +16041,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45281</v>
+        <v>44943</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16077,7 +16057,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16120,7 +16100,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16134,10 +16114,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44798</v>
+        <v>45735</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16149,8 +16129,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16193,7 +16178,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16207,10 +16192,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45594</v>
+        <v>45735</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16222,8 +16207,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16266,7 +16256,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16280,10 +16270,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45735</v>
+        <v>46147</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16295,13 +16285,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16344,7 +16329,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16354,14 +16339,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45735</v>
+        <v>45923</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16373,13 +16358,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16422,7 +16402,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16436,10 +16416,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44573</v>
+        <v>46155</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16495,7 +16475,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16509,10 +16489,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45076</v>
+        <v>45905</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16525,7 +16505,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16568,7 +16548,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16582,10 +16562,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44608</v>
+        <v>46181</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16598,7 +16578,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16641,7 +16621,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16655,10 +16635,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44594</v>
+        <v>46181</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16671,7 +16651,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16714,7 +16694,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16728,10 +16708,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44910</v>
+        <v>46181</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16743,13 +16723,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16792,7 +16767,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16806,10 +16781,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45630</v>
+        <v>46181</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16822,7 +16797,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16865,7 +16840,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16879,10 +16854,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44967</v>
+        <v>46181</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16895,7 +16870,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16938,7 +16913,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16952,10 +16927,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45135</v>
+        <v>46181</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16967,13 +16942,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17016,7 +16986,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17030,10 +17000,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44496</v>
+        <v>46181</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17046,7 +17016,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17089,7 +17059,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17103,10 +17073,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44937</v>
+        <v>46195</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17119,7 +17089,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17162,7 +17132,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17176,10 +17146,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44938</v>
+        <v>46253</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17192,7 +17162,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17235,7 +17205,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17249,10 +17219,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44744</v>
+        <v>46213</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17264,8 +17234,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17308,7 +17283,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17318,14 +17293,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45740</v>
+        <v>46213</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17339,11 +17314,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17386,7 +17361,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17400,10 +17375,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45749</v>
+        <v>46265</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17416,7 +17391,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17459,7 +17434,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17473,10 +17448,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45226</v>
+        <v>46265</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17488,8 +17463,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17532,7 +17512,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17546,10 +17526,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45755</v>
+        <v>46265</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17561,8 +17541,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17605,7 +17590,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17619,10 +17604,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45576</v>
+        <v>46265</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17634,8 +17619,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17678,7 +17668,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17692,10 +17682,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45598</v>
+        <v>46253</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17708,7 +17698,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17751,7 +17741,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17761,14 +17751,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45594</v>
+        <v>46231</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17780,13 +17770,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>5</v>
+        <v>10.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17829,7 +17814,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17843,10 +17828,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45576</v>
+        <v>46274</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17859,7 +17844,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>17.1</v>
+        <v>3.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17902,7 +17887,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17916,10 +17901,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45817</v>
+        <v>46274</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17931,8 +17916,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17975,7 +17965,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17989,10 +17979,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45803</v>
+        <v>46274</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18004,8 +17994,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18048,7 +18043,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18062,10 +18057,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44685</v>
+        <v>46275</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18077,8 +18072,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18121,24 +18121,24 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>S 1502-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45733</v>
+        <v>45051</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18150,8 +18150,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18194,7 +18199,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 1502-2023</t>
+          <t>S 1214-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18208,10 +18213,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45051</v>
+        <v>45761</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18225,11 +18230,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18272,7 +18277,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 1214-2025</t>
+          <t>S 1213-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18289,7 +18294,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18307,7 +18312,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18350,7 +18355,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 1213-2025</t>
+          <t>S 1266-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18364,10 +18369,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45761</v>
+        <v>45764</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18385,7 +18390,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18428,7 +18433,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 1266-2025</t>
+          <t>S 1260-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18442,10 +18447,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45764</v>
+        <v>45763</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18463,7 +18468,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18503,10 +18508,10 @@
       </c>
       <c r="V238" s="2" t="inlineStr"/>
     </row>
-    <row r="239" ht="15" customHeight="1">
+    <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 1260-2025</t>
+          <t>S 1137-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18520,10 +18525,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45763</v>
+        <v>45755</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18535,13 +18540,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>1.3</v>
+        <v>10.6</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18580,79 +18580,6 @@
         <v>0</v>
       </c>
       <c r="V239" s="2" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>S 1137-2025</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D240" s="1" t="n">
-        <v>45755</v>
-      </c>
-      <c r="E240" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I240" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J240" t="n">
-        <v>0</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0</v>
-      </c>
-      <c r="L240" t="n">
-        <v>0</v>
-      </c>
-      <c r="M240" t="n">
-        <v>0</v>
-      </c>
-      <c r="N240" t="n">
-        <v>0</v>
-      </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="P240" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="n">
-        <v>0</v>
-      </c>
-      <c r="T240" t="n">
-        <v>0</v>
-      </c>
-      <c r="U240" t="n">
-        <v>0</v>
-      </c>
-      <c r="V240" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1826-2023</t>
+          <t>A 10541-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44938</v>
+        <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1111,264 +1111,264 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Ekticka
+Rödvingetrast
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 10541-2026 artfynd.xlsx", "A 10541-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 10541-2026 karta.png", "A 10541-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 10541-2026 georefererad karta.tif", "A 10541-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 10541-2026 FSC-klagomål.docx", "A 10541-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 10541-2026 FSC-klagomål mail.docx", "A 10541-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 10541-2026 tillsynsbegäran.docx", "A 10541-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 10541-2026 tillsynsbegäran mail.docx", "A 10541-2026")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 10541-2026 prioriterade fågelarter.docx", "A 10541-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 1826-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44938</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Vanlig backsmörblomma
 Gullviva</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 1826-2023 artfynd.xlsx", "A 1826-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 1826-2023 karta.png", "A 1826-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 1826-2023 georefererad karta.tif", "A 1826-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 1826-2023 FSC-klagomål.docx", "A 1826-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 1826-2023 FSC-klagomål mail.docx", "A 1826-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 1826-2023 tillsynsbegäran.docx", "A 1826-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 1826-2023 tillsynsbegäran mail.docx", "A 1826-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 30575-2022</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>44762</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>10.5</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Skogsknipprot
 Blåsippa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 30575-2022 artfynd.xlsx", "A 30575-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 30575-2022 karta.png", "A 30575-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 30575-2022 georefererad karta.tif", "A 30575-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 30575-2022 FSC-klagomål.docx", "A 30575-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 30575-2022 FSC-klagomål mail.docx", "A 30575-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 30575-2022 tillsynsbegäran.docx", "A 30575-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 30575-2022 tillsynsbegäran mail.docx", "A 30575-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 10541-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46077</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Ekticka
-Rödvingetrast
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 10541-2026 artfynd.xlsx", "A 10541-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 10541-2026 karta.png", "A 10541-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 10541-2026 georefererad karta.tif", "A 10541-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 10541-2026 FSC-klagomål.docx", "A 10541-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 10541-2026 FSC-klagomål mail.docx", "A 10541-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 10541-2026 tillsynsbegäran.docx", "A 10541-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 10541-2026 tillsynsbegäran mail.docx", "A 10541-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 10541-2026 prioriterade fågelarter.docx", "A 10541-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57938-2025</t>
+          <t>A 58185-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 57938-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58185-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 7821-2022</t>
+          <t>A 14537-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44608</v>
+        <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2013,8 +2013,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2057,7 +2062,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14537-2022</t>
+          <t>A 10438-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2067,14 +2072,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44655</v>
+        <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2086,13 +2091,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10438-2022</t>
+          <t>A 7821-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2145,14 +2145,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44623</v>
+        <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44888</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 29366-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45096</v>
+        <v>44752</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3186,13 +3186,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3235,7 +3230,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 26244-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3249,10 +3244,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45749</v>
+        <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3265,7 +3260,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3308,7 +3303,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29366-2022</t>
+          <t>A 56633-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3322,10 +3317,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44752</v>
+        <v>44480</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3338,7 +3333,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>11.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3381,7 +3376,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26244-2022</t>
+          <t>A 17628-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3395,10 +3390,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44735</v>
+        <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3411,7 +3406,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3454,7 +3449,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56633-2021</t>
+          <t>A 14522-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44480</v>
+        <v>44655</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3483,8 +3478,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>11.2</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 12856-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45483</v>
+        <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>44475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45051</v>
+        <v>45755</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45740</v>
+        <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3775,13 +3775,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3824,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17628-2022</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3838,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44680</v>
+        <v>44734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3854,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3897,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14522-2022</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3911,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44655</v>
+        <v>44830</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3926,13 +3921,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3975,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3989,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44744</v>
+        <v>45735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4005,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4048,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12856-2022</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4062,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44642</v>
+        <v>44910</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4078,7 +4068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4121,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4135,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45191</v>
+        <v>44977</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4151,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4194,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45226</v>
+        <v>45483</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4224,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4267,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44725</v>
+        <v>45184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4296,8 +4286,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4340,7 +4335,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4354,10 +4349,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45297</v>
+        <v>45036</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4370,7 +4365,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4413,7 +4408,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4427,10 +4422,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45774</v>
+        <v>45275</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4443,7 +4438,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4486,7 +4481,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4500,10 +4495,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45576</v>
+        <v>45191</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4516,7 +4511,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4559,7 +4554,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4573,10 +4568,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45440</v>
+        <v>44937</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4589,7 +4584,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4632,7 +4627,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4646,10 +4641,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44945</v>
+        <v>44593</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4662,7 +4657,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4705,7 +4700,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4719,10 +4714,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44496</v>
+        <v>44594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4735,7 +4730,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4778,7 +4773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45755</v>
+        <v>44496</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4808,7 +4803,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4851,7 +4846,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4865,10 +4860,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44888</v>
+        <v>45120</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4880,8 +4875,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45598</v>
+        <v>45013</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45237</v>
+        <v>44999</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5026,8 +5026,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5070,7 +5075,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5080,14 +5085,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44594</v>
+        <v>44623</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5100,7 +5105,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5143,7 +5148,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5153,14 +5158,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45236</v>
+        <v>45343</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5173,7 +5178,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5216,7 +5221,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5230,10 +5235,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45053</v>
+        <v>45076</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5246,7 +5251,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5289,7 +5294,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5303,10 +5308,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45735</v>
+        <v>45076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5319,7 +5324,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5362,7 +5367,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5376,10 +5381,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44918</v>
+        <v>44476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5392,7 +5397,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5435,7 +5440,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5449,10 +5454,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45076</v>
+        <v>44938</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5465,7 +5470,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5508,7 +5513,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5518,14 +5523,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44470</v>
+        <v>44903</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5538,7 +5543,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5581,7 +5586,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5595,10 +5600,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45076</v>
+        <v>44678</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5611,7 +5616,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5654,7 +5659,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5668,10 +5673,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45321</v>
+        <v>45041</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5684,7 +5689,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5727,7 +5732,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5737,14 +5742,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45594</v>
+        <v>45576</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5756,13 +5761,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44468</v>
+        <v>44918</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5878,7 +5878,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45615</v>
+        <v>45096</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5907,8 +5907,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5951,7 +5956,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5965,10 +5970,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44918</v>
+        <v>45432</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5981,7 +5986,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6024,7 +6029,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6038,10 +6043,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44979</v>
+        <v>45210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6054,7 +6059,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6097,7 +6102,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44859</v>
+        <v>45754</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6126,8 +6131,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6170,7 +6180,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6184,10 +6194,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44859</v>
+        <v>44511</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6200,7 +6210,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6243,7 +6253,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6257,10 +6267,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45275</v>
+        <v>45428</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6273,7 +6283,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6316,7 +6326,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6330,10 +6340,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45576</v>
+        <v>45175</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6346,7 +6356,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>17.1</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6389,7 +6399,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6403,10 +6413,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45432</v>
+        <v>45236</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6419,7 +6429,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6462,7 +6472,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6476,10 +6486,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45120</v>
+        <v>45880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6491,13 +6501,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6540,7 +6545,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6554,10 +6559,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45021</v>
+        <v>44742</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6570,7 +6575,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6613,7 +6618,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6627,10 +6632,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45306</v>
+        <v>45582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6643,7 +6648,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6686,7 +6691,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6700,10 +6705,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>46136</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6716,7 +6721,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6776,7 +6781,7 @@
         <v>45905</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6832,7 +6837,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6842,14 +6847,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44623</v>
+        <v>45905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6862,7 +6867,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6905,7 +6910,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6919,10 +6924,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45529</v>
+        <v>44902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6935,7 +6940,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6978,7 +6983,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6988,14 +6993,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44903</v>
+        <v>44594</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7008,7 +7013,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7051,7 +7056,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7065,10 +7070,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44476</v>
+        <v>44496</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7081,7 +7086,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7124,7 +7129,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7138,10 +7143,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45109</v>
+        <v>45294</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7154,7 +7159,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7197,7 +7202,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44496</v>
+        <v>45529</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7227,7 +7232,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7270,7 +7275,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7284,10 +7289,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45275</v>
+        <v>45278</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7300,7 +7305,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7343,7 +7348,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7357,10 +7362,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44859</v>
+        <v>45636</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7373,7 +7378,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7416,7 +7421,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7430,10 +7435,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44475</v>
+        <v>44945</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7446,7 +7451,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7489,7 +7494,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7503,10 +7508,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44937</v>
+        <v>44943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7519,7 +7524,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7562,7 +7567,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7576,10 +7581,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44511</v>
+        <v>45986</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7592,7 +7597,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7635,7 +7640,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7649,10 +7654,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44990</v>
+        <v>46136</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7665,7 +7670,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7708,7 +7713,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7722,10 +7727,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45428</v>
+        <v>45297</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7738,7 +7743,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7781,7 +7786,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7795,10 +7800,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45448</v>
+        <v>44573</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7811,7 +7816,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7854,7 +7859,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7864,14 +7869,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45174</v>
+        <v>44917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7884,7 +7889,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7927,7 +7932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7941,10 +7946,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44977</v>
+        <v>44917</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7957,7 +7962,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8000,7 +8005,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8010,14 +8015,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45302</v>
+        <v>45247</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8030,7 +8035,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8073,7 +8078,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8087,10 +8092,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45418</v>
+        <v>45285</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8103,7 +8108,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8146,7 +8151,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8160,10 +8165,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44993</v>
+        <v>45239</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8175,13 +8180,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>18.6</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8224,7 +8224,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44573</v>
+        <v>44565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44967</v>
+        <v>45959</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45754</v>
+        <v>44990</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8399,13 +8399,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8448,7 +8443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8462,10 +8457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44617</v>
+        <v>45597</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8477,13 +8472,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8526,7 +8516,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8540,10 +8530,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45764</v>
+        <v>44859</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8555,13 +8545,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8604,7 +8589,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8618,10 +8603,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8634,7 +8619,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8677,7 +8662,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8691,10 +8676,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44917</v>
+        <v>45981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8706,8 +8691,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>15.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8750,7 +8740,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8764,10 +8754,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44594</v>
+        <v>45980</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8780,7 +8770,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8823,7 +8813,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8837,10 +8827,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44910</v>
+        <v>45306</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8853,7 +8843,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8896,7 +8886,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8910,10 +8900,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45041</v>
+        <v>45982</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8926,7 +8916,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8969,7 +8959,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8983,10 +8973,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45630</v>
+        <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8999,7 +8989,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9042,7 +9032,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9056,10 +9046,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45036</v>
+        <v>44859</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9072,7 +9062,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9115,7 +9105,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9129,10 +9119,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44671</v>
+        <v>45630</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9145,7 +9135,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9188,7 +9178,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9202,10 +9192,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45056</v>
+        <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9218,7 +9208,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9261,7 +9251,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9275,10 +9265,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44937</v>
+        <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9291,7 +9281,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9334,7 +9324,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9348,10 +9338,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45594</v>
+        <v>46147</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9364,7 +9354,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9407,7 +9397,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9417,14 +9407,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44938</v>
+        <v>45923</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9437,7 +9427,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9480,7 +9470,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9494,10 +9484,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45817</v>
+        <v>44474</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9510,7 +9500,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9553,7 +9543,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9567,10 +9557,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44593</v>
+        <v>45995</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9583,7 +9573,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9626,7 +9616,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9640,10 +9630,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45181</v>
+        <v>44475</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9656,7 +9646,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9699,7 +9689,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9713,10 +9703,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44651</v>
+        <v>45191</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9728,13 +9718,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9777,7 +9762,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9787,14 +9772,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45076</v>
+        <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9807,7 +9792,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9850,7 +9835,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9864,10 +9849,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45552</v>
+        <v>46155</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9880,7 +9865,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9923,7 +9908,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9937,10 +9922,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45959</v>
+        <v>44468</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9953,7 +9938,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9996,7 +9981,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10010,10 +9995,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44594</v>
+        <v>45056</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10026,7 +10011,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10069,7 +10054,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10083,10 +10068,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44565</v>
+        <v>45109</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10099,7 +10084,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10142,7 +10127,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10156,10 +10141,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45069</v>
+        <v>44617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10171,8 +10156,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10215,7 +10205,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10229,10 +10219,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45239</v>
+        <v>44893</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10245,7 +10235,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10288,7 +10278,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10302,10 +10292,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44642</v>
+        <v>45153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10318,7 +10308,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10361,7 +10351,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10375,10 +10365,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45096</v>
+        <v>45905</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10390,13 +10380,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10439,7 +10424,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10453,10 +10438,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45109</v>
+        <v>44990</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10469,7 +10454,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10512,7 +10497,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10526,10 +10511,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45980</v>
+        <v>44993</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10541,8 +10526,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>18.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10585,7 +10575,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10599,10 +10589,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45195</v>
+        <v>45755</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,13 +10604,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10663,7 +10648,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10677,10 +10662,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45247</v>
+        <v>46023</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10693,7 +10678,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10736,7 +10721,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10746,14 +10731,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44734</v>
+        <v>45302</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10766,7 +10751,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10809,7 +10794,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10823,10 +10808,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44496</v>
+        <v>46037</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10839,7 +10824,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10882,7 +10867,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10896,10 +10881,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45981</v>
+        <v>45237</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,13 +10896,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>15.9</v>
+        <v>4.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10960,7 +10940,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10974,10 +10954,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45982</v>
+        <v>45195</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,8 +10969,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11033,7 +11018,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11047,10 +11032,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44999</v>
+        <v>44470</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,13 +11047,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11111,7 +11091,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11125,10 +11105,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44791</v>
+        <v>44651</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11140,8 +11120,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11184,7 +11169,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11198,10 +11183,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45194</v>
+        <v>45774</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11214,7 +11199,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11257,7 +11242,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11271,10 +11256,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44474</v>
+        <v>45053</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11287,7 +11272,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11330,7 +11315,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11344,10 +11329,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45135</v>
+        <v>45072</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11361,11 +11346,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11408,7 +11393,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11422,10 +11407,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45755</v>
+        <v>45194</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11438,7 +11423,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11481,7 +11466,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11495,10 +11480,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45236</v>
+        <v>44979</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11511,7 +11496,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11554,7 +11539,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11568,10 +11553,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46023</v>
+        <v>44565</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11584,7 +11569,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.4</v>
+        <v>13.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11627,7 +11612,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11641,10 +11626,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45995</v>
+        <v>45275</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11657,7 +11642,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11700,7 +11685,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11714,10 +11699,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45755</v>
+        <v>46077</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11730,7 +11715,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11773,7 +11758,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11783,14 +11768,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46002</v>
+        <v>46077</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11803,7 +11788,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11846,7 +11831,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11856,14 +11841,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45317</v>
+        <v>46069</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11876,7 +11861,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11919,7 +11904,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11933,10 +11918,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44830</v>
+        <v>44725</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11949,7 +11934,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11992,7 +11977,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12006,10 +11991,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45294</v>
+        <v>44791</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12022,7 +12007,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12065,7 +12050,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12079,10 +12064,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45210</v>
+        <v>44942</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12095,7 +12080,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.2</v>
+        <v>9.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12138,7 +12123,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12152,10 +12137,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45120</v>
+        <v>45076</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12167,13 +12152,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12216,7 +12196,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12230,10 +12210,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44678</v>
+        <v>45120</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12245,8 +12225,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12289,7 +12274,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12303,10 +12288,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46037</v>
+        <v>46181</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12319,7 +12304,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12362,7 +12347,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12376,10 +12361,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44608</v>
+        <v>46181</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12392,7 +12377,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12435,7 +12420,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12449,10 +12434,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45243</v>
+        <v>46181</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12465,7 +12450,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12508,7 +12493,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12522,10 +12507,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45191</v>
+        <v>46181</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12538,7 +12523,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12581,7 +12566,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12591,14 +12576,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44990</v>
+        <v>46181</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12611,7 +12596,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12654,7 +12639,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12668,10 +12653,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44910</v>
+        <v>46181</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12683,13 +12668,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12732,7 +12712,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12746,10 +12726,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46077</v>
+        <v>46181</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12762,7 +12742,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12805,7 +12785,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12819,10 +12799,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46077</v>
+        <v>44977</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12835,7 +12815,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12878,7 +12858,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12892,10 +12872,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45498</v>
+        <v>45096</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12907,8 +12887,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12951,7 +12936,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12965,10 +12950,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45576</v>
+        <v>45109</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12981,7 +12966,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.7</v>
+        <v>11.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13024,7 +13009,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13038,10 +13023,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44798</v>
+        <v>44888</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13054,7 +13039,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13097,7 +13082,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13107,14 +13092,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45343</v>
+        <v>45615</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13127,7 +13112,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13170,7 +13155,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13180,14 +13165,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46069</v>
+        <v>45448</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13200,7 +13185,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13243,7 +13228,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13257,10 +13242,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45072</v>
+        <v>45236</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13272,13 +13257,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13321,7 +13301,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13331,14 +13311,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44942</v>
+        <v>46121</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13351,7 +13331,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>9.1</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13394,7 +13374,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13408,10 +13388,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45153</v>
+        <v>45076</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13424,7 +13404,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13467,7 +13447,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13481,10 +13461,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44565</v>
+        <v>45321</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13497,7 +13477,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>13.4</v>
+        <v>3.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13540,7 +13520,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13554,10 +13534,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44573</v>
+        <v>45053</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13570,7 +13550,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13613,7 +13593,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13627,10 +13607,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45803</v>
+        <v>46135</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13643,7 +13623,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13686,7 +13666,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13700,10 +13680,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45733</v>
+        <v>45297</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13716,7 +13696,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13759,7 +13739,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13773,10 +13753,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44859</v>
+        <v>44830</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13789,7 +13769,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13832,7 +13812,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13846,10 +13826,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45013</v>
+        <v>46195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13862,7 +13842,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13905,7 +13885,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13915,14 +13895,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44685</v>
+        <v>45174</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13935,7 +13915,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13978,7 +13958,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13992,10 +13972,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45597</v>
+        <v>45552</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14008,7 +13988,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14051,7 +14031,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14065,10 +14045,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45076</v>
+        <v>45021</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14081,7 +14061,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14124,7 +14104,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14138,10 +14118,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45110</v>
+        <v>44917</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14154,7 +14134,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14197,7 +14177,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14211,10 +14191,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45175</v>
+        <v>45110</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14227,7 +14207,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14270,7 +14250,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14284,10 +14264,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45281</v>
+        <v>44671</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14300,7 +14280,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14343,7 +14323,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14357,10 +14337,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44830</v>
+        <v>45317</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14373,7 +14353,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14416,7 +14396,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14426,14 +14406,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46121</v>
+        <v>45069</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14446,7 +14426,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14489,7 +14469,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14503,10 +14483,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44917</v>
+        <v>46253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14519,7 +14499,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14562,7 +14542,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14576,10 +14556,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44938</v>
+        <v>45498</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14592,7 +14572,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14635,7 +14615,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14649,10 +14629,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44977</v>
+        <v>45764</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14664,8 +14644,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14708,7 +14693,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14722,10 +14707,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45278</v>
+        <v>45418</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14738,7 +14723,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14781,7 +14766,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14795,10 +14780,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44859</v>
+        <v>46213</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14810,8 +14795,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14854,7 +14844,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14864,14 +14854,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45636</v>
+        <v>46213</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14883,8 +14873,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14927,7 +14922,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14941,10 +14936,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46135</v>
+        <v>45440</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14957,7 +14952,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15000,7 +14995,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15014,10 +15009,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45880</v>
+        <v>45181</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15030,7 +15025,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15073,7 +15068,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15087,10 +15082,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46136</v>
+        <v>45051</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15103,7 +15098,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15146,7 +15141,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15160,10 +15155,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45184</v>
+        <v>45243</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15175,13 +15170,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15224,7 +15214,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15238,10 +15228,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44893</v>
+        <v>46265</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15254,7 +15244,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15297,7 +15287,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15311,10 +15301,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45053</v>
+        <v>46265</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15326,8 +15316,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15370,7 +15365,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15384,10 +15379,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45630</v>
+        <v>46265</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15399,8 +15394,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15443,7 +15443,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15457,10 +15457,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44742</v>
+        <v>46265</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15472,8 +15472,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15516,7 +15521,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15530,10 +15535,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45076</v>
+        <v>45281</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15546,7 +15551,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15589,7 +15594,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15603,10 +15608,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45582</v>
+        <v>44798</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15662,7 +15667,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15676,10 +15681,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45986</v>
+        <v>46253</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15692,7 +15697,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15735,7 +15740,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15749,10 +15754,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45285</v>
+        <v>45594</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15765,7 +15770,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15808,7 +15813,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15822,10 +15827,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46136</v>
+        <v>46231</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15838,7 +15843,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>10.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15881,7 +15886,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15895,10 +15900,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45297</v>
+        <v>45735</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15910,8 +15915,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15954,7 +15964,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15968,10 +15978,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44902</v>
+        <v>45735</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15983,8 +15993,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16027,7 +16042,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16041,10 +16056,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44943</v>
+        <v>46274</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16056,8 +16071,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16100,7 +16120,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16114,10 +16134,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45735</v>
+        <v>46275</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16135,7 +16155,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16178,7 +16198,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16192,10 +16212,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45735</v>
+        <v>46274</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16207,13 +16227,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16256,7 +16271,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16270,10 +16285,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46147</v>
+        <v>44573</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16286,7 +16301,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16329,7 +16344,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16339,14 +16354,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45923</v>
+        <v>45076</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16359,7 +16374,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16402,7 +16417,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16416,10 +16431,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46155</v>
+        <v>46274</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16431,8 +16446,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16475,7 +16495,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16489,10 +16509,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45905</v>
+        <v>44608</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16505,7 +16525,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16548,7 +16568,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16562,10 +16582,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46181</v>
+        <v>44594</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16578,7 +16598,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16621,7 +16641,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16635,10 +16655,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46181</v>
+        <v>44910</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16650,8 +16670,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16694,7 +16719,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16708,10 +16733,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46181</v>
+        <v>45630</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16767,7 +16792,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16781,10 +16806,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46181</v>
+        <v>44967</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16797,7 +16822,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16840,7 +16865,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16854,10 +16879,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46181</v>
+        <v>45135</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16869,8 +16894,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16913,7 +16943,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16927,10 +16957,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46181</v>
+        <v>44496</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16943,7 +16973,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16986,7 +17016,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17000,10 +17030,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46181</v>
+        <v>44937</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17016,7 +17046,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17059,7 +17089,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17073,10 +17103,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46195</v>
+        <v>44938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17089,7 +17119,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17132,7 +17162,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17146,10 +17176,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46253</v>
+        <v>44744</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17162,7 +17192,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17205,7 +17235,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17219,10 +17249,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46213</v>
+        <v>45740</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17236,11 +17266,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17283,7 +17313,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17293,14 +17323,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46213</v>
+        <v>45749</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17312,13 +17342,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>0.3</v>
+        <v>6.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17361,7 +17386,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17375,10 +17400,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46265</v>
+        <v>45226</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17391,7 +17416,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17434,7 +17459,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17448,10 +17473,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46265</v>
+        <v>45755</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17463,13 +17488,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17512,7 +17532,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17526,10 +17546,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46265</v>
+        <v>45576</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17541,13 +17561,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17590,7 +17605,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17604,10 +17619,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46265</v>
+        <v>45598</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17619,13 +17634,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17668,7 +17678,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17678,14 +17688,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46253</v>
+        <v>45594</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17697,8 +17707,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17741,7 +17756,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17755,10 +17770,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46231</v>
+        <v>45576</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17771,7 +17786,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17814,7 +17829,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17828,10 +17843,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46274</v>
+        <v>45817</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17844,7 +17859,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17887,7 +17902,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17901,10 +17916,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46274</v>
+        <v>45803</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17916,13 +17931,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17965,7 +17975,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17979,10 +17989,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46274</v>
+        <v>44685</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17994,13 +18004,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18043,7 +18048,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18057,10 +18062,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46275</v>
+        <v>45733</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18072,13 +18077,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18138,7 +18138,7 @@
         <v>45051</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45761</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45764</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45763</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45755</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE239"/>
+  <dimension ref="A1:AE240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58185-2025</t>
+          <t>A 57938-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45983</v>
+        <v>45982</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58185-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 57938-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45982</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7739-2022</t>
+          <t>A 67835-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44608</v>
+        <v>44525</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 67835-2021</t>
+          <t>A 7739-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44525</v>
+        <v>44608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44888</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44752</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44480</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44655</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45755</v>
+        <v>44725</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44642</v>
+        <v>44918</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44734</v>
+        <v>45321</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44830</v>
+        <v>44979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45735</v>
+        <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44910</v>
+        <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44977</v>
+        <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45483</v>
+        <v>45432</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45184</v>
+        <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4286,13 +4286,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4335,7 +4330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4349,10 +4344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45036</v>
+        <v>44594</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4365,7 +4360,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4408,7 +4403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4422,10 +4417,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45275</v>
+        <v>46023</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4438,7 +4433,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4481,7 +4476,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4491,14 +4486,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45191</v>
+        <v>45594</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4510,8 +4505,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44937</v>
+        <v>45529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44593</v>
+        <v>44903</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44594</v>
+        <v>44476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44496</v>
+        <v>45109</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>11.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45120</v>
+        <v>44496</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4875,13 +4875,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4924,7 +4919,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45013</v>
+        <v>45576</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4954,7 +4949,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>17.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4997,7 +4992,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44999</v>
+        <v>44475</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5026,13 +5021,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5075,7 +5065,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5085,14 +5075,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44623</v>
+        <v>46037</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5105,7 +5095,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5148,7 +5138,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5158,14 +5148,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45343</v>
+        <v>44511</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5178,7 +5168,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5221,7 +5211,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5235,10 +5225,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45076</v>
+        <v>45448</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5251,7 +5241,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5294,7 +5284,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5308,10 +5298,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45076</v>
+        <v>45905</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5324,7 +5314,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5367,7 +5357,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44476</v>
+        <v>45905</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5397,7 +5387,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5440,7 +5430,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5454,10 +5444,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44938</v>
+        <v>44617</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5469,8 +5459,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5513,7 +5508,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5523,14 +5518,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44903</v>
+        <v>44917</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5543,7 +5538,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5586,7 +5581,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5600,10 +5595,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44678</v>
+        <v>44917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5616,7 +5611,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5659,7 +5654,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,10 +5668,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45041</v>
+        <v>44910</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5689,7 +5684,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5732,7 +5727,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5746,10 +5741,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45576</v>
+        <v>45041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5762,7 +5757,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5805,7 +5800,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5819,10 +5814,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44918</v>
+        <v>46077</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5835,7 +5830,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5878,7 +5873,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5892,10 +5887,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45096</v>
+        <v>46077</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5907,13 +5902,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5956,7 +5946,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5970,10 +5960,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45432</v>
+        <v>44671</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5986,7 +5976,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6029,7 +6019,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6043,10 +6033,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45210</v>
+        <v>45056</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6059,7 +6049,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6102,7 +6092,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6116,10 +6106,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45754</v>
+        <v>44937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6131,13 +6121,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6180,7 +6165,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6194,10 +6179,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44511</v>
+        <v>45594</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6210,7 +6195,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6253,7 +6238,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6267,10 +6252,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45428</v>
+        <v>44938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6283,7 +6268,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6326,7 +6311,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6336,14 +6321,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45175</v>
+        <v>46069</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6356,7 +6341,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6399,7 +6384,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6413,10 +6398,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45236</v>
+        <v>45552</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6429,7 +6414,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6472,7 +6457,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6486,10 +6471,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45880</v>
+        <v>45959</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6502,7 +6487,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6545,7 +6530,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6555,14 +6540,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44742</v>
+        <v>46121</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6575,7 +6560,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6618,7 +6603,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6632,10 +6617,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45582</v>
+        <v>44496</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6648,7 +6633,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6691,7 +6676,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6705,10 +6690,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46136</v>
+        <v>44999</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6720,8 +6705,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6764,7 +6754,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6778,10 +6768,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45905</v>
+        <v>45980</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6794,7 +6784,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6837,7 +6827,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6851,10 +6841,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45905</v>
+        <v>45981</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6866,8 +6856,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>15.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6910,7 +6905,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6924,10 +6919,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44902</v>
+        <v>45982</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6940,7 +6935,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6983,7 +6978,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6997,10 +6992,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44594</v>
+        <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7013,7 +7008,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7056,7 +7051,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44496</v>
+        <v>45096</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7085,8 +7080,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7129,7 +7129,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45294</v>
+        <v>46136</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45529</v>
+        <v>45817</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45278</v>
+        <v>44474</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7348,7 +7348,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7362,10 +7362,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45636</v>
+        <v>45995</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44945</v>
+        <v>45483</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7494,7 +7494,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7504,14 +7504,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44943</v>
+        <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7567,7 +7567,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45986</v>
+        <v>45051</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7640,7 +7640,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7654,10 +7654,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46136</v>
+        <v>45582</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7713,7 +7713,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7727,10 +7727,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45297</v>
+        <v>45191</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7786,7 +7786,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44573</v>
+        <v>45986</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7859,7 +7859,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7873,10 +7873,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44917</v>
+        <v>45297</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7932,7 +7932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44917</v>
+        <v>45774</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8005,7 +8005,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45247</v>
+        <v>45440</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8078,7 +8078,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45285</v>
+        <v>44945</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8151,7 +8151,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45239</v>
+        <v>46136</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8224,7 +8224,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44565</v>
+        <v>44888</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8297,7 +8297,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45959</v>
+        <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44990</v>
+        <v>45236</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8443,7 +8443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8457,10 +8457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45597</v>
+        <v>45053</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8516,7 +8516,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44859</v>
+        <v>45735</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8589,7 +8589,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8603,10 +8603,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44918</v>
+        <v>45076</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8662,7 +8662,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45981</v>
+        <v>46147</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8691,13 +8691,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>15.9</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8740,7 +8735,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8754,10 +8749,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45980</v>
+        <v>44470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8770,7 +8765,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8813,7 +8808,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8827,10 +8822,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45306</v>
+        <v>45076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8843,7 +8838,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8886,7 +8881,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8900,10 +8895,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45982</v>
+        <v>44468</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8916,7 +8911,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8959,7 +8954,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8969,14 +8964,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44859</v>
+        <v>45923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8989,7 +8984,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9032,7 +9027,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9046,10 +9041,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44859</v>
+        <v>45615</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9062,7 +9057,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>8.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9105,7 +9100,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9119,10 +9114,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45630</v>
+        <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9135,7 +9130,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9178,7 +9173,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9192,10 +9187,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44859</v>
+        <v>46155</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9208,7 +9203,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9251,7 +9246,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9265,10 +9260,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44859</v>
+        <v>45905</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9281,7 +9276,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9324,7 +9319,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9338,10 +9333,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46147</v>
+        <v>45275</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9354,7 +9349,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9397,7 +9392,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9407,14 +9402,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45923</v>
+        <v>45120</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,8 +9421,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9470,7 +9470,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9484,10 +9484,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44474</v>
+        <v>45021</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9543,7 +9543,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45995</v>
+        <v>45803</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9630,10 +9630,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44475</v>
+        <v>45733</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45191</v>
+        <v>44685</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>44623</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9835,7 +9835,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46155</v>
+        <v>45275</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9908,7 +9908,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44468</v>
+        <v>44859</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9981,7 +9981,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45056</v>
+        <v>44937</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10054,7 +10054,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10068,10 +10068,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45109</v>
+        <v>44990</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10127,7 +10127,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10141,10 +10141,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44617</v>
+        <v>45428</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,13 +10156,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10205,7 +10200,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10219,10 +10214,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44893</v>
+        <v>46181</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10235,7 +10230,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10278,7 +10273,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10292,10 +10287,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45153</v>
+        <v>46181</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10308,7 +10303,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10351,7 +10346,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10365,10 +10360,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45905</v>
+        <v>46181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10381,7 +10376,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10424,7 +10419,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10438,10 +10433,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44990</v>
+        <v>46181</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10497,7 +10492,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10511,10 +10506,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44993</v>
+        <v>46181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,13 +10521,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>18.6</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10575,7 +10565,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10589,10 +10579,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45755</v>
+        <v>46181</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10605,7 +10595,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10648,7 +10638,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10662,10 +10652,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46023</v>
+        <v>46181</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10678,7 +10668,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10721,7 +10711,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10735,10 +10725,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45302</v>
+        <v>45174</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10751,7 +10741,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10794,7 +10784,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10808,10 +10798,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46037</v>
+        <v>44977</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10824,7 +10814,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10867,7 +10857,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10877,14 +10867,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45237</v>
+        <v>45302</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10897,7 +10887,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10940,7 +10930,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10954,10 +10944,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45195</v>
+        <v>45418</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10969,13 +10959,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11018,7 +11003,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11032,10 +11017,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44470</v>
+        <v>44993</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11047,8 +11032,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>4.7</v>
+        <v>18.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11091,7 +11081,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11105,10 +11095,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44651</v>
+        <v>44573</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11120,13 +11110,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11169,7 +11154,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11183,10 +11168,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45774</v>
+        <v>44967</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11199,7 +11184,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11242,7 +11227,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11256,10 +11241,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45053</v>
+        <v>45754</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11271,8 +11256,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11315,7 +11305,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11329,10 +11319,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45072</v>
+        <v>45764</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11350,7 +11340,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11393,7 +11383,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11407,10 +11397,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45194</v>
+        <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11423,7 +11413,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11466,7 +11456,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11480,10 +11470,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44979</v>
+        <v>44594</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11496,7 +11486,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11539,7 +11529,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11553,10 +11543,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44565</v>
+        <v>45630</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11569,7 +11559,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>13.4</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11612,7 +11602,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11626,10 +11616,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45275</v>
+        <v>45880</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11642,7 +11632,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11685,7 +11675,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11699,10 +11689,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46077</v>
+        <v>45036</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11715,7 +11705,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11758,7 +11748,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11772,10 +11762,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46077</v>
+        <v>44593</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11788,7 +11778,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11831,7 +11821,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11841,14 +11831,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46069</v>
+        <v>45181</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11861,7 +11851,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11904,7 +11894,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11918,10 +11908,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44725</v>
+        <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11933,8 +11923,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11977,7 +11972,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11991,10 +11986,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44791</v>
+        <v>45076</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12007,7 +12002,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12050,7 +12045,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12064,10 +12059,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44942</v>
+        <v>44594</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12080,7 +12075,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>9.1</v>
+        <v>3.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12123,7 +12118,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12137,10 +12132,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45076</v>
+        <v>44565</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12153,7 +12148,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12196,7 +12191,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12210,10 +12205,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45120</v>
+        <v>45069</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12225,13 +12220,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12274,7 +12264,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12288,10 +12278,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46181</v>
+        <v>45239</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12304,7 +12294,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12347,7 +12337,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12361,10 +12351,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46181</v>
+        <v>46253</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12377,7 +12367,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12420,7 +12410,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12434,10 +12424,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46181</v>
+        <v>44642</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12450,7 +12440,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12493,7 +12483,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12507,10 +12497,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46181</v>
+        <v>45096</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12522,8 +12512,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12566,7 +12561,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12580,10 +12575,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46181</v>
+        <v>46213</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12595,8 +12590,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12639,7 +12639,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46181</v>
+        <v>45109</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12712,7 +12712,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12722,14 +12722,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46181</v>
+        <v>46213</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12741,8 +12741,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12785,7 +12790,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12799,10 +12804,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44977</v>
+        <v>45195</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12814,8 +12819,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12858,7 +12868,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12872,10 +12882,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45096</v>
+        <v>45247</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12887,13 +12897,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12936,7 +12941,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12950,10 +12955,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45109</v>
+        <v>44734</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12966,7 +12971,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>11.8</v>
+        <v>4.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13009,7 +13014,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13023,10 +13028,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44888</v>
+        <v>44791</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13039,7 +13044,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13082,7 +13087,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13096,10 +13101,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45615</v>
+        <v>45194</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13112,7 +13117,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13155,7 +13160,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13169,10 +13174,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45448</v>
+        <v>45135</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13184,8 +13189,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13228,7 +13238,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13242,10 +13252,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45236</v>
+        <v>45755</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13258,7 +13268,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13301,7 +13311,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13311,14 +13321,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46121</v>
+        <v>45236</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13331,7 +13341,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13374,7 +13384,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13388,10 +13398,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45076</v>
+        <v>46265</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13404,7 +13414,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13447,7 +13457,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13461,10 +13471,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45321</v>
+        <v>46265</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13476,8 +13486,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13520,7 +13535,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13534,10 +13549,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45053</v>
+        <v>45755</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13550,7 +13565,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13593,7 +13608,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13607,10 +13622,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46135</v>
+        <v>46265</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13622,8 +13637,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13666,7 +13686,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13680,10 +13700,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45297</v>
+        <v>46265</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13695,8 +13715,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13739,7 +13764,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13753,10 +13778,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44830</v>
+        <v>45317</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13769,7 +13794,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13812,7 +13837,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13826,10 +13851,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46195</v>
+        <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13842,7 +13867,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13885,7 +13910,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13895,14 +13920,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45174</v>
+        <v>45294</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13915,7 +13940,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13958,7 +13983,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13972,10 +13997,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45552</v>
+        <v>45210</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13988,7 +14013,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14031,7 +14056,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14045,10 +14070,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45021</v>
+        <v>45120</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14060,8 +14085,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14104,7 +14134,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14118,10 +14148,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44917</v>
+        <v>44678</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14134,7 +14164,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14177,7 +14207,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14191,10 +14221,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45110</v>
+        <v>46253</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14207,7 +14237,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14250,7 +14280,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14264,10 +14294,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44671</v>
+        <v>46231</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14280,7 +14310,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14323,7 +14353,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14337,10 +14367,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45317</v>
+        <v>46274</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14353,7 +14383,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14396,7 +14426,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14410,10 +14440,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45069</v>
+        <v>46274</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14423,6 +14453,11 @@
       <c r="G184" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I184" t="n">
@@ -14469,7 +14504,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14483,10 +14518,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46253</v>
+        <v>46274</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14498,8 +14533,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14542,7 +14582,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14556,10 +14596,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45498</v>
+        <v>44608</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14572,7 +14612,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14615,7 +14655,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14629,10 +14669,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45764</v>
+        <v>46275</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14646,11 +14686,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14693,7 +14733,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14707,10 +14747,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45418</v>
+        <v>45243</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14723,7 +14763,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14766,7 +14806,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14780,10 +14820,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46213</v>
+        <v>45191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14795,13 +14835,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14844,7 +14879,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14858,10 +14893,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46213</v>
+        <v>44990</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14873,13 +14908,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14922,7 +14952,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14936,10 +14966,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45440</v>
+        <v>44910</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14951,8 +14981,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14995,7 +15030,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15009,10 +15044,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45181</v>
+        <v>45498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15025,7 +15060,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15068,7 +15103,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15082,10 +15117,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45051</v>
+        <v>45576</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15098,7 +15133,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15141,7 +15176,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15155,10 +15190,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45243</v>
+        <v>44798</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15171,7 +15206,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15214,7 +15249,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15224,14 +15259,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46265</v>
+        <v>45343</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15244,7 +15279,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15287,7 +15322,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15301,10 +15336,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46265</v>
+        <v>45072</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15322,7 +15357,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15365,7 +15400,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15379,10 +15414,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46265</v>
+        <v>44942</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15394,13 +15429,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>6</v>
+        <v>9.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15443,7 +15473,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15457,10 +15487,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46265</v>
+        <v>45153</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15472,13 +15502,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15521,7 +15546,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15535,10 +15560,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45281</v>
+        <v>44565</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15551,7 +15576,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>13.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15594,7 +15619,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15608,10 +15633,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44798</v>
+        <v>44573</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15624,7 +15649,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15667,7 +15692,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 39830-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15677,14 +15702,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46253</v>
+        <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15697,7 +15722,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15740,7 +15765,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15754,10 +15779,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45594</v>
+        <v>44859</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15770,7 +15795,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15813,7 +15838,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15827,10 +15852,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46231</v>
+        <v>45013</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15843,7 +15868,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>10.1</v>
+        <v>3.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15886,7 +15911,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15900,10 +15925,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45735</v>
+        <v>45597</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15915,13 +15940,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15964,7 +15984,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15978,10 +15998,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45735</v>
+        <v>45076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15993,13 +16013,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16042,7 +16057,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16056,10 +16071,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46274</v>
+        <v>45110</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16071,13 +16086,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16120,7 +16130,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16134,10 +16144,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46275</v>
+        <v>45175</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16149,13 +16159,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16198,7 +16203,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16212,10 +16217,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46274</v>
+        <v>45281</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16228,7 +16233,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16271,7 +16276,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16285,10 +16290,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44573</v>
+        <v>44830</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16301,7 +16306,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16344,7 +16349,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16358,10 +16363,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45076</v>
+        <v>44917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16374,7 +16379,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16417,7 +16422,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16431,10 +16436,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46274</v>
+        <v>44938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16446,13 +16451,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16495,7 +16495,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16509,10 +16509,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44608</v>
+        <v>44977</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16568,7 +16568,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16582,10 +16582,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44594</v>
+        <v>45278</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16641,7 +16641,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16655,10 +16655,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44910</v>
+        <v>44859</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16670,13 +16670,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16719,7 +16714,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16733,10 +16728,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45630</v>
+        <v>45636</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16749,7 +16744,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16792,7 +16787,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16806,10 +16801,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44967</v>
+        <v>45184</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16821,8 +16816,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16865,7 +16865,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16879,10 +16879,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45135</v>
+        <v>44893</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16894,13 +16894,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16943,7 +16938,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16957,10 +16952,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44496</v>
+        <v>45053</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16973,7 +16968,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17016,7 +17011,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17030,10 +17025,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44937</v>
+        <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17046,7 +17041,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17089,7 +17084,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17103,10 +17098,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44938</v>
+        <v>44742</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17119,7 +17114,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17162,7 +17157,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17176,10 +17171,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44744</v>
+        <v>45076</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17192,7 +17187,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17235,7 +17230,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17249,10 +17244,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45740</v>
+        <v>45285</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17264,13 +17259,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17313,7 +17303,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17327,10 +17317,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45749</v>
+        <v>45297</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17343,7 +17333,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17386,7 +17376,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17400,10 +17390,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45226</v>
+        <v>44902</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17416,7 +17406,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17459,7 +17449,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17473,10 +17463,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45755</v>
+        <v>44943</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17489,7 +17479,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17532,7 +17522,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 13185-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17546,10 +17536,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45576</v>
+        <v>45735</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17561,8 +17551,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17605,7 +17600,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 13192-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17619,10 +17614,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45598</v>
+        <v>45735</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17634,8 +17629,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17678,7 +17678,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17688,14 +17688,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45594</v>
+        <v>45749</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17707,13 +17707,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17756,7 +17751,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17770,10 +17765,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45576</v>
+        <v>45740</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17785,8 +17780,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>17.1</v>
+        <v>2.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17829,7 +17829,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45817</v>
+        <v>44744</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17902,7 +17902,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17916,10 +17916,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45803</v>
+        <v>45226</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17989,10 +17989,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44685</v>
+        <v>45576</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45733</v>
+        <v>45755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18121,24 +18121,24 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 1502-2023</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45051</v>
+        <v>45598</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18150,13 +18150,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18199,7 +18194,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 1214-2025</t>
+          <t>S 1502-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18213,10 +18208,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45761</v>
+        <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18230,11 +18225,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18277,7 +18272,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 1213-2025</t>
+          <t>S 1214-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18294,7 +18289,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18312,7 +18307,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18355,7 +18350,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 1266-2025</t>
+          <t>S 1213-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18369,10 +18364,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45764</v>
+        <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18390,7 +18385,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18433,153 +18428,231 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
+          <t>S 1266-2025</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="n">
+        <v>45764</v>
+      </c>
+      <c r="E238" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>0</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="n">
+        <v>0</v>
+      </c>
+      <c r="T238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="n">
+        <v>0</v>
+      </c>
+      <c r="V238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239" ht="15" customHeight="1">
+      <c r="A239" t="inlineStr">
+        <is>
           <t>S 1260-2025</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D238" s="1" t="n">
+      <c r="D239" s="1" t="n">
         <v>45763</v>
       </c>
-      <c r="E238" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
+      <c r="E239" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I238" t="n">
+      <c r="I239" t="n">
         <v>1.3</v>
       </c>
-      <c r="J238" t="n">
-        <v>0</v>
-      </c>
-      <c r="K238" t="n">
-        <v>0</v>
-      </c>
-      <c r="L238" t="n">
-        <v>0</v>
-      </c>
-      <c r="M238" t="n">
-        <v>0</v>
-      </c>
-      <c r="N238" t="n">
-        <v>0</v>
-      </c>
-      <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="P238" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0</v>
-      </c>
-      <c r="S238" t="n">
-        <v>0</v>
-      </c>
-      <c r="T238" t="n">
-        <v>0</v>
-      </c>
-      <c r="U238" t="n">
-        <v>0</v>
-      </c>
-      <c r="V238" s="2" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>0</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="n">
+        <v>0</v>
+      </c>
+      <c r="T239" t="n">
+        <v>0</v>
+      </c>
+      <c r="U239" t="n">
+        <v>0</v>
+      </c>
+      <c r="V239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>S 1137-2025</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D239" s="1" t="n">
+      <c r="D240" s="1" t="n">
         <v>45755</v>
       </c>
-      <c r="E239" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I239" t="n">
+      <c r="E240" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
         <v>10.6</v>
       </c>
-      <c r="J239" t="n">
-        <v>0</v>
-      </c>
-      <c r="K239" t="n">
-        <v>0</v>
-      </c>
-      <c r="L239" t="n">
-        <v>0</v>
-      </c>
-      <c r="M239" t="n">
-        <v>0</v>
-      </c>
-      <c r="N239" t="n">
-        <v>0</v>
-      </c>
-      <c r="O239" t="n">
-        <v>0</v>
-      </c>
-      <c r="P239" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0</v>
-      </c>
-      <c r="S239" t="n">
-        <v>0</v>
-      </c>
-      <c r="T239" t="n">
-        <v>0</v>
-      </c>
-      <c r="U239" t="n">
-        <v>0</v>
-      </c>
-      <c r="V239" s="2" t="inlineStr"/>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
+      <c r="V240" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45982</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45983</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44525</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44888</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44752</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44480</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44655</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44725</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44918</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45321</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45432</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44594</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46023</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45594</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44903</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45109</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>44496</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45576</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44475</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46037</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44511</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45448</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45905</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45905</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44617</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44917</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44910</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>46077</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>46077</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44671</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45056</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45594</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46069</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45552</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45959</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>46121</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44496</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44999</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45980</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45981</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45982</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>45096</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>46136</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45817</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>44474</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45995</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45483</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45051</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45582</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45191</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45986</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45297</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45774</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45440</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44945</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>46136</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44888</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45236</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45053</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45735</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45076</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>46147</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44468</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45615</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>46155</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45905</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45275</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45120</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45021</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45803</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45733</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44685</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>44623</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45275</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>44859</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44937</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>44990</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45428</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>46181</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46181</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>46181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>46181</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>46181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>46181</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>46181</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45174</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>44977</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45302</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45418</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44993</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44573</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44967</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>45754</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45764</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44594</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45630</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45880</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45036</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>44593</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45181</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45076</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44594</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44565</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45069</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45239</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>46253</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44642</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45096</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>46213</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45109</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>46213</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45195</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45247</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44734</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44791</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>45194</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45135</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45755</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45236</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>46265</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>46265</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45755</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>46265</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>46265</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45317</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>45294</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45210</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45120</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44678</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>46253</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>46231</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>46274</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>46274</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>46274</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44608</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>46275</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45243</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>44990</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44910</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45576</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44798</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45343</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45072</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>44942</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45153</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>44565</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44573</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>44859</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45013</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45597</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45110</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45175</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45281</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>44830</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>44917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44977</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45278</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>44859</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45636</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45184</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44893</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45053</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44742</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45076</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45285</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45297</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>44902</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>44943</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45735</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45735</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45749</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45740</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44744</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45226</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45576</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45598</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45982</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45983</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44525</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44888</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44752</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44480</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44655</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44725</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44918</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45321</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>44979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45432</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45306</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44594</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46023</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45594</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44903</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45109</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>44496</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45576</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44475</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46037</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44511</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45448</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45905</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45905</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44617</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44917</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44910</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>46077</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>46077</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44671</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45056</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45594</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46069</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45552</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45959</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>46121</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44496</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44999</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45980</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45981</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45982</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>45096</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>46136</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45817</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>44474</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45995</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45483</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45051</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45582</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45191</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45986</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45297</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45774</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45440</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44945</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>46136</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44888</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45236</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45053</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45735</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45076</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>46147</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44468</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45615</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>46155</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45905</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45275</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45120</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45021</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45803</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45733</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44685</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>44623</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45275</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>44859</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44937</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>44990</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45428</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>46181</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46181</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>46181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>46181</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>46181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>46181</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>46181</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45174</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>44977</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45302</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45418</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44993</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44573</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44967</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>45754</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45764</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44594</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45630</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45880</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45036</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>44593</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45181</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45076</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44594</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44565</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45069</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45239</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>46253</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44642</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45096</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>46213</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45109</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>46213</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45195</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45247</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44734</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44791</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>45194</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45135</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45755</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45236</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>46265</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>46265</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45755</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>46265</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>46265</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>45317</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>45294</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45210</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45120</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44678</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>46253</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>46231</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>46274</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>46274</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>46274</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44608</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>46275</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45243</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>44990</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44910</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45576</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44798</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45343</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45072</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>44942</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45153</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>44565</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44573</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>44859</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45013</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45597</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45110</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45175</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45281</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>44830</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>44917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44977</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45278</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>44859</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45636</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45184</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44893</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45053</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44742</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45076</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45285</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45297</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>44902</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>44943</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45735</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45735</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45749</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45740</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44744</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45226</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45576</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45598</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE240"/>
+  <dimension ref="A1:AE238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57938-2025</t>
+          <t>A 58185-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 57938-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58185-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 67835-2021</t>
+          <t>A 7739-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44525</v>
+        <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7739-2022</t>
+          <t>A 67835-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44608</v>
+        <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44888</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44752</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44480</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44655</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44725</v>
+        <v>44734</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44918</v>
+        <v>45755</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45321</v>
+        <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44979</v>
+        <v>44830</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44859</v>
+        <v>45735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44859</v>
+        <v>44910</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44496</v>
+        <v>44977</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45432</v>
+        <v>45483</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45306</v>
+        <v>45184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4286,8 +4286,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4330,7 +4335,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4344,10 +4349,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44594</v>
+        <v>45036</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4360,7 +4365,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4403,7 +4408,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46023</v>
+        <v>45740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4432,8 +4437,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4476,7 +4486,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4486,14 +4496,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45594</v>
+        <v>45749</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4505,13 +4515,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4554,7 +4559,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,10 +4573,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45529</v>
+        <v>45226</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4584,7 +4589,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4627,7 +4632,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4641,10 +4646,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44903</v>
+        <v>46002</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4657,7 +4662,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4700,7 +4705,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4714,10 +4719,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44476</v>
+        <v>45755</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4730,7 +4735,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4773,7 +4778,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45109</v>
+        <v>44496</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4803,7 +4808,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>11.8</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4846,7 +4851,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4860,10 +4865,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44496</v>
+        <v>45013</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4876,7 +4881,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4919,7 +4924,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4929,14 +4934,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45576</v>
+        <v>45343</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4949,7 +4954,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>17.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4992,7 +4997,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44475</v>
+        <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5022,7 +5027,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5065,7 +5070,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46037</v>
+        <v>45275</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5095,7 +5100,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44511</v>
+        <v>45598</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5211,7 +5216,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5221,14 +5226,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45448</v>
+        <v>45594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5240,8 +5245,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5284,7 +5294,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5298,10 +5308,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45905</v>
+        <v>44937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5314,7 +5324,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5357,7 +5367,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5371,10 +5381,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45905</v>
+        <v>45576</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5387,7 +5397,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>17.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5430,7 +5440,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5444,10 +5454,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44617</v>
+        <v>45191</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5459,13 +5469,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5508,7 +5513,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5522,10 +5527,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44917</v>
+        <v>44593</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5538,7 +5543,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5581,7 +5586,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5595,10 +5600,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44917</v>
+        <v>44594</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5611,7 +5616,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5654,7 +5659,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5668,10 +5673,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44910</v>
+        <v>45905</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5684,7 +5689,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5727,7 +5732,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5741,10 +5746,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45041</v>
+        <v>45905</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5757,7 +5762,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5800,7 +5805,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5814,10 +5819,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46077</v>
+        <v>45120</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5829,8 +5834,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5873,7 +5883,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5887,10 +5897,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46077</v>
+        <v>44999</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5902,8 +5912,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5946,7 +5961,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5960,10 +5975,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44671</v>
+        <v>45817</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5976,7 +5991,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6019,7 +6034,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6033,10 +6048,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45056</v>
+        <v>45076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6049,7 +6064,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6092,7 +6107,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6106,10 +6121,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44937</v>
+        <v>45076</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6122,7 +6137,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6165,7 +6180,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6175,14 +6190,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45594</v>
+        <v>44623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6195,7 +6210,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6238,7 +6253,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6252,10 +6267,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44938</v>
+        <v>44476</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6268,7 +6283,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6311,7 +6326,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6321,14 +6336,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46069</v>
+        <v>44938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6341,7 +6356,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6384,7 +6399,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6394,14 +6409,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45552</v>
+        <v>44903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6414,7 +6429,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6457,7 +6472,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6471,10 +6486,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45959</v>
+        <v>44678</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6487,7 +6502,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6530,7 +6545,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6540,14 +6555,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46121</v>
+        <v>45041</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6560,7 +6575,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6603,7 +6618,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6617,10 +6632,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44496</v>
+        <v>44918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6633,7 +6648,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6676,7 +6691,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6690,10 +6705,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44999</v>
+        <v>45803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6705,13 +6720,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6754,7 +6764,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6768,10 +6778,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45980</v>
+        <v>45576</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6784,7 +6794,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6827,7 +6837,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6841,10 +6851,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45981</v>
+        <v>44685</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6856,13 +6866,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>15.9</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6905,7 +6910,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6919,10 +6924,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45982</v>
+        <v>45733</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6935,7 +6940,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6978,7 +6983,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6992,10 +6997,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46135</v>
+        <v>46023</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7008,7 +7013,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7068,7 +7073,7 @@
         <v>45096</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7129,7 +7134,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7143,10 +7148,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46136</v>
+        <v>45210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7159,7 +7164,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7202,7 +7207,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7216,10 +7221,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45817</v>
+        <v>45432</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7232,7 +7237,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7275,7 +7280,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7289,10 +7294,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44474</v>
+        <v>45754</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7304,8 +7309,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7348,7 +7358,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7362,10 +7372,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45995</v>
+        <v>44511</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7378,7 +7388,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7421,7 +7431,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7435,10 +7445,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45483</v>
+        <v>45236</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7451,7 +7461,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7494,7 +7504,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7504,14 +7514,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46002</v>
+        <v>45959</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7524,7 +7534,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7567,7 +7577,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7581,10 +7591,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45051</v>
+        <v>45880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7597,7 +7607,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7640,7 +7650,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7654,10 +7664,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45582</v>
+        <v>45428</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7670,7 +7680,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7713,7 +7723,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7727,10 +7737,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45191</v>
+        <v>45175</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7743,7 +7753,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7786,7 +7796,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7800,10 +7810,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45986</v>
+        <v>46037</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7859,7 +7869,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7873,10 +7883,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45297</v>
+        <v>45981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7888,8 +7898,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>15.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7932,7 +7947,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7946,10 +7961,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45774</v>
+        <v>44594</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7962,7 +7977,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8005,7 +8020,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8019,10 +8034,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45440</v>
+        <v>45980</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8035,7 +8050,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8078,7 +8093,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8092,10 +8107,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44945</v>
+        <v>44496</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8108,7 +8123,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8151,7 +8166,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8165,10 +8180,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46136</v>
+        <v>45982</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8181,7 +8196,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8224,7 +8239,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8238,10 +8253,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44888</v>
+        <v>44474</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8254,7 +8269,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8297,7 +8312,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8311,10 +8326,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45237</v>
+        <v>44742</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8327,7 +8342,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8370,7 +8385,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8384,10 +8399,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45236</v>
+        <v>45995</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8400,7 +8415,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8443,7 +8458,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8457,10 +8472,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45053</v>
+        <v>44902</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8473,7 +8488,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8516,7 +8531,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8530,10 +8545,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45735</v>
+        <v>45294</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8546,7 +8561,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8589,7 +8604,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8603,10 +8618,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45076</v>
+        <v>45529</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8619,7 +8634,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8662,7 +8677,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8676,10 +8691,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46147</v>
+        <v>45278</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8692,7 +8707,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8735,7 +8750,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8749,10 +8764,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44470</v>
+        <v>46077</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8765,7 +8780,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8808,7 +8823,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8822,10 +8837,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45076</v>
+        <v>46077</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8838,7 +8853,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8881,7 +8896,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8895,10 +8910,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44468</v>
+        <v>45636</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8911,7 +8926,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8954,7 +8969,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8964,14 +8979,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45923</v>
+        <v>44945</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8984,7 +8999,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9027,7 +9042,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9041,10 +9056,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45615</v>
+        <v>44943</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9057,7 +9072,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>8.9</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9100,7 +9115,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9110,14 +9125,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44918</v>
+        <v>46069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9130,7 +9145,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9173,7 +9188,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9187,10 +9202,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46155</v>
+        <v>45297</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9203,7 +9218,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9246,7 +9261,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9260,10 +9275,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45905</v>
+        <v>44573</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9276,7 +9291,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9319,7 +9334,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9333,10 +9348,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45275</v>
+        <v>44917</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9349,7 +9364,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9392,7 +9407,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9406,10 +9421,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45120</v>
+        <v>44917</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,13 +9436,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9470,7 +9480,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9484,10 +9494,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45021</v>
+        <v>45247</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9500,7 +9510,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9543,7 +9553,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9557,10 +9567,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45803</v>
+        <v>45285</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9573,7 +9583,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9616,7 +9626,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9630,10 +9640,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45733</v>
+        <v>45239</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9646,7 +9656,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9689,7 +9699,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9703,10 +9713,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44685</v>
+        <v>44565</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9719,7 +9729,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9762,7 +9772,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9776,10 +9786,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44623</v>
+        <v>44990</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9835,7 +9845,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9845,14 +9855,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45275</v>
+        <v>46121</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9865,7 +9875,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9908,7 +9918,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9922,10 +9932,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44859</v>
+        <v>45597</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9938,7 +9948,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9981,7 +9991,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9995,10 +10005,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44937</v>
+        <v>44859</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10011,7 +10021,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10054,7 +10064,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10068,10 +10078,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44990</v>
+        <v>44918</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10084,7 +10094,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10127,7 +10137,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10141,10 +10151,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45428</v>
+        <v>45306</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10157,7 +10167,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10200,7 +10210,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10214,10 +10224,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46181</v>
+        <v>46135</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10230,7 +10240,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10273,7 +10283,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10287,10 +10297,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46181</v>
+        <v>44859</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10303,7 +10313,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10346,7 +10356,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10360,10 +10370,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46181</v>
+        <v>44859</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10376,7 +10386,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10419,7 +10429,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10433,10 +10443,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46181</v>
+        <v>45630</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10449,7 +10459,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10492,7 +10502,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10506,10 +10516,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46181</v>
+        <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10522,7 +10532,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10565,7 +10575,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10579,10 +10589,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46181</v>
+        <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10595,7 +10605,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10638,7 +10648,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10652,10 +10662,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46181</v>
+        <v>44475</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10668,7 +10678,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10711,7 +10721,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10721,14 +10731,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45174</v>
+        <v>45191</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10741,7 +10751,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10784,7 +10794,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10798,10 +10808,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44977</v>
+        <v>45582</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10814,7 +10824,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10857,7 +10867,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10867,14 +10877,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45302</v>
+        <v>46136</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10887,7 +10897,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10930,7 +10940,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 53863-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10944,10 +10954,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45418</v>
+        <v>44468</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10960,7 +10970,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11003,7 +11013,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11017,10 +11027,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44993</v>
+        <v>45056</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11032,13 +11042,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>18.6</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11081,7 +11086,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11095,10 +11100,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44573</v>
+        <v>45986</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11111,7 +11116,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11154,7 +11159,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11168,10 +11173,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44967</v>
+        <v>45109</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11184,7 +11189,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11227,7 +11232,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11241,10 +11246,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45754</v>
+        <v>46136</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11256,13 +11261,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11305,7 +11305,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11319,10 +11319,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45764</v>
+        <v>44617</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11336,11 +11336,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46195</v>
+        <v>44893</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11456,7 +11456,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44594</v>
+        <v>45153</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11529,7 +11529,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45630</v>
+        <v>44990</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11616,10 +11616,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45880</v>
+        <v>44993</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11631,8 +11631,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>2.6</v>
+        <v>18.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11675,7 +11680,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11689,10 +11694,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45036</v>
+        <v>45755</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11705,7 +11710,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11748,7 +11753,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11758,14 +11763,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44593</v>
+        <v>45302</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11778,7 +11783,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11821,7 +11826,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11835,10 +11840,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45181</v>
+        <v>45237</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11851,7 +11856,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11894,7 +11899,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11908,10 +11913,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44651</v>
+        <v>45195</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11925,11 +11930,11 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11972,7 +11977,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11986,10 +11991,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45076</v>
+        <v>44470</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12002,7 +12007,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12045,7 +12050,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12059,10 +12064,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44594</v>
+        <v>46147</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12075,7 +12080,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12118,7 +12123,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12132,10 +12137,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44565</v>
+        <v>44651</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12147,8 +12152,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12191,7 +12201,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12205,10 +12215,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45069</v>
+        <v>45774</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12221,7 +12231,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12264,7 +12274,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12274,14 +12284,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45239</v>
+        <v>45923</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12294,7 +12304,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12337,7 +12347,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12351,10 +12361,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46253</v>
+        <v>45053</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12367,7 +12377,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12410,7 +12420,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12424,10 +12434,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44642</v>
+        <v>45072</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12439,8 +12449,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12483,7 +12498,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12497,10 +12512,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45096</v>
+        <v>46155</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12512,13 +12527,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12561,7 +12571,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12575,10 +12585,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46213</v>
+        <v>45194</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12590,13 +12600,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12639,7 +12644,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12653,10 +12658,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45109</v>
+        <v>44979</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12669,7 +12674,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12712,7 +12717,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12722,14 +12727,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46213</v>
+        <v>45905</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12741,13 +12746,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12790,7 +12790,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12804,10 +12804,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45195</v>
+        <v>44565</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12819,13 +12819,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>13.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12868,7 +12863,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12882,10 +12877,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45247</v>
+        <v>45275</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12898,7 +12893,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12941,7 +12936,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12955,10 +12950,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44734</v>
+        <v>44725</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12971,7 +12966,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13031,7 +13026,7 @@
         <v>44791</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13087,7 +13082,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13101,10 +13096,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45194</v>
+        <v>44942</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13117,7 +13112,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.8</v>
+        <v>9.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13160,7 +13155,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13174,10 +13169,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45135</v>
+        <v>45076</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13189,13 +13184,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13238,7 +13228,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13252,10 +13242,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45755</v>
+        <v>45120</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13267,8 +13257,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13311,7 +13306,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13325,10 +13320,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45236</v>
+        <v>44977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13341,7 +13336,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13384,7 +13379,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13398,10 +13393,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46265</v>
+        <v>45096</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13411,6 +13406,11 @@
       <c r="G170" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -13457,7 +13457,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46265</v>
+        <v>45109</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13486,13 +13486,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>2.7</v>
+        <v>11.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13535,7 +13530,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13549,10 +13544,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45755</v>
+        <v>44888</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13565,7 +13560,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13608,7 +13603,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13622,10 +13617,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46265</v>
+        <v>45615</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13637,13 +13632,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>8.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13686,7 +13676,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13700,10 +13690,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46265</v>
+        <v>45448</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13715,13 +13705,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13764,7 +13749,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13778,10 +13763,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45317</v>
+        <v>45236</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13794,7 +13779,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13837,7 +13822,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13851,10 +13836,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44830</v>
+        <v>45076</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13867,7 +13852,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13910,7 +13895,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13924,10 +13909,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45294</v>
+        <v>45321</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13940,7 +13925,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13983,7 +13968,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13997,10 +13982,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45210</v>
+        <v>46181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14013,7 +13998,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14056,7 +14041,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14070,10 +14055,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45120</v>
+        <v>46181</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14085,13 +14070,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14134,7 +14114,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14148,10 +14128,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44678</v>
+        <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14164,7 +14144,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14207,7 +14187,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14221,10 +14201,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46253</v>
+        <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14237,7 +14217,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14280,7 +14260,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14294,10 +14274,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46231</v>
+        <v>46181</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14310,7 +14290,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>10.1</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14353,7 +14333,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14367,10 +14347,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46274</v>
+        <v>46181</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14383,7 +14363,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14426,7 +14406,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14440,10 +14420,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46274</v>
+        <v>46181</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14455,13 +14435,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14504,7 +14479,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 37329-2026</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14518,10 +14493,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46274</v>
+        <v>45053</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14533,13 +14508,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14582,7 +14552,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14596,10 +14566,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44608</v>
+        <v>45297</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14612,7 +14582,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14655,7 +14625,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37325-2026</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14669,10 +14639,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46275</v>
+        <v>44830</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14684,13 +14654,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14733,7 +14698,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14743,14 +14708,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45243</v>
+        <v>45174</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14763,7 +14728,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14806,7 +14771,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14820,10 +14785,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45191</v>
+        <v>45552</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14836,7 +14801,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14879,7 +14844,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14889,14 +14854,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44990</v>
+        <v>45021</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14909,7 +14874,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14952,7 +14917,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14966,10 +14931,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44910</v>
+        <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14981,13 +14946,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15030,7 +14990,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15044,10 +15004,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45498</v>
+        <v>44917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15060,7 +15020,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15103,7 +15063,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15117,10 +15077,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45576</v>
+        <v>45110</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15133,7 +15093,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15176,7 +15136,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15190,10 +15150,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44798</v>
+        <v>44671</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15206,7 +15166,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15249,7 +15209,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15259,14 +15219,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45343</v>
+        <v>45317</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15279,7 +15239,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15322,7 +15282,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15336,10 +15296,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45072</v>
+        <v>45069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15351,13 +15311,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15400,7 +15355,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15414,10 +15369,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44942</v>
+        <v>45498</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15430,7 +15385,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>9.1</v>
+        <v>2.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15473,7 +15428,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15487,10 +15442,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45153</v>
+        <v>45764</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15502,8 +15457,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15546,7 +15506,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15560,10 +15520,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44565</v>
+        <v>45418</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15576,7 +15536,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>13.4</v>
+        <v>5.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15619,7 +15579,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15633,10 +15593,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44573</v>
+        <v>46253</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15649,7 +15609,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15692,7 +15652,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 39830-2026</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15702,14 +15662,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46290</v>
+        <v>45440</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15722,7 +15682,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15765,7 +15725,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15779,10 +15739,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44859</v>
+        <v>46213</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15794,8 +15754,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15838,7 +15803,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15852,10 +15817,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45013</v>
+        <v>45181</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15868,7 +15833,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15911,7 +15876,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15925,10 +15890,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45597</v>
+        <v>45051</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15941,7 +15906,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15984,7 +15949,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15994,14 +15959,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45076</v>
+        <v>46213</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16013,8 +15978,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16057,7 +16027,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16071,10 +16041,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45110</v>
+        <v>45243</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16087,7 +16057,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16130,7 +16100,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16144,10 +16114,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45175</v>
+        <v>46265</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16160,7 +16130,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16203,7 +16173,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16217,10 +16187,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45281</v>
+        <v>46265</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16232,8 +16202,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16276,7 +16251,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16290,10 +16265,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44830</v>
+        <v>45281</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16306,7 +16281,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16349,7 +16324,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16363,10 +16338,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44917</v>
+        <v>46265</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16378,8 +16353,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16422,7 +16402,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16436,10 +16416,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44938</v>
+        <v>46265</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16451,8 +16431,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16495,7 +16480,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16509,10 +16494,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44977</v>
+        <v>44798</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16525,7 +16510,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16568,7 +16553,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16582,10 +16567,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45278</v>
+        <v>45594</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16598,7 +16583,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16641,7 +16626,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16655,10 +16640,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44859</v>
+        <v>46253</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16671,7 +16656,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16714,7 +16699,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16728,10 +16713,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45636</v>
+        <v>44573</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16744,7 +16729,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16787,7 +16772,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16801,10 +16786,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45184</v>
+        <v>45076</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16816,13 +16801,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16865,7 +16845,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16879,10 +16859,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44893</v>
+        <v>46231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16895,7 +16875,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>10.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16938,7 +16918,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 37329-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16952,10 +16932,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45053</v>
+        <v>46274</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16967,8 +16947,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17011,7 +16996,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 37325-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17025,10 +17010,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45630</v>
+        <v>46275</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17040,8 +17025,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17084,7 +17074,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17098,10 +17088,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44742</v>
+        <v>46274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17114,7 +17104,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17157,7 +17147,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17171,10 +17161,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45076</v>
+        <v>44608</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17187,7 +17177,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17230,7 +17220,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17244,10 +17234,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45285</v>
+        <v>46274</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17259,8 +17249,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17303,7 +17298,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17317,10 +17312,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45297</v>
+        <v>44594</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17333,7 +17328,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17376,7 +17371,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17390,10 +17385,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44902</v>
+        <v>44910</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17405,8 +17400,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17449,7 +17449,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17463,10 +17463,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44943</v>
+        <v>45630</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17522,7 +17522,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 13185-2025</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17536,10 +17536,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45735</v>
+        <v>44967</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17551,13 +17551,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17600,7 +17595,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 13192-2025</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17614,10 +17609,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45735</v>
+        <v>45135</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17631,11 +17626,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17678,7 +17673,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17692,10 +17687,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45749</v>
+        <v>44496</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17708,7 +17703,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17751,7 +17746,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17765,10 +17760,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45740</v>
+        <v>44937</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17780,13 +17775,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17829,7 +17819,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17843,10 +17833,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44744</v>
+        <v>44938</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17859,7 +17849,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17902,7 +17892,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17916,10 +17906,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45226</v>
+        <v>44744</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17932,7 +17922,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17975,7 +17965,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 39830-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17985,14 +17975,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45576</v>
+        <v>46290</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18005,7 +17995,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18048,24 +18038,24 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>S 1502-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45755</v>
+        <v>45051</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18077,8 +18067,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18121,24 +18116,24 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>S 1214-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45598</v>
+        <v>45761</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18150,8 +18145,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 1502-2023</t>
+          <t>S 1213-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45051</v>
+        <v>45761</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18225,11 +18225,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 1214-2025</t>
+          <t>S 1266-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18286,10 +18286,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45761</v>
+        <v>45764</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18350,7 +18350,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 1213-2025</t>
+          <t>S 1260-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45761</v>
+        <v>45763</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18425,10 +18425,10 @@
       </c>
       <c r="V237" s="2" t="inlineStr"/>
     </row>
-    <row r="238" ht="15" customHeight="1">
+    <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 1266-2025</t>
+          <t>S 1137-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45764</v>
+        <v>45755</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18457,13 +18457,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>1.1</v>
+        <v>10.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18502,157 +18497,6 @@
         <v>0</v>
       </c>
       <c r="V238" s="2" t="inlineStr"/>
-    </row>
-    <row r="239" ht="15" customHeight="1">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>S 1260-2025</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D239" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E239" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I239" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J239" t="n">
-        <v>0</v>
-      </c>
-      <c r="K239" t="n">
-        <v>0</v>
-      </c>
-      <c r="L239" t="n">
-        <v>0</v>
-      </c>
-      <c r="M239" t="n">
-        <v>0</v>
-      </c>
-      <c r="N239" t="n">
-        <v>0</v>
-      </c>
-      <c r="O239" t="n">
-        <v>0</v>
-      </c>
-      <c r="P239" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0</v>
-      </c>
-      <c r="S239" t="n">
-        <v>0</v>
-      </c>
-      <c r="T239" t="n">
-        <v>0</v>
-      </c>
-      <c r="U239" t="n">
-        <v>0</v>
-      </c>
-      <c r="V239" s="2" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>S 1137-2025</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D240" s="1" t="n">
-        <v>45755</v>
-      </c>
-      <c r="E240" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I240" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J240" t="n">
-        <v>0</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0</v>
-      </c>
-      <c r="L240" t="n">
-        <v>0</v>
-      </c>
-      <c r="M240" t="n">
-        <v>0</v>
-      </c>
-      <c r="N240" t="n">
-        <v>0</v>
-      </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="P240" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="n">
-        <v>0</v>
-      </c>
-      <c r="T240" t="n">
-        <v>0</v>
-      </c>
-      <c r="U240" t="n">
-        <v>0</v>
-      </c>
-      <c r="V240" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE238"/>
+  <dimension ref="A1:AE237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>44938</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44762</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58185-2025</t>
+          <t>A 57938-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45983</v>
+        <v>45982</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58185-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 57938-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45982</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44655</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44692</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44487</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44617</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7742-2022</t>
+          <t>A 64406-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44608</v>
+        <v>44511</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 64406-2021</t>
+          <t>A 7742-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44511</v>
+        <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44888</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44752</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44480</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44655</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26086-2022</t>
+          <t>A 24106-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44734</v>
+        <v>44725</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17169-2025</t>
+          <t>A 131-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45755</v>
+        <v>44918</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12861-2022</t>
+          <t>A 3748-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44642</v>
+        <v>45321</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42146-2022</t>
+          <t>A 48627-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44830</v>
+        <v>44859</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13201-2025</t>
+          <t>A 48638-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45735</v>
+        <v>44859</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60298-2022</t>
+          <t>A 45426-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44910</v>
+        <v>45576</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8465-2023</t>
+          <t>A 10154-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44977</v>
+        <v>44979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29490-2024</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45483</v>
+        <v>44496</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44607-2023</t>
+          <t>A 16986-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45184</v>
+        <v>45755</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4286,13 +4286,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4335,7 +4330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17656-2023</t>
+          <t>A 19645-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4349,10 +4344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45036</v>
+        <v>45432</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4365,7 +4360,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4408,7 +4403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14073-2025</t>
+          <t>A 50100-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4422,10 +4417,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45740</v>
+        <v>45598</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4437,13 +4432,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4486,7 +4476,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16069-2025</t>
+          <t>A 1627-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4500,10 +4490,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45749</v>
+        <v>45306</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4516,7 +4506,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.7</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4559,7 +4549,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54390-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4573,10 +4563,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45226</v>
+        <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4589,7 +4579,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4632,7 +4622,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61576-2025</t>
+          <t>A 609-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4642,14 +4632,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46002</v>
+        <v>46023</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4662,7 +4652,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4705,7 +4695,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16986-2025</t>
+          <t>A 48875-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4715,14 +4705,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45755</v>
+        <v>45594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4734,8 +4724,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4778,7 +4773,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60572-2021</t>
+          <t>A 35131-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44496</v>
+        <v>45529</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4808,7 +4803,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4851,7 +4846,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14597-2023</t>
+          <t>A 58842-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4861,14 +4856,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45013</v>
+        <v>44903</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4881,7 +4876,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4924,7 +4919,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7136-2024</t>
+          <t>A 55730-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4934,14 +4929,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45343</v>
+        <v>44476</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4954,7 +4949,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4997,7 +4992,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45426-2024</t>
+          <t>A 32279-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45576</v>
+        <v>45109</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5027,7 +5022,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5070,7 +5065,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63614-2023</t>
+          <t>A 60572-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5084,10 +5079,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45275</v>
+        <v>44496</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5100,7 +5095,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5143,7 +5138,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50100-2024</t>
+          <t>A 45422-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45598</v>
+        <v>45576</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5173,7 +5168,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>17.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5216,7 +5211,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48875-2024</t>
+          <t>A 55434-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5226,14 +5221,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45594</v>
+        <v>44475</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5245,13 +5240,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5294,7 +5284,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1788-2023</t>
+          <t>A 64397-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5308,10 +5298,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44937</v>
+        <v>44511</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5324,7 +5314,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5367,7 +5357,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 45422-2024</t>
+          <t>A 42416-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45576</v>
+        <v>45905</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5397,7 +5387,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>17.1</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5440,7 +5430,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45149-2023</t>
+          <t>A 42455-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5454,10 +5444,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45191</v>
+        <v>45905</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5470,7 +5460,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5513,7 +5503,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4959-2022</t>
+          <t>A 22866-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5527,10 +5517,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44593</v>
+        <v>45448</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5543,7 +5533,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5586,7 +5576,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5349-2022</t>
+          <t>A 27960-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5600,10 +5590,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44594</v>
+        <v>45817</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5616,7 +5606,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5659,7 +5649,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 42455-2025</t>
+          <t>A 2601-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,10 +5663,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45905</v>
+        <v>46037</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5689,7 +5679,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5732,7 +5722,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 42416-2025</t>
+          <t>A 9543-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5746,10 +5736,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45905</v>
+        <v>44617</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5761,8 +5751,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5805,7 +5800,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32325-2023</t>
+          <t>A 61840-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5819,10 +5814,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45120</v>
+        <v>44917</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5834,13 +5829,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5883,7 +5873,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12716-2023</t>
+          <t>A 61842-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5897,10 +5887,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44999</v>
+        <v>44917</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5912,13 +5902,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5961,7 +5946,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 27960-2025</t>
+          <t>A 60298-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5975,10 +5960,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45817</v>
+        <v>44910</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5991,7 +5976,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6034,7 +6019,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24382-2023</t>
+          <t>A 18182-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6048,10 +6033,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45076</v>
+        <v>45041</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6064,7 +6049,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6107,7 +6092,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24414-2023</t>
+          <t>A 16495-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6121,10 +6106,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45076</v>
+        <v>44671</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6137,7 +6122,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6180,7 +6165,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10440-2022</t>
+          <t>A 20427-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6190,14 +6175,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44623</v>
+        <v>45056</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6210,7 +6195,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6253,7 +6238,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55730-2021</t>
+          <t>A 1460-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6267,10 +6252,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44476</v>
+        <v>44937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6283,7 +6268,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6326,7 +6311,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 1714-2023</t>
+          <t>A 49153-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6340,10 +6325,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44938</v>
+        <v>45594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6356,7 +6341,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6399,7 +6384,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58842-2022</t>
+          <t>A 1721-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6409,14 +6394,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44903</v>
+        <v>44938</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6429,7 +6414,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6472,7 +6457,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17435-2022</t>
+          <t>A 25493-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6486,10 +6471,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44678</v>
+        <v>45803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6502,7 +6487,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6545,7 +6530,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18182-2023</t>
+          <t>A 12714-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6559,10 +6544,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45041</v>
+        <v>45733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6575,7 +6560,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6618,7 +6603,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 131-2023</t>
+          <t>A 18241-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6632,10 +6617,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44918</v>
+        <v>44685</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6648,7 +6633,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6691,7 +6676,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25493-2025</t>
+          <t>A 39779-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6705,10 +6690,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45803</v>
+        <v>45552</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6721,7 +6706,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6764,7 +6749,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 45425-2024</t>
+          <t>A 37740-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6778,10 +6763,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45576</v>
+        <v>45880</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6794,7 +6779,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6837,7 +6822,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18241-2022</t>
+          <t>A 53316-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6851,10 +6836,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44685</v>
+        <v>45959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6867,7 +6852,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6910,7 +6895,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12714-2025</t>
+          <t>A 60578-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6924,10 +6909,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45733</v>
+        <v>44496</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6940,7 +6925,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6983,7 +6968,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 609-2026</t>
+          <t>A 12716-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6997,10 +6982,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46023</v>
+        <v>44999</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7012,8 +6997,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7056,7 +7046,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 27238-2023</t>
+          <t>A 57393-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7070,10 +7060,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45096</v>
+        <v>45980</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7085,13 +7075,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7134,7 +7119,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50756-2023</t>
+          <t>A 57862-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7148,10 +7133,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45210</v>
+        <v>45981</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7163,8 +7148,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7207,7 +7197,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 19645-2024</t>
+          <t>A 58174-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7221,10 +7211,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45432</v>
+        <v>45982</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7237,7 +7227,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7280,7 +7270,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16617-2025</t>
+          <t>A 10546-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7294,10 +7284,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45754</v>
+        <v>46077</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7309,13 +7299,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7358,7 +7343,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 64397-2021</t>
+          <t>A 10549-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7372,10 +7357,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44511</v>
+        <v>46077</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7388,7 +7373,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7431,7 +7416,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54780-2023</t>
+          <t>A 27238-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7445,10 +7430,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45236</v>
+        <v>45096</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7460,8 +7445,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7504,7 +7494,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 53316-2025</t>
+          <t>A 54978-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7518,10 +7508,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45959</v>
+        <v>44474</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7534,7 +7524,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7577,7 +7567,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37740-2025</t>
+          <t>A 29490-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7591,10 +7581,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45880</v>
+        <v>45483</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7607,7 +7597,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7650,7 +7640,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19165-2024</t>
+          <t>A 60467-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7664,10 +7654,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45428</v>
+        <v>45995</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7680,7 +7670,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7723,7 +7713,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42084-2023</t>
+          <t>A 20192-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7737,10 +7727,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45175</v>
+        <v>45051</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7753,7 +7743,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7796,7 +7786,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2601-2026</t>
+          <t>A 61576-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7806,14 +7796,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46037</v>
+        <v>46002</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7826,7 +7816,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7869,7 +7859,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57862-2025</t>
+          <t>A 8997-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7879,14 +7869,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45981</v>
+        <v>46069</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7898,13 +7888,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>15.9</v>
+        <v>5.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7947,7 +7932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 45162-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7961,10 +7946,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44594</v>
+        <v>45191</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7977,7 +7962,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8020,7 +8005,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57393-2025</t>
+          <t>A 466-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8034,10 +8019,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45980</v>
+        <v>45297</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8050,7 +8035,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8093,7 +8078,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 20301-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8107,10 +8092,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44496</v>
+        <v>45774</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8123,7 +8108,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8166,7 +8151,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58174-2025</t>
+          <t>A 21160-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8180,10 +8165,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45982</v>
+        <v>45440</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8196,7 +8181,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8239,7 +8224,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 54978-2021</t>
+          <t>A 2888-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8253,10 +8238,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44474</v>
+        <v>44945</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8269,7 +8254,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8312,7 +8297,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 27341-2022</t>
+          <t>A 55640-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8326,10 +8311,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44742</v>
+        <v>44888</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8342,7 +8327,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8385,7 +8370,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 60467-2025</t>
+          <t>A 55092-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8399,10 +8384,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45995</v>
+        <v>45237</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8415,7 +8400,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8458,7 +8443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59988-2022</t>
+          <t>A 54780-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8472,10 +8457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44902</v>
+        <v>45236</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8488,7 +8473,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8531,7 +8516,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 192-2024</t>
+          <t>A 19861-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8545,10 +8530,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45294</v>
+        <v>45053</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8561,7 +8546,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8604,7 +8589,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35131-2024</t>
+          <t>A 13201-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8618,10 +8603,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45529</v>
+        <v>45735</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8634,7 +8619,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8677,7 +8662,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63764-2023</t>
+          <t>A 24382-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8691,10 +8676,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45278</v>
+        <v>45076</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8707,7 +8692,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8750,7 +8735,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 10546-2026</t>
+          <t>A 54112-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8764,10 +8749,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46077</v>
+        <v>44470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8780,7 +8765,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8823,7 +8808,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10549-2026</t>
+          <t>A 24414-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8837,10 +8822,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46077</v>
+        <v>45076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8853,7 +8838,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8896,7 +8881,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 58908-2024</t>
+          <t>A 17731-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8906,14 +8891,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45636</v>
+        <v>46121</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8926,7 +8911,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8969,7 +8954,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2888-2023</t>
+          <t>A 54051-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8983,10 +8968,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44945</v>
+        <v>45615</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8999,7 +8984,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>8.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9042,7 +9027,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 2586-2023</t>
+          <t>A 132-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9056,10 +9041,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44943</v>
+        <v>44918</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9072,7 +9057,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9115,7 +9100,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8997-2026</t>
+          <t>A 63614-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9125,14 +9110,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46069</v>
+        <v>45275</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9145,7 +9130,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9188,7 +9173,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 465-2024</t>
+          <t>A 32325-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9202,10 +9187,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45297</v>
+        <v>45120</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9217,8 +9202,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9261,7 +9251,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1670-2022</t>
+          <t>A 16071-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9275,10 +9265,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44573</v>
+        <v>45021</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9291,7 +9281,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9334,7 +9324,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61840-2022</t>
+          <t>A 19792-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9348,10 +9338,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44917</v>
+        <v>46135</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9364,7 +9354,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9407,7 +9397,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61842-2022</t>
+          <t>A 19920-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9421,10 +9411,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44917</v>
+        <v>46136</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9437,7 +9427,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9480,7 +9470,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58806-2023</t>
+          <t>A 10440-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9490,14 +9480,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45247</v>
+        <v>44623</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9510,7 +9500,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9553,7 +9543,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 65066-2023</t>
+          <t>A 63584-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9567,10 +9557,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45285</v>
+        <v>45275</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9583,7 +9573,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9626,7 +9616,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 55824-2023</t>
+          <t>A 48644-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9640,10 +9630,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45239</v>
+        <v>44859</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9656,7 +9646,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9699,7 +9689,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 326-2022</t>
+          <t>A 1788-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9713,10 +9703,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44565</v>
+        <v>44937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9729,7 +9719,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9772,7 +9762,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 11376-2023</t>
+          <t>A 46464-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9782,14 +9772,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44990</v>
+        <v>45582</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9802,7 +9792,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9845,7 +9835,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 17731-2026</t>
+          <t>A 58801-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9855,14 +9845,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46121</v>
+        <v>45986</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9875,7 +9865,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9918,7 +9908,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 50099-2024</t>
+          <t>A 11371-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9932,10 +9922,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45597</v>
+        <v>44990</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9948,7 +9938,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9991,7 +9981,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 48638-2022</t>
+          <t>A 19165-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10005,10 +9995,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44859</v>
+        <v>45428</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10021,7 +10011,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10064,7 +10054,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 132-2023</t>
+          <t>A 20243-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10078,10 +10068,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44918</v>
+        <v>46136</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10094,7 +10084,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10137,7 +10127,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1627-2024</t>
+          <t>A 41870-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10147,14 +10137,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45306</v>
+        <v>45174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10167,7 +10157,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10210,7 +10200,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19792-2026</t>
+          <t>A 8442-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10224,10 +10214,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46135</v>
+        <v>44977</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10240,7 +10230,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10283,7 +10273,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 48620-2022</t>
+          <t>A 1128-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10293,14 +10283,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44859</v>
+        <v>45302</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10313,7 +10303,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10356,7 +10346,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 48627-2022</t>
+          <t>A 17768-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10370,10 +10360,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44859</v>
+        <v>45418</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10386,7 +10376,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10429,7 +10419,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 57632-2024</t>
+          <t>A 11400-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10443,10 +10433,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45630</v>
+        <v>44993</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,8 +10448,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>18.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10502,7 +10497,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 48631-2022</t>
+          <t>A 1670-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10516,10 +10511,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44859</v>
+        <v>44573</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10532,7 +10527,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10575,7 +10570,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 48644-2022</t>
+          <t>A 6824-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10589,10 +10584,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44859</v>
+        <v>44967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10605,7 +10600,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10648,7 +10643,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 55434-2021</t>
+          <t>A 16617-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10662,10 +10657,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44475</v>
+        <v>45754</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,8 +10672,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10721,7 +10721,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 45162-2023</t>
+          <t>A 18797-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10735,10 +10735,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45191</v>
+        <v>45764</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10750,8 +10750,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10794,7 +10799,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 46464-2024</t>
+          <t>A 5349-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10808,10 +10813,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45582</v>
+        <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10824,7 +10829,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10867,7 +10872,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19920-2026</t>
+          <t>A 57632-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10881,10 +10886,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46136</v>
+        <v>45630</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10897,7 +10902,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10940,7 +10945,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 53863-2021</t>
+          <t>A 17656-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10954,10 +10959,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44468</v>
+        <v>45036</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10970,7 +10975,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11013,7 +11018,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20427-2023</t>
+          <t>A 21551-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11027,10 +11032,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45056</v>
+        <v>46147</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11043,7 +11048,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11086,7 +11091,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 58801-2025</t>
+          <t>A 45731-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11096,14 +11101,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45986</v>
+        <v>45923</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11116,7 +11121,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11159,7 +11164,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32273-2023</t>
+          <t>A 4959-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11173,10 +11178,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45109</v>
+        <v>44593</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11189,7 +11194,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11232,7 +11237,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 20243-2026</t>
+          <t>A 42564-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11246,10 +11251,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46136</v>
+        <v>45181</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11262,7 +11267,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11305,7 +11310,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9543-2022</t>
+          <t>A 14087-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11319,10 +11324,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44617</v>
+        <v>44651</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11336,11 +11341,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11383,7 +11388,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 58224-2022</t>
+          <t>A 24405-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11397,10 +11402,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44893</v>
+        <v>45076</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11413,7 +11418,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11456,7 +11461,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 36649-2023</t>
+          <t>A 22525-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11470,10 +11475,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45153</v>
+        <v>46155</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11486,7 +11491,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11529,7 +11534,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 11371-2023</t>
+          <t>A 5348-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11543,10 +11548,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44990</v>
+        <v>44594</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11559,7 +11564,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11602,7 +11607,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 11400-2023</t>
+          <t>A 326-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11616,10 +11621,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44993</v>
+        <v>44565</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11631,13 +11636,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>18.6</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11680,7 +11680,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17178-2025</t>
+          <t>A 42446-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45755</v>
+        <v>45905</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 1128-2024</t>
+          <t>A 22135-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11763,14 +11763,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45302</v>
+        <v>45069</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 55092-2023</t>
+          <t>A 55824-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11840,10 +11840,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45237</v>
+        <v>45239</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11899,7 +11899,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 45792-2023</t>
+          <t>A 12861-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45195</v>
+        <v>44642</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11928,13 +11928,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11977,7 +11972,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 54112-2021</t>
+          <t>A 27207-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11991,10 +11986,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44470</v>
+        <v>45096</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12006,8 +12001,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21551-2026</t>
+          <t>A 32273-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12064,10 +12064,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46147</v>
+        <v>45109</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12123,7 +12123,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14087-2022</t>
+          <t>A 45792-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12137,10 +12137,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44651</v>
+        <v>45195</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12154,11 +12154,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 20301-2025</t>
+          <t>A 58806-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12215,10 +12215,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45774</v>
+        <v>45247</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 45731-2025</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12284,14 +12284,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45923</v>
+        <v>44734</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12347,7 +12347,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 19861-2023</t>
+          <t>A 34159-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45053</v>
+        <v>44791</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12420,7 +12420,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22835-2023</t>
+          <t>A 46420-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12434,10 +12434,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45072</v>
+        <v>45194</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12449,13 +12449,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12498,7 +12493,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22525-2026</t>
+          <t>A 34019-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12512,10 +12507,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46155</v>
+        <v>45135</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12527,8 +12522,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12571,7 +12571,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 46420-2023</t>
+          <t>A 17178-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12585,10 +12585,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45194</v>
+        <v>45755</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12644,7 +12644,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 10154-2023</t>
+          <t>A 54742-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44979</v>
+        <v>45236</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12717,7 +12717,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 42446-2025</t>
+          <t>A 17169-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45905</v>
+        <v>45755</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12790,7 +12790,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 356-2022</t>
+          <t>A 26141-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12804,10 +12804,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44565</v>
+        <v>46181</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>13.4</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12863,7 +12863,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 63584-2023</t>
+          <t>A 3304-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12877,10 +12877,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45275</v>
+        <v>45317</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12936,7 +12936,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24106-2022</t>
+          <t>A 26144-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44725</v>
+        <v>46181</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13009,7 +13009,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 34159-2022</t>
+          <t>A 26146-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44791</v>
+        <v>46181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13082,7 +13082,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 2270-2023</t>
+          <t>A 26142-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13096,10 +13096,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44942</v>
+        <v>46181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>9.1</v>
+        <v>3.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13155,7 +13155,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 24405-2023</t>
+          <t>A 26147-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13169,10 +13169,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45076</v>
+        <v>46181</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13228,7 +13228,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 32316-2023</t>
+          <t>A 26155-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13242,10 +13242,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45120</v>
+        <v>46181</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13257,13 +13257,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13306,7 +13301,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 8442-2023</t>
+          <t>A 41952-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13320,10 +13315,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44977</v>
+        <v>44830</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13336,7 +13331,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13379,7 +13374,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 27207-2023</t>
+          <t>A 192-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13393,10 +13388,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45096</v>
+        <v>45294</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13408,13 +13403,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13457,7 +13447,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32279-2023</t>
+          <t>A 50756-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13471,10 +13461,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45109</v>
+        <v>45210</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13487,7 +13477,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>11.8</v>
+        <v>3.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13530,7 +13520,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 55640-2022</t>
+          <t>A 26143-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13544,10 +13534,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44888</v>
+        <v>46181</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13560,7 +13550,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13603,7 +13593,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 54051-2024</t>
+          <t>A 32316-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13617,10 +13607,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45615</v>
+        <v>45120</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13632,8 +13622,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>8.9</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13676,7 +13671,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 22866-2024</t>
+          <t>A 17435-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13690,10 +13685,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45448</v>
+        <v>44678</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13706,7 +13701,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13749,7 +13744,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 54742-2023</t>
+          <t>A 7825-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13763,10 +13758,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45236</v>
+        <v>44608</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13779,7 +13774,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13822,7 +13817,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 23415-2023</t>
+          <t>A 27978-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13836,10 +13831,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45076</v>
+        <v>46195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13852,7 +13847,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13895,7 +13890,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 3748-2024</t>
+          <t>A 56627-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13909,10 +13904,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45321</v>
+        <v>45243</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13925,7 +13920,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13968,7 +13963,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 26141-2026</t>
+          <t>A 45149-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13982,10 +13977,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46181</v>
+        <v>45191</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13998,7 +13993,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14041,7 +14036,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 26142-2026</t>
+          <t>A 11376-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14051,14 +14046,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46181</v>
+        <v>44990</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14071,7 +14066,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14114,7 +14109,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 26147-2026</t>
+          <t>A 61534-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14128,10 +14123,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46181</v>
+        <v>44910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14143,8 +14138,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14187,7 +14187,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 26155-2026</t>
+          <t>A 30931-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46181</v>
+        <v>45498</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 26143-2026</t>
+          <t>A 45425-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14274,10 +14274,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46181</v>
+        <v>45576</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14333,7 +14333,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 26144-2026</t>
+          <t>A 35257-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14347,10 +14347,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46181</v>
+        <v>44798</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26146-2026</t>
+          <t>A 7136-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14416,14 +14416,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46181</v>
+        <v>45343</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14479,7 +14479,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 19860-2023</t>
+          <t>A 22835-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14493,10 +14493,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45053</v>
+        <v>45072</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14508,8 +14508,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14552,7 +14557,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 466-2024</t>
+          <t>A 2270-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14566,10 +14571,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45297</v>
+        <v>44942</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14582,7 +14587,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.9</v>
+        <v>9.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14625,7 +14630,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 41952-2022</t>
+          <t>A 36649-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14639,10 +14644,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44830</v>
+        <v>45153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14655,7 +14660,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14698,7 +14703,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 41870-2023</t>
+          <t>A 356-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14708,14 +14713,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45174</v>
+        <v>44565</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14728,7 +14733,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.8</v>
+        <v>13.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14771,7 +14776,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 39779-2024</t>
+          <t>A 1668-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14785,10 +14790,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45552</v>
+        <v>44573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14801,7 +14806,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14844,7 +14849,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 16071-2023</t>
+          <t>A 34157-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14858,10 +14863,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45021</v>
+        <v>46253</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14874,7 +14879,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14917,7 +14922,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27978-2026</t>
+          <t>A 48620-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14931,10 +14936,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46195</v>
+        <v>44859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14947,7 +14952,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14990,7 +14995,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 61825-2022</t>
+          <t>A 14597-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15004,10 +15009,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44917</v>
+        <v>45013</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15020,7 +15025,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15063,7 +15068,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32522-2023</t>
+          <t>A 31377-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15077,10 +15082,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45110</v>
+        <v>46213</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15092,8 +15097,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15136,7 +15146,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 16495-2022</t>
+          <t>A 50099-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15150,10 +15160,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44671</v>
+        <v>45597</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15166,7 +15176,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15209,7 +15219,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 3304-2024</t>
+          <t>A 31375-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15219,14 +15229,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45317</v>
+        <v>46213</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15238,8 +15248,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15282,7 +15297,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 22135-2023</t>
+          <t>A 23429-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15296,10 +15311,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45069</v>
+        <v>45076</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15312,7 +15327,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15355,7 +15370,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30931-2024</t>
+          <t>A 32522-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15369,10 +15384,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45498</v>
+        <v>45110</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15385,7 +15400,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15428,7 +15443,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 18797-2025</t>
+          <t>A 42084-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15442,10 +15457,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45764</v>
+        <v>45175</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15457,13 +15472,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15506,7 +15516,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 17768-2024</t>
+          <t>A 64770-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15520,10 +15530,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45418</v>
+        <v>45281</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15536,7 +15546,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15579,7 +15589,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34157-2026</t>
+          <t>A 42146-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15593,10 +15603,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46253</v>
+        <v>44830</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15609,7 +15619,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15652,7 +15662,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 21160-2024</t>
+          <t>A 61825-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15666,10 +15676,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45440</v>
+        <v>44917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15682,7 +15692,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15725,7 +15735,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31377-2026</t>
+          <t>A 1714-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15739,10 +15749,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46213</v>
+        <v>44938</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15754,13 +15764,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15803,7 +15808,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 42564-2023</t>
+          <t>A 35638-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15817,10 +15822,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45181</v>
+        <v>46265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15833,7 +15838,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15876,7 +15881,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20192-2023</t>
+          <t>A 8465-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15890,10 +15895,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45051</v>
+        <v>44977</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15906,7 +15911,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15949,7 +15954,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31375-2026</t>
+          <t>A 63764-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15959,14 +15964,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46213</v>
+        <v>45278</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15978,13 +15983,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16027,7 +16027,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 56627-2023</t>
+          <t>A 35687-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16041,10 +16041,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45243</v>
+        <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16056,8 +16056,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16100,7 +16105,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 35638-2026</t>
+          <t>A 35686-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16117,7 +16122,7 @@
         <v>46265</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16127,6 +16132,11 @@
       <c r="G207" t="inlineStr">
         <is>
           <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I207" t="n">
@@ -16173,7 +16183,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35686-2026</t>
+          <t>A 35683-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16190,7 +16200,7 @@
         <v>46265</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16208,7 +16218,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16251,7 +16261,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 64770-2023</t>
+          <t>A 48631-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16265,10 +16275,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45281</v>
+        <v>44859</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16281,7 +16291,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16324,7 +16334,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35683-2026</t>
+          <t>A 58908-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16338,10 +16348,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46265</v>
+        <v>45636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16353,13 +16363,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16402,7 +16407,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35687-2026</t>
+          <t>A 34130-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16416,10 +16421,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16431,13 +16436,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16480,7 +16480,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 35257-2022</t>
+          <t>A 31913-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16494,10 +16494,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44798</v>
+        <v>46231</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16553,7 +16553,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 49153-2024</t>
+          <t>A 44607-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16567,10 +16567,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45594</v>
+        <v>45184</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16582,8 +16582,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16626,7 +16631,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 34130-2026</t>
+          <t>A 58224-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16640,10 +16645,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46253</v>
+        <v>44893</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16656,7 +16661,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16699,7 +16704,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 1668-2022</t>
+          <t>A 37229-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16713,10 +16718,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44573</v>
+        <v>46274</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16729,7 +16734,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16772,7 +16777,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 23429-2023</t>
+          <t>A 19860-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16786,10 +16791,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45076</v>
+        <v>45053</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16802,7 +16807,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16845,7 +16850,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31913-2026</t>
+          <t>A 37334-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16859,10 +16864,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46231</v>
+        <v>46274</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16874,8 +16879,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>10.1</v>
+        <v>1.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16935,7 +16945,7 @@
         <v>46274</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17013,7 +17023,7 @@
         <v>46275</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17074,7 +17084,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37229-2026</t>
+          <t>A 57608-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17088,10 +17098,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46274</v>
+        <v>45630</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17104,7 +17114,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17147,7 +17157,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 7825-2022</t>
+          <t>A 27341-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17161,10 +17171,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44608</v>
+        <v>44742</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17177,7 +17187,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17220,7 +17230,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 37334-2026</t>
+          <t>A 23415-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17234,10 +17244,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46274</v>
+        <v>45076</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17249,13 +17259,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17298,7 +17303,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 5348-2022</t>
+          <t>A 65066-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17312,10 +17317,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44594</v>
+        <v>45285</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17328,7 +17333,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17371,7 +17376,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 61534-2022</t>
+          <t>A 465-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17385,10 +17390,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44910</v>
+        <v>45297</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17400,13 +17405,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17449,7 +17449,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 57608-2024</t>
+          <t>A 59988-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17463,10 +17463,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45630</v>
+        <v>44902</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17522,7 +17522,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 6824-2023</t>
+          <t>A 2586-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17536,10 +17536,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44967</v>
+        <v>44943</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 34019-2023</t>
+          <t>A 39830-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17605,14 +17605,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45135</v>
+        <v>46290</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17624,13 +17624,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17673,7 +17668,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 60578-2021</t>
+          <t>A 16069-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17687,10 +17682,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44496</v>
+        <v>45749</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17703,7 +17698,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.9</v>
+        <v>6.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17746,7 +17741,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 1460-2023</t>
+          <t>A 14073-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17760,10 +17755,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44937</v>
+        <v>45740</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17775,8 +17770,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17819,7 +17819,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 1721-2023</t>
+          <t>A 28003-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17833,10 +17833,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44938</v>
+        <v>44744</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 28003-2022</t>
+          <t>A 54390-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17906,10 +17906,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44744</v>
+        <v>45226</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17965,24 +17965,24 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 39830-2026</t>
+          <t>S 1502-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46290</v>
+        <v>45051</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17994,8 +17994,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18038,7 +18043,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S 1502-2023</t>
+          <t>S 1214-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18052,10 +18057,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45051</v>
+        <v>45761</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18069,11 +18074,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18116,7 +18121,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 1214-2025</t>
+          <t>S 1213-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18133,7 +18138,7 @@
         <v>45761</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18151,7 +18156,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18194,7 +18199,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 1213-2025</t>
+          <t>S 1266-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18208,10 +18213,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45761</v>
+        <v>45764</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18229,7 +18234,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18272,7 +18277,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 1266-2025</t>
+          <t>S 1260-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18286,10 +18291,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45764</v>
+        <v>45763</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18307,7 +18312,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18347,10 +18352,10 @@
       </c>
       <c r="V236" s="2" t="inlineStr"/>
     </row>
-    <row r="237" ht="15" customHeight="1">
+    <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 1260-2025</t>
+          <t>S 1137-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18364,10 +18369,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45763</v>
+        <v>45755</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18379,13 +18384,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>10.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18424,79 +18424,6 @@
         <v>0</v>
       </c>
       <c r="V237" s="2" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>S 1137-2025</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D238" s="1" t="n">
-        <v>45755</v>
-      </c>
-      <c r="E238" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I238" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J238" t="n">
-        <v>0</v>
-      </c>
-      <c r="K238" t="n">
-        <v>0</v>
-      </c>
-      <c r="L238" t="n">
-        <v>0</v>
-      </c>
-      <c r="M238" t="n">
-        <v>0</v>
-      </c>
-      <c r="N238" t="n">
-        <v>0</v>
-      </c>
-      <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="P238" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0</v>
-      </c>
-      <c r="S238" t="n">
-        <v>0</v>
-      </c>
-      <c r="T238" t="n">
-        <v>0</v>
-      </c>
-      <c r="U238" t="n">
-        <v>0</v>
-      </c>
-      <c r="V238" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VINGÅKER.xlsx
+++ b/Översikt VINGÅKER.xlsx
@@ -601,7 +601,7 @@
         <v>45226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45001</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44872</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44518</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 10541-2026</t>
+          <t>A 1826-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46077</v>
+        <v>44938</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1111,264 +1111,264 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Vanlig backsmörblomma
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 1826-2023 artfynd.xlsx", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 1826-2023 karta.png", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 1826-2023 georefererad karta.tif", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 1826-2023 FSC-klagomål.docx", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 1826-2023 FSC-klagomål mail.docx", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 1826-2023 tillsynsbegäran.docx", "A 1826-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 1826-2023 tillsynsbegäran mail.docx", "A 1826-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 30575-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44762</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Skogsknipprot
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 30575-2022 artfynd.xlsx", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 30575-2022 karta.png", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 30575-2022 georefererad karta.tif", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 30575-2022 FSC-klagomål.docx", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 30575-2022 FSC-klagomål mail.docx", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 30575-2022 tillsynsbegäran.docx", "A 30575-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 30575-2022 tillsynsbegäran mail.docx", "A 30575-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 10541-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Ekticka
 Rödvingetrast
 Spillkråka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 10541-2026 artfynd.xlsx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 10541-2026 karta.png", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 10541-2026 georefererad karta.tif", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 10541-2026 FSC-klagomål.docx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 10541-2026 FSC-klagomål mail.docx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 10541-2026 tillsynsbegäran.docx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 10541-2026 tillsynsbegäran mail.docx", "A 10541-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 10541-2026 prioriterade fågelarter.docx", "A 10541-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 1826-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44938</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Vanlig backsmörblomma
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 1826-2023 artfynd.xlsx", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 1826-2023 karta.png", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 1826-2023 georefererad karta.tif", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 1826-2023 FSC-klagomål.docx", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 1826-2023 FSC-klagomål mail.docx", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 1826-2023 tillsynsbegäran.docx", "A 1826-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 1826-2023 tillsynsbegäran mail.docx", "A 1826-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 30575-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44762</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Skogsknipprot
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 30575-2022 artfynd.xlsx", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 30575-2022 karta.png", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 30575-2022 georefererad karta.tif", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 30575-2022 FSC-klagomål.docx", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 30575-2022 FSC-klagomål mail.docx", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 30575-2022 tillsynsbegäran.docx", "A 30575-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 30575-2022 tillsynsbegäran mail.docx", "A 30575-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44686</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44482</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57938-2025</t>
+          <t>A 58185-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1767,147 +1767,147 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 57938-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VINGÅKER</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 57938-2025 artfynd.xlsx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 57938-2025 karta.png", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 57938-2025 georefererad karta.tif", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 57938-2025 FSC-klagomål.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 57938-2025 FSC-klagomål mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 57938-2025 tillsynsbegäran.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 57938-2025 tillsynsbegäran mail.docx", "A 57938-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 57938-2025 prioriterade fågelarter.docx", "A 57938-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58185-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VINGÅKER</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/artfynd/A 58185-2025 artfynd.xlsx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor/A 58185-2025 karta.png", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/kartor_geotiff/A 58185-2025 georefererad karta.tif", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomål/A 58185-2025 FSC-klagomål.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/klagomålsmail/A 58185-2025 FSC-klagomål mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsyn/A 58185-2025 tillsynsbegäran.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/tillsynsmail/A 58185-2025 tillsynsbegäran mail.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0428/fåglar/A 58185-2025 prioriterade fågelarter.docx", "A 58185-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 14537-2022</t>
+          <t>A 7821-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44655</v>
+        <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2013,13 +2013,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2062,7 +2057,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10438-2022</t>
+          <t>A 14537-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2072,14 +2067,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44623</v>
+        <v>44655</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2091,8 +2086,13 @@
           <t>VINGÅKER</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7821-2022</t>
+          <t>A 10438-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2145,14 +2145,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44608</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44525</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19370-2022</t>
+          <t>A 7742-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44692</v>
+        <v>44608</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58031-2021</t>
+          <t>A 64406-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44487</v>
+        <v>44511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9648-2022</t>
+          <t>A 42161-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44617</v>
+        <v>44830</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 64406-2021</t>
+          <t>A 19370-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44511</v>
+        <v>44692</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7742-2022</t>
+          <t>A 51891-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44608</v>
+        <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2865,7 +2865,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42161-2022</t>
+          <t>A 58031-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44830</v>
+        <v>44487</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2938,7 +2938,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51891-2022</t>
+          <t>A 11326-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44867</v>
+        <v>44629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>10.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55645-2022</t>
+          <t>A 9648-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44888</v>
+        <v>44617</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11326-2022</t>
+          <t>A 29366-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44629</v>
+        <v>44752</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.4</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29366-2022</t>
+          <t>A 12856-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44752</v>
+        <v>44642</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
         <v>44735</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44480</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17628-2022</t>
+          <t>A 55450-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44680</v>
+        <v>44475</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14522-2022</t>
+          <t>A 55645-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44655</v>
+        <v>44888</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3478,13 +3478,8 @@
           <t>VINGÅKER</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3527,7 +3522,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12856-2022</t>
+          <t>A 17628-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3541,10 +3536,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44642</v>
+        <v>44680</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3557,7 +3552,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3600,7 +3595,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 55450-2021</t>
+          <t>A 26086-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,10 +3609,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44475</v>
+        <v>44734</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>